--- a/MSE__API__Plano_de_Desenvolvimentos_2026.xlsx
+++ b/MSE__API__Plano_de_Desenvolvimentos_2026.xlsx
@@ -2770,32 +2770,12 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -2816,27 +2796,20 @@
       <family val="2"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="45">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3037,13 +3010,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF305496"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
+        <fgColor rgb="FFF8CBAD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3067,37 +3034,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4B183"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
+        <fgColor rgb="FF9DC3E6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6E0B4"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF70AD47"/>
+        <fgColor rgb="FF548235"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4919,7 +4880,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="594">
+  <cellXfs count="588">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6592,7 +6553,7 @@
     <xf numFmtId="0" fontId="95" fillId="32" applyFill="1" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="32" applyFill="1" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="102" fillId="32" applyFill="1" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="96" fillId="33" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
@@ -6601,32 +6562,26 @@
     <xf numFmtId="0" fontId="96" fillId="33" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="106" fillId="33" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="99" fillId="33" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="44" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="99" fillId="42" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="34" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="43" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="43" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="43" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="98" fillId="34" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="98" fillId="35" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6648,18 +6603,6 @@
     </xf>
     <xf numFmtId="0" fontId="98" fillId="41" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="42" applyFill="1" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="140" applyBorder="1" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -16447,15 +16390,15 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BG55"/>
+  <dimension ref="A1:BG35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="54" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="59" width="3.6" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16467,72 +16410,66 @@
       </c>
       <c r="G1" s="571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Versão semanal · 53 semanas (W01–W53) · Semana atual: W25 (18-06-2026) · Fonte: «Overview Geral»</t>
+          <t xml:space="preserve">Versão semanal (W01–W53) · dados da calendarização original · Semana atual: W25</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:59">
-      <c r="A2" s="592" t="inlineStr">
+      <c r="A2" s="578" t="inlineStr">
         <is>
           <t xml:space="preserve">Legenda (fase):</t>
         </is>
       </c>
-      <c r="G2" s="583"/>
-      <c r="H2" s="592" t="inlineStr">
+      <c r="G2" s="580"/>
+      <c r="H2" s="578" t="inlineStr">
         <is>
           <t xml:space="preserve">Em Research</t>
         </is>
       </c>
-      <c r="K2" s="584"/>
-      <c r="L2" s="592" t="inlineStr">
+      <c r="K2" s="581"/>
+      <c r="L2" s="578" t="inlineStr">
         <is>
           <t xml:space="preserve">Em Escrita</t>
         </is>
       </c>
-      <c r="O2" s="585"/>
-      <c r="P2" s="592" t="inlineStr">
+      <c r="O2" s="582"/>
+      <c r="P2" s="578" t="inlineStr">
         <is>
           <t xml:space="preserve">User Stories</t>
         </is>
       </c>
-      <c r="S2" s="586"/>
-      <c r="T2" s="592" t="inlineStr">
+      <c r="S2" s="583"/>
+      <c r="T2" s="578" t="inlineStr">
         <is>
-          <t xml:space="preserve">US Escritas</t>
+          <t xml:space="preserve">User Stories Escritas</t>
         </is>
       </c>
-      <c r="W2" s="587"/>
-      <c r="X2" s="592" t="inlineStr">
+      <c r="W2" s="584"/>
+      <c r="X2" s="578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Em Design</t>
+          <t xml:space="preserve">Em Design (Bliss)</t>
         </is>
       </c>
-      <c r="AA2" s="588"/>
-      <c r="AB2" s="592" t="inlineStr">
+      <c r="AA2" s="585"/>
+      <c r="AB2" s="578" t="inlineStr">
         <is>
           <t xml:space="preserve">Desenvolvimento IT</t>
         </is>
       </c>
-      <c r="AE2" s="589"/>
-      <c r="AF2" s="592" t="inlineStr">
+      <c r="AE2" s="586"/>
+      <c r="AF2" s="578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qualidade/Certif. (QUA→PROD)</t>
+          <t xml:space="preserve">Certificação</t>
         </is>
       </c>
-      <c r="AI2" s="590"/>
-      <c r="AJ2" s="592" t="inlineStr">
+      <c r="AI2" s="587"/>
+      <c r="AJ2" s="578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Produção (go-live)</t>
+          <t xml:space="preserve">Produção</t>
         </is>
       </c>
-      <c r="AM2" s="582"/>
-      <c r="AN2" s="592" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Standby</t>
-        </is>
-      </c>
-      <c r="AQ2" s="575"/>
-      <c r="AR2" s="592" t="inlineStr">
+      <c r="AM2" s="575"/>
+      <c r="AN2" s="578" t="inlineStr">
         <is>
           <t xml:space="preserve">Semana atual</t>
         </is>
@@ -16897,714 +16834,667 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="1:59">
+    <row r="5" ht="26" customHeight="1" spans="1:59">
       <c r="A5" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit Lab   (12 projetos)</t>
+          <t xml:space="preserve">Confirming</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="70" customHeight="1" spans="1:59">
-      <c r="A6" s="577" t="inlineStr">
+      <c r="B5" s="577"/>
+      <c r="C5" s="577"/>
+      <c r="D5" s="577"/>
+      <c r="E5" s="577"/>
+      <c r="F5" s="577"/>
+      <c r="G5" s="586"/>
+      <c r="H5" s="586"/>
+      <c r="I5" s="586"/>
+      <c r="J5" s="586"/>
+      <c r="K5" s="586"/>
+      <c r="L5" s="586"/>
+      <c r="M5" s="586"/>
+      <c r="N5" s="586"/>
+      <c r="O5" s="586"/>
+      <c r="P5" s="587"/>
+      <c r="Q5" s="587"/>
+      <c r="R5" s="587"/>
+      <c r="S5" s="587"/>
+      <c r="T5" s="577"/>
+      <c r="U5" s="577"/>
+      <c r="V5" s="577"/>
+      <c r="W5" s="577"/>
+      <c r="X5" s="577"/>
+      <c r="Y5" s="577"/>
+      <c r="Z5" s="577"/>
+      <c r="AA5" s="577"/>
+      <c r="AB5" s="577"/>
+      <c r="AC5" s="577"/>
+      <c r="AD5" s="577"/>
+      <c r="AE5" s="577"/>
+      <c r="AF5" s="577"/>
+      <c r="AG5" s="577"/>
+      <c r="AH5" s="577"/>
+      <c r="AI5" s="577"/>
+      <c r="AJ5" s="577"/>
+      <c r="AK5" s="577"/>
+      <c r="AL5" s="577"/>
+      <c r="AM5" s="577"/>
+      <c r="AN5" s="577"/>
+      <c r="AO5" s="577"/>
+      <c r="AP5" s="577"/>
+      <c r="AQ5" s="577"/>
+      <c r="AR5" s="577"/>
+      <c r="AS5" s="577"/>
+      <c r="AT5" s="577"/>
+      <c r="AU5" s="577"/>
+      <c r="AV5" s="577"/>
+      <c r="AW5" s="577"/>
+      <c r="AX5" s="577"/>
+      <c r="AY5" s="577"/>
+      <c r="AZ5" s="577"/>
+      <c r="BA5" s="577"/>
+      <c r="BB5" s="577"/>
+      <c r="BC5" s="577"/>
+      <c r="BD5" s="577"/>
+      <c r="BE5" s="577"/>
+      <c r="BF5" s="577"/>
+      <c r="BG5" s="577"/>
+    </row>
+    <row r="6" ht="26" customHeight="1" spans="1:59">
+      <c r="A6" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">New UX/UI Supply Chain Financing for Suppliers</t>
+          <t xml:space="preserve">Consulta de créditos</t>
         </is>
       </c>
-      <c r="B6" s="579"/>
-      <c r="C6" s="579"/>
-      <c r="D6" s="578" t="inlineStr">
+      <c r="B6" s="577"/>
+      <c r="C6" s="577"/>
+      <c r="D6" s="577"/>
+      <c r="E6" s="577"/>
+      <c r="F6" s="577"/>
+      <c r="G6" s="586"/>
+      <c r="H6" s="586"/>
+      <c r="I6" s="586"/>
+      <c r="J6" s="586"/>
+      <c r="K6" s="586"/>
+      <c r="L6" s="586"/>
+      <c r="M6" s="586"/>
+      <c r="N6" s="586"/>
+      <c r="O6" s="586"/>
+      <c r="P6" s="587"/>
+      <c r="Q6" s="587"/>
+      <c r="R6" s="587"/>
+      <c r="S6" s="587"/>
+      <c r="T6" s="577"/>
+      <c r="U6" s="577"/>
+      <c r="V6" s="577"/>
+      <c r="W6" s="577"/>
+      <c r="X6" s="577"/>
+      <c r="Y6" s="577"/>
+      <c r="Z6" s="577"/>
+      <c r="AA6" s="577"/>
+      <c r="AB6" s="577"/>
+      <c r="AC6" s="577"/>
+      <c r="AD6" s="577"/>
+      <c r="AE6" s="577"/>
+      <c r="AF6" s="577"/>
+      <c r="AG6" s="577"/>
+      <c r="AH6" s="577"/>
+      <c r="AI6" s="577"/>
+      <c r="AJ6" s="577"/>
+      <c r="AK6" s="577"/>
+      <c r="AL6" s="577"/>
+      <c r="AM6" s="577"/>
+      <c r="AN6" s="577"/>
+      <c r="AO6" s="577"/>
+      <c r="AP6" s="577"/>
+      <c r="AQ6" s="577"/>
+      <c r="AR6" s="577"/>
+      <c r="AS6" s="577"/>
+      <c r="AT6" s="577"/>
+      <c r="AU6" s="577"/>
+      <c r="AV6" s="577"/>
+      <c r="AW6" s="577"/>
+      <c r="AX6" s="577"/>
+      <c r="AY6" s="577"/>
+      <c r="AZ6" s="577"/>
+      <c r="BA6" s="577"/>
+      <c r="BB6" s="577"/>
+      <c r="BC6" s="577"/>
+      <c r="BD6" s="577"/>
+      <c r="BE6" s="577"/>
+      <c r="BF6" s="577"/>
+      <c r="BG6" s="577"/>
+    </row>
+    <row r="7" ht="26" customHeight="1" spans="1:59">
+      <c r="A7" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nova jornada digital de antecipação de Avisos de Pagamento por Fornecedores (Clientes e Não Clientes)</t>
+          <t xml:space="preserve">CDT - Valor Alternativo</t>
         </is>
       </c>
-      <c r="E6" s="579" t="inlineStr">
+      <c r="B7" s="577"/>
+      <c r="C7" s="577"/>
+      <c r="D7" s="577"/>
+      <c r="E7" s="577"/>
+      <c r="F7" s="577"/>
+      <c r="G7" s="586"/>
+      <c r="H7" s="586"/>
+      <c r="I7" s="586"/>
+      <c r="J7" s="586"/>
+      <c r="K7" s="586"/>
+      <c r="L7" s="586"/>
+      <c r="M7" s="586"/>
+      <c r="N7" s="586"/>
+      <c r="O7" s="586"/>
+      <c r="P7" s="586"/>
+      <c r="Q7" s="586"/>
+      <c r="R7" s="586"/>
+      <c r="S7" s="586"/>
+      <c r="T7" s="577"/>
+      <c r="U7" s="577"/>
+      <c r="V7" s="577"/>
+      <c r="W7" s="577"/>
+      <c r="X7" s="577"/>
+      <c r="Y7" s="577"/>
+      <c r="Z7" s="577"/>
+      <c r="AA7" s="577"/>
+      <c r="AB7" s="577"/>
+      <c r="AC7" s="577"/>
+      <c r="AD7" s="577"/>
+      <c r="AE7" s="577"/>
+      <c r="AF7" s="577"/>
+      <c r="AG7" s="577"/>
+      <c r="AH7" s="577"/>
+      <c r="AI7" s="577"/>
+      <c r="AJ7" s="577"/>
+      <c r="AK7" s="577"/>
+      <c r="AL7" s="577"/>
+      <c r="AM7" s="577"/>
+      <c r="AN7" s="577"/>
+      <c r="AO7" s="577"/>
+      <c r="AP7" s="577"/>
+      <c r="AQ7" s="577"/>
+      <c r="AR7" s="577"/>
+      <c r="AS7" s="577"/>
+      <c r="AT7" s="577"/>
+      <c r="AU7" s="577"/>
+      <c r="AV7" s="577"/>
+      <c r="AW7" s="577"/>
+      <c r="AX7" s="577"/>
+      <c r="AY7" s="577"/>
+      <c r="AZ7" s="577"/>
+      <c r="BA7" s="577"/>
+      <c r="BB7" s="577"/>
+      <c r="BC7" s="577"/>
+      <c r="BD7" s="577"/>
+      <c r="BE7" s="577"/>
+      <c r="BF7" s="577"/>
+      <c r="BG7" s="577"/>
+    </row>
+    <row r="8" ht="26" customHeight="1" spans="1:59">
+      <c r="A8" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-03-2026</t>
+          <t xml:space="preserve">Recenseamento não clientes</t>
         </is>
       </c>
-      <c r="F6" s="578" t="inlineStr">
+      <c r="B8" s="577"/>
+      <c r="C8" s="577"/>
+      <c r="D8" s="577"/>
+      <c r="E8" s="577"/>
+      <c r="F8" s="577"/>
+      <c r="G8" s="585"/>
+      <c r="H8" s="585"/>
+      <c r="I8" s="585"/>
+      <c r="J8" s="585"/>
+      <c r="K8" s="585"/>
+      <c r="L8" s="586"/>
+      <c r="M8" s="586"/>
+      <c r="N8" s="586"/>
+      <c r="O8" s="586"/>
+      <c r="P8" s="586"/>
+      <c r="Q8" s="586"/>
+      <c r="R8" s="586"/>
+      <c r="S8" s="586"/>
+      <c r="T8" s="584"/>
+      <c r="U8" s="584"/>
+      <c r="V8" s="584"/>
+      <c r="W8" s="584"/>
+      <c r="X8" s="584"/>
+      <c r="Y8" s="577"/>
+      <c r="Z8" s="577"/>
+      <c r="AA8" s="577"/>
+      <c r="AB8" s="577"/>
+      <c r="AC8" s="577"/>
+      <c r="AD8" s="577"/>
+      <c r="AE8" s="577"/>
+      <c r="AF8" s="577"/>
+      <c r="AG8" s="577"/>
+      <c r="AH8" s="577"/>
+      <c r="AI8" s="577"/>
+      <c r="AJ8" s="577"/>
+      <c r="AK8" s="577"/>
+      <c r="AL8" s="577"/>
+      <c r="AM8" s="577"/>
+      <c r="AN8" s="577"/>
+      <c r="AO8" s="577"/>
+      <c r="AP8" s="577"/>
+      <c r="AQ8" s="577"/>
+      <c r="AR8" s="577"/>
+      <c r="AS8" s="577"/>
+      <c r="AT8" s="577"/>
+      <c r="AU8" s="577"/>
+      <c r="AV8" s="577"/>
+      <c r="AW8" s="577"/>
+      <c r="AX8" s="577"/>
+      <c r="AY8" s="577"/>
+      <c r="AZ8" s="577"/>
+      <c r="BA8" s="577"/>
+      <c r="BB8" s="577"/>
+      <c r="BC8" s="577"/>
+      <c r="BD8" s="577"/>
+      <c r="BE8" s="577"/>
+      <c r="BF8" s="577"/>
+      <c r="BG8" s="577"/>
+    </row>
+    <row r="9" ht="26" customHeight="1" spans="1:59">
+      <c r="A9" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Certificação complexa pode impactar na data de passagem a produção e abertura a clientes (piloto)</t>
+          <t xml:space="preserve">Transformação dos IML´s para 5512</t>
         </is>
       </c>
-      <c r="G6" s="591"/>
-      <c r="H6" s="591"/>
-      <c r="I6" s="591"/>
-      <c r="J6" s="591"/>
-      <c r="K6" s="591"/>
-      <c r="L6" s="591"/>
-      <c r="M6" s="591"/>
-      <c r="N6" s="591"/>
-      <c r="O6" s="591"/>
-      <c r="P6" s="591"/>
-      <c r="Q6" s="591"/>
-      <c r="R6" s="591"/>
-      <c r="S6" s="590"/>
-      <c r="T6" s="591"/>
-      <c r="U6" s="591"/>
-      <c r="V6" s="591"/>
-      <c r="W6" s="591"/>
-      <c r="X6" s="591"/>
-      <c r="Y6" s="591"/>
-      <c r="Z6" s="591"/>
-      <c r="AA6" s="591"/>
-      <c r="AB6" s="591"/>
-      <c r="AC6" s="591"/>
-      <c r="AD6" s="591"/>
-      <c r="AE6" s="591"/>
-      <c r="AF6" s="591"/>
-      <c r="AG6" s="591"/>
-      <c r="AH6" s="591"/>
-      <c r="AI6" s="591"/>
-      <c r="AJ6" s="591"/>
-      <c r="AK6" s="591"/>
-      <c r="AL6" s="591"/>
-      <c r="AM6" s="591"/>
-      <c r="AN6" s="591"/>
-      <c r="AO6" s="591"/>
-      <c r="AP6" s="591"/>
-      <c r="AQ6" s="591"/>
-      <c r="AR6" s="591"/>
-      <c r="AS6" s="591"/>
-      <c r="AT6" s="591"/>
-      <c r="AU6" s="591"/>
-      <c r="AV6" s="591"/>
-      <c r="AW6" s="591"/>
-      <c r="AX6" s="591"/>
-      <c r="AY6" s="591"/>
-      <c r="AZ6" s="591"/>
-      <c r="BA6" s="591"/>
-      <c r="BB6" s="591"/>
-      <c r="BC6" s="591"/>
-      <c r="BD6" s="591"/>
-      <c r="BE6" s="591"/>
-      <c r="BF6" s="591"/>
-      <c r="BG6" s="591"/>
-    </row>
-    <row r="7" ht="70" customHeight="1" spans="1:59">
-      <c r="A7" s="577" t="inlineStr">
+      <c r="B9" s="577"/>
+      <c r="C9" s="577"/>
+      <c r="D9" s="577"/>
+      <c r="E9" s="577"/>
+      <c r="F9" s="577"/>
+      <c r="G9" s="582"/>
+      <c r="H9" s="582"/>
+      <c r="I9" s="582"/>
+      <c r="J9" s="582"/>
+      <c r="K9" s="582"/>
+      <c r="L9" s="585"/>
+      <c r="M9" s="585"/>
+      <c r="N9" s="585"/>
+      <c r="O9" s="585"/>
+      <c r="P9" s="585"/>
+      <c r="Q9" s="585"/>
+      <c r="R9" s="585"/>
+      <c r="S9" s="585"/>
+      <c r="T9" s="587"/>
+      <c r="U9" s="587"/>
+      <c r="V9" s="587"/>
+      <c r="W9" s="587"/>
+      <c r="X9" s="587"/>
+      <c r="Y9" s="577"/>
+      <c r="Z9" s="577"/>
+      <c r="AA9" s="577"/>
+      <c r="AB9" s="577"/>
+      <c r="AC9" s="577"/>
+      <c r="AD9" s="577"/>
+      <c r="AE9" s="577"/>
+      <c r="AF9" s="577"/>
+      <c r="AG9" s="577"/>
+      <c r="AH9" s="577"/>
+      <c r="AI9" s="577"/>
+      <c r="AJ9" s="577"/>
+      <c r="AK9" s="577"/>
+      <c r="AL9" s="577"/>
+      <c r="AM9" s="577"/>
+      <c r="AN9" s="577"/>
+      <c r="AO9" s="577"/>
+      <c r="AP9" s="577"/>
+      <c r="AQ9" s="577"/>
+      <c r="AR9" s="577"/>
+      <c r="AS9" s="577"/>
+      <c r="AT9" s="577"/>
+      <c r="AU9" s="577"/>
+      <c r="AV9" s="577"/>
+      <c r="AW9" s="577"/>
+      <c r="AX9" s="577"/>
+      <c r="AY9" s="577"/>
+      <c r="AZ9" s="577"/>
+      <c r="BA9" s="577"/>
+      <c r="BB9" s="577"/>
+      <c r="BC9" s="577"/>
+      <c r="BD9" s="577"/>
+      <c r="BE9" s="577"/>
+      <c r="BF9" s="577"/>
+      <c r="BG9" s="577"/>
+    </row>
+    <row r="10" ht="26" customHeight="1" spans="1:59">
+      <c r="A10" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">API integration on ERP – Confirming &amp; Factoring files</t>
+          <t xml:space="preserve">Modo de envio Ime|Urgente</t>
         </is>
       </c>
-      <c r="B7" s="579"/>
-      <c r="C7" s="579"/>
-      <c r="D7" s="578" t="inlineStr">
+      <c r="B10" s="577"/>
+      <c r="C10" s="577"/>
+      <c r="D10" s="577"/>
+      <c r="E10" s="577"/>
+      <c r="F10" s="577"/>
+      <c r="G10" s="582"/>
+      <c r="H10" s="582"/>
+      <c r="I10" s="582"/>
+      <c r="J10" s="582"/>
+      <c r="K10" s="582"/>
+      <c r="L10" s="585"/>
+      <c r="M10" s="585"/>
+      <c r="N10" s="585"/>
+      <c r="O10" s="585"/>
+      <c r="P10" s="585"/>
+      <c r="Q10" s="585"/>
+      <c r="R10" s="585"/>
+      <c r="S10" s="585"/>
+      <c r="T10" s="587"/>
+      <c r="U10" s="587"/>
+      <c r="V10" s="587"/>
+      <c r="W10" s="587"/>
+      <c r="X10" s="587"/>
+      <c r="Y10" s="577"/>
+      <c r="Z10" s="577"/>
+      <c r="AA10" s="577"/>
+      <c r="AB10" s="577"/>
+      <c r="AC10" s="577"/>
+      <c r="AD10" s="577"/>
+      <c r="AE10" s="577"/>
+      <c r="AF10" s="577"/>
+      <c r="AG10" s="577"/>
+      <c r="AH10" s="577"/>
+      <c r="AI10" s="577"/>
+      <c r="AJ10" s="577"/>
+      <c r="AK10" s="577"/>
+      <c r="AL10" s="577"/>
+      <c r="AM10" s="577"/>
+      <c r="AN10" s="577"/>
+      <c r="AO10" s="577"/>
+      <c r="AP10" s="577"/>
+      <c r="AQ10" s="577"/>
+      <c r="AR10" s="577"/>
+      <c r="AS10" s="577"/>
+      <c r="AT10" s="577"/>
+      <c r="AU10" s="577"/>
+      <c r="AV10" s="577"/>
+      <c r="AW10" s="577"/>
+      <c r="AX10" s="577"/>
+      <c r="AY10" s="577"/>
+      <c r="AZ10" s="577"/>
+      <c r="BA10" s="577"/>
+      <c r="BB10" s="577"/>
+      <c r="BC10" s="577"/>
+      <c r="BD10" s="577"/>
+      <c r="BE10" s="577"/>
+      <c r="BF10" s="577"/>
+      <c r="BG10" s="577"/>
+    </row>
+    <row r="11" ht="26" customHeight="1" spans="1:59">
+      <c r="A11" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ficheiros de retorno com informação de Factoring e Confirming (eventos kafka)</t>
+          <t xml:space="preserve">Cliente Aplauso</t>
         </is>
       </c>
-      <c r="E7" s="579" t="inlineStr">
+      <c r="B11" s="577"/>
+      <c r="C11" s="577"/>
+      <c r="D11" s="577"/>
+      <c r="E11" s="577"/>
+      <c r="F11" s="577"/>
+      <c r="G11" s="582"/>
+      <c r="H11" s="582"/>
+      <c r="I11" s="582"/>
+      <c r="J11" s="582"/>
+      <c r="K11" s="582"/>
+      <c r="L11" s="585"/>
+      <c r="M11" s="585"/>
+      <c r="N11" s="585"/>
+      <c r="O11" s="585"/>
+      <c r="P11" s="585"/>
+      <c r="Q11" s="585"/>
+      <c r="R11" s="585"/>
+      <c r="S11" s="585"/>
+      <c r="T11" s="585"/>
+      <c r="U11" s="585"/>
+      <c r="V11" s="585"/>
+      <c r="W11" s="585"/>
+      <c r="X11" s="585"/>
+      <c r="Y11" s="585"/>
+      <c r="Z11" s="585"/>
+      <c r="AA11" s="585"/>
+      <c r="AB11" s="585"/>
+      <c r="AC11" s="585"/>
+      <c r="AD11" s="585"/>
+      <c r="AE11" s="585"/>
+      <c r="AF11" s="585"/>
+      <c r="AG11" s="577"/>
+      <c r="AH11" s="577"/>
+      <c r="AI11" s="577"/>
+      <c r="AJ11" s="577"/>
+      <c r="AK11" s="577"/>
+      <c r="AL11" s="577"/>
+      <c r="AM11" s="577"/>
+      <c r="AN11" s="577"/>
+      <c r="AO11" s="577"/>
+      <c r="AP11" s="577"/>
+      <c r="AQ11" s="577"/>
+      <c r="AR11" s="577"/>
+      <c r="AS11" s="577"/>
+      <c r="AT11" s="577"/>
+      <c r="AU11" s="577"/>
+      <c r="AV11" s="577"/>
+      <c r="AW11" s="577"/>
+      <c r="AX11" s="577"/>
+      <c r="AY11" s="577"/>
+      <c r="AZ11" s="577"/>
+      <c r="BA11" s="577"/>
+      <c r="BB11" s="577"/>
+      <c r="BC11" s="577"/>
+      <c r="BD11" s="577"/>
+      <c r="BE11" s="577"/>
+      <c r="BF11" s="577"/>
+      <c r="BG11" s="577"/>
+    </row>
+    <row r="12" ht="26" customHeight="1" spans="1:59">
+      <c r="A12" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abr 26</t>
+          <t xml:space="preserve">Encerramento de conta digital</t>
         </is>
       </c>
-      <c r="F7" s="578" t="inlineStr">
+      <c r="B12" s="577"/>
+      <c r="C12" s="577"/>
+      <c r="D12" s="577"/>
+      <c r="E12" s="577"/>
+      <c r="F12" s="577"/>
+      <c r="G12" s="585"/>
+      <c r="H12" s="585"/>
+      <c r="I12" s="585"/>
+      <c r="J12" s="585"/>
+      <c r="K12" s="585"/>
+      <c r="L12" s="585"/>
+      <c r="M12" s="585"/>
+      <c r="N12" s="585"/>
+      <c r="O12" s="585"/>
+      <c r="P12" s="585"/>
+      <c r="Q12" s="585"/>
+      <c r="R12" s="585"/>
+      <c r="S12" s="585"/>
+      <c r="T12" s="587"/>
+      <c r="U12" s="587"/>
+      <c r="V12" s="587"/>
+      <c r="W12" s="587"/>
+      <c r="X12" s="587"/>
+      <c r="Y12" s="577"/>
+      <c r="Z12" s="577"/>
+      <c r="AA12" s="577"/>
+      <c r="AB12" s="577"/>
+      <c r="AC12" s="577"/>
+      <c r="AD12" s="577"/>
+      <c r="AE12" s="577"/>
+      <c r="AF12" s="577"/>
+      <c r="AG12" s="577"/>
+      <c r="AH12" s="577"/>
+      <c r="AI12" s="577"/>
+      <c r="AJ12" s="577"/>
+      <c r="AK12" s="577"/>
+      <c r="AL12" s="577"/>
+      <c r="AM12" s="577"/>
+      <c r="AN12" s="577"/>
+      <c r="AO12" s="577"/>
+      <c r="AP12" s="577"/>
+      <c r="AQ12" s="577"/>
+      <c r="AR12" s="577"/>
+      <c r="AS12" s="577"/>
+      <c r="AT12" s="577"/>
+      <c r="AU12" s="577"/>
+      <c r="AV12" s="577"/>
+      <c r="AW12" s="577"/>
+      <c r="AX12" s="577"/>
+      <c r="AY12" s="577"/>
+      <c r="AZ12" s="577"/>
+      <c r="BA12" s="577"/>
+      <c r="BB12" s="577"/>
+      <c r="BC12" s="577"/>
+      <c r="BD12" s="577"/>
+      <c r="BE12" s="577"/>
+      <c r="BF12" s="577"/>
+      <c r="BG12" s="577"/>
+    </row>
+    <row r="13" ht="26" customHeight="1" spans="1:59">
+      <c r="A13" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Novo serviço disponível para todos os canais</t>
+          <t xml:space="preserve">Pedido de cartão de crédito (email)</t>
         </is>
       </c>
-      <c r="G7" s="591"/>
-      <c r="H7" s="591"/>
-      <c r="I7" s="591"/>
-      <c r="J7" s="591"/>
-      <c r="K7" s="591"/>
-      <c r="L7" s="591"/>
-      <c r="M7" s="591"/>
-      <c r="N7" s="591"/>
-      <c r="O7" s="591"/>
-      <c r="P7" s="591"/>
-      <c r="Q7" s="591"/>
-      <c r="R7" s="591"/>
-      <c r="S7" s="591"/>
-      <c r="T7" s="590"/>
-      <c r="U7" s="591"/>
-      <c r="V7" s="591"/>
-      <c r="W7" s="591"/>
-      <c r="X7" s="591"/>
-      <c r="Y7" s="591"/>
-      <c r="Z7" s="591"/>
-      <c r="AA7" s="591"/>
-      <c r="AB7" s="591"/>
-      <c r="AC7" s="591"/>
-      <c r="AD7" s="591"/>
-      <c r="AE7" s="591"/>
-      <c r="AF7" s="591"/>
-      <c r="AG7" s="591"/>
-      <c r="AH7" s="591"/>
-      <c r="AI7" s="591"/>
-      <c r="AJ7" s="591"/>
-      <c r="AK7" s="591"/>
-      <c r="AL7" s="591"/>
-      <c r="AM7" s="591"/>
-      <c r="AN7" s="591"/>
-      <c r="AO7" s="591"/>
-      <c r="AP7" s="591"/>
-      <c r="AQ7" s="591"/>
-      <c r="AR7" s="591"/>
-      <c r="AS7" s="591"/>
-      <c r="AT7" s="591"/>
-      <c r="AU7" s="591"/>
-      <c r="AV7" s="591"/>
-      <c r="AW7" s="591"/>
-      <c r="AX7" s="591"/>
-      <c r="AY7" s="591"/>
-      <c r="AZ7" s="591"/>
-      <c r="BA7" s="591"/>
-      <c r="BB7" s="591"/>
-      <c r="BC7" s="591"/>
-      <c r="BD7" s="591"/>
-      <c r="BE7" s="591"/>
-      <c r="BF7" s="591"/>
-      <c r="BG7" s="591"/>
-    </row>
-    <row r="8" ht="70" customHeight="1" spans="1:59">
-      <c r="A8" s="577" t="inlineStr">
+      <c r="B13" s="577"/>
+      <c r="C13" s="577"/>
+      <c r="D13" s="577"/>
+      <c r="E13" s="577"/>
+      <c r="F13" s="577"/>
+      <c r="G13" s="585"/>
+      <c r="H13" s="585"/>
+      <c r="I13" s="585"/>
+      <c r="J13" s="585"/>
+      <c r="K13" s="585"/>
+      <c r="L13" s="585"/>
+      <c r="M13" s="585"/>
+      <c r="N13" s="585"/>
+      <c r="O13" s="585"/>
+      <c r="P13" s="585"/>
+      <c r="Q13" s="585"/>
+      <c r="R13" s="585"/>
+      <c r="S13" s="585"/>
+      <c r="T13" s="585"/>
+      <c r="U13" s="585"/>
+      <c r="V13" s="585"/>
+      <c r="W13" s="585"/>
+      <c r="X13" s="585"/>
+      <c r="Y13" s="577"/>
+      <c r="Z13" s="577"/>
+      <c r="AA13" s="577"/>
+      <c r="AB13" s="577"/>
+      <c r="AC13" s="577"/>
+      <c r="AD13" s="577"/>
+      <c r="AE13" s="577"/>
+      <c r="AF13" s="577"/>
+      <c r="AG13" s="577"/>
+      <c r="AH13" s="577"/>
+      <c r="AI13" s="577"/>
+      <c r="AJ13" s="577"/>
+      <c r="AK13" s="577"/>
+      <c r="AL13" s="577"/>
+      <c r="AM13" s="577"/>
+      <c r="AN13" s="577"/>
+      <c r="AO13" s="577"/>
+      <c r="AP13" s="577"/>
+      <c r="AQ13" s="577"/>
+      <c r="AR13" s="577"/>
+      <c r="AS13" s="577"/>
+      <c r="AT13" s="577"/>
+      <c r="AU13" s="577"/>
+      <c r="AV13" s="577"/>
+      <c r="AW13" s="577"/>
+      <c r="AX13" s="577"/>
+      <c r="AY13" s="577"/>
+      <c r="AZ13" s="577"/>
+      <c r="BA13" s="577"/>
+      <c r="BB13" s="577"/>
+      <c r="BC13" s="577"/>
+      <c r="BD13" s="577"/>
+      <c r="BE13" s="577"/>
+      <c r="BF13" s="577"/>
+      <c r="BG13" s="577"/>
+    </row>
+    <row r="14" ht="26" customHeight="1" spans="1:59">
+      <c r="A14" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">New UI/UX Credit Details</t>
+          <t xml:space="preserve">Cartões - A NOSSA OFERTA</t>
         </is>
       </c>
-      <c r="B8" s="579"/>
-      <c r="C8" s="579"/>
-      <c r="D8" s="578" t="inlineStr">
+      <c r="B14" s="577"/>
+      <c r="C14" s="577"/>
+      <c r="D14" s="577"/>
+      <c r="E14" s="577"/>
+      <c r="F14" s="577"/>
+      <c r="G14" s="585"/>
+      <c r="H14" s="585"/>
+      <c r="I14" s="585"/>
+      <c r="J14" s="585"/>
+      <c r="K14" s="585"/>
+      <c r="L14" s="585"/>
+      <c r="M14" s="585"/>
+      <c r="N14" s="585"/>
+      <c r="O14" s="585"/>
+      <c r="P14" s="585"/>
+      <c r="Q14" s="585"/>
+      <c r="R14" s="585"/>
+      <c r="S14" s="585"/>
+      <c r="T14" s="585"/>
+      <c r="U14" s="585"/>
+      <c r="V14" s="585"/>
+      <c r="W14" s="585"/>
+      <c r="X14" s="585"/>
+      <c r="Y14" s="577"/>
+      <c r="Z14" s="577"/>
+      <c r="AA14" s="577"/>
+      <c r="AB14" s="577"/>
+      <c r="AC14" s="577"/>
+      <c r="AD14" s="577"/>
+      <c r="AE14" s="577"/>
+      <c r="AF14" s="577"/>
+      <c r="AG14" s="577"/>
+      <c r="AH14" s="577"/>
+      <c r="AI14" s="577"/>
+      <c r="AJ14" s="577"/>
+      <c r="AK14" s="577"/>
+      <c r="AL14" s="577"/>
+      <c r="AM14" s="577"/>
+      <c r="AN14" s="577"/>
+      <c r="AO14" s="577"/>
+      <c r="AP14" s="577"/>
+      <c r="AQ14" s="577"/>
+      <c r="AR14" s="577"/>
+      <c r="AS14" s="577"/>
+      <c r="AT14" s="577"/>
+      <c r="AU14" s="577"/>
+      <c r="AV14" s="577"/>
+      <c r="AW14" s="577"/>
+      <c r="AX14" s="577"/>
+      <c r="AY14" s="577"/>
+      <c r="AZ14" s="577"/>
+      <c r="BA14" s="577"/>
+      <c r="BB14" s="577"/>
+      <c r="BC14" s="577"/>
+      <c r="BD14" s="577"/>
+      <c r="BE14" s="577"/>
+      <c r="BF14" s="577"/>
+      <c r="BG14" s="577"/>
+    </row>
+    <row r="15" ht="26" customHeight="1" spans="1:59">
+      <c r="A15" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nova área de consulta de produtos de crédito</t>
+          <t xml:space="preserve">SAF-T - Upload de ficheiro</t>
         </is>
       </c>
-      <c r="E8" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26-03-2026</t>
-        </is>
-      </c>
-      <c r="F8" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Certificação complexa com eventual impactar na abertura a clientes</t>
-        </is>
-      </c>
-      <c r="G8" s="591"/>
-      <c r="H8" s="591"/>
-      <c r="I8" s="591"/>
-      <c r="J8" s="591"/>
-      <c r="K8" s="589"/>
-      <c r="L8" s="589"/>
-      <c r="M8" s="589"/>
-      <c r="N8" s="589"/>
-      <c r="O8" s="589"/>
-      <c r="P8" s="589"/>
-      <c r="Q8" s="589"/>
-      <c r="R8" s="589"/>
-      <c r="S8" s="590"/>
-      <c r="T8" s="591"/>
-      <c r="U8" s="591"/>
-      <c r="V8" s="591"/>
-      <c r="W8" s="591"/>
-      <c r="X8" s="591"/>
-      <c r="Y8" s="591"/>
-      <c r="Z8" s="591"/>
-      <c r="AA8" s="591"/>
-      <c r="AB8" s="591"/>
-      <c r="AC8" s="591"/>
-      <c r="AD8" s="591"/>
-      <c r="AE8" s="591"/>
-      <c r="AF8" s="591"/>
-      <c r="AG8" s="591"/>
-      <c r="AH8" s="591"/>
-      <c r="AI8" s="591"/>
-      <c r="AJ8" s="591"/>
-      <c r="AK8" s="591"/>
-      <c r="AL8" s="591"/>
-      <c r="AM8" s="591"/>
-      <c r="AN8" s="591"/>
-      <c r="AO8" s="591"/>
-      <c r="AP8" s="591"/>
-      <c r="AQ8" s="591"/>
-      <c r="AR8" s="591"/>
-      <c r="AS8" s="591"/>
-      <c r="AT8" s="591"/>
-      <c r="AU8" s="591"/>
-      <c r="AV8" s="591"/>
-      <c r="AW8" s="591"/>
-      <c r="AX8" s="591"/>
-      <c r="AY8" s="591"/>
-      <c r="AZ8" s="591"/>
-      <c r="BA8" s="591"/>
-      <c r="BB8" s="591"/>
-      <c r="BC8" s="591"/>
-      <c r="BD8" s="591"/>
-      <c r="BE8" s="591"/>
-      <c r="BF8" s="591"/>
-      <c r="BG8" s="591"/>
-    </row>
-    <row r="9" ht="70" customHeight="1" spans="1:59">
-      <c r="A9" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crédito Digital Tesouraria (Phase 2)</t>
-        </is>
-      </c>
-      <c r="B9" s="579"/>
-      <c r="C9" s="579"/>
-      <c r="D9" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integração Valor Alternativo (ADS II) - Capacidade de oferta de conta proposta imediata de montante inferior</t>
-        </is>
-      </c>
-      <c r="E9" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26-03-2026</t>
-        </is>
-      </c>
-      <c r="F9" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JML020226 - Desenvolvimento em curso</t>
-        </is>
-      </c>
-      <c r="G9" s="591"/>
-      <c r="H9" s="591"/>
-      <c r="I9" s="591"/>
-      <c r="J9" s="591"/>
-      <c r="K9" s="591"/>
-      <c r="L9" s="591"/>
-      <c r="M9" s="591"/>
-      <c r="N9" s="591"/>
-      <c r="O9" s="591"/>
-      <c r="P9" s="591"/>
-      <c r="Q9" s="591"/>
-      <c r="R9" s="591"/>
-      <c r="S9" s="590"/>
-      <c r="T9" s="591"/>
-      <c r="U9" s="591"/>
-      <c r="V9" s="591"/>
-      <c r="W9" s="591"/>
-      <c r="X9" s="591"/>
-      <c r="Y9" s="591"/>
-      <c r="Z9" s="591"/>
-      <c r="AA9" s="591"/>
-      <c r="AB9" s="591"/>
-      <c r="AC9" s="591"/>
-      <c r="AD9" s="591"/>
-      <c r="AE9" s="591"/>
-      <c r="AF9" s="591"/>
-      <c r="AG9" s="591"/>
-      <c r="AH9" s="591"/>
-      <c r="AI9" s="591"/>
-      <c r="AJ9" s="591"/>
-      <c r="AK9" s="591"/>
-      <c r="AL9" s="591"/>
-      <c r="AM9" s="591"/>
-      <c r="AN9" s="591"/>
-      <c r="AO9" s="591"/>
-      <c r="AP9" s="591"/>
-      <c r="AQ9" s="591"/>
-      <c r="AR9" s="591"/>
-      <c r="AS9" s="591"/>
-      <c r="AT9" s="591"/>
-      <c r="AU9" s="591"/>
-      <c r="AV9" s="591"/>
-      <c r="AW9" s="591"/>
-      <c r="AX9" s="591"/>
-      <c r="AY9" s="591"/>
-      <c r="AZ9" s="591"/>
-      <c r="BA9" s="591"/>
-      <c r="BB9" s="591"/>
-      <c r="BC9" s="591"/>
-      <c r="BD9" s="591"/>
-      <c r="BE9" s="591"/>
-      <c r="BF9" s="591"/>
-      <c r="BG9" s="591"/>
-    </row>
-    <row r="10" ht="70" customHeight="1" spans="1:59">
-      <c r="A10" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Factoring - Digital notifications</t>
-        </is>
-      </c>
-      <c r="B10" s="579"/>
-      <c r="C10" s="579"/>
-      <c r="D10" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Processo de notificação digital de devedores de factoring (clientes)</t>
-        </is>
-      </c>
-      <c r="E10" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F10" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Falta ainda avaliação técnica das Equipas da PUCC e XFAC.
-JML020226 - US's e design concluidos</t>
-        </is>
-      </c>
-      <c r="G10" s="591"/>
-      <c r="H10" s="591"/>
-      <c r="I10" s="591"/>
-      <c r="J10" s="591"/>
-      <c r="K10" s="591"/>
-      <c r="L10" s="591"/>
-      <c r="M10" s="591"/>
-      <c r="N10" s="591"/>
-      <c r="O10" s="591"/>
-      <c r="P10" s="591"/>
-      <c r="Q10" s="591"/>
-      <c r="R10" s="591"/>
-      <c r="S10" s="591"/>
-      <c r="T10" s="591"/>
-      <c r="U10" s="591"/>
-      <c r="V10" s="591"/>
-      <c r="W10" s="591"/>
-      <c r="X10" s="591"/>
-      <c r="Y10" s="591"/>
-      <c r="Z10" s="591"/>
-      <c r="AA10" s="591"/>
-      <c r="AB10" s="591"/>
-      <c r="AC10" s="591"/>
-      <c r="AD10" s="591"/>
-      <c r="AE10" s="591"/>
-      <c r="AF10" s="591"/>
-      <c r="AG10" s="591"/>
-      <c r="AH10" s="591"/>
-      <c r="AI10" s="591"/>
-      <c r="AJ10" s="591"/>
-      <c r="AK10" s="591"/>
-      <c r="AL10" s="591"/>
-      <c r="AM10" s="591"/>
-      <c r="AN10" s="591"/>
-      <c r="AO10" s="591"/>
-      <c r="AP10" s="591"/>
-      <c r="AQ10" s="591"/>
-      <c r="AR10" s="591"/>
-      <c r="AS10" s="591"/>
-      <c r="AT10" s="591"/>
-      <c r="AU10" s="591"/>
-      <c r="AV10" s="591"/>
-      <c r="AW10" s="591"/>
-      <c r="AX10" s="591"/>
-      <c r="AY10" s="591"/>
-      <c r="AZ10" s="591"/>
-      <c r="BA10" s="591"/>
-      <c r="BB10" s="591"/>
-      <c r="BC10" s="591"/>
-      <c r="BD10" s="591"/>
-      <c r="BE10" s="591"/>
-      <c r="BF10" s="591"/>
-      <c r="BG10" s="591"/>
-    </row>
-    <row r="11" ht="70" customHeight="1" spans="1:59">
-      <c r="A11" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crédito Digital Avançar (Wave 1)</t>
-        </is>
-      </c>
-      <c r="B11" s="579"/>
-      <c r="C11" s="579"/>
-      <c r="D11" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Simulador incorporado no MSE com conexão direta ao SWOC através do Credit Experience</t>
-        </is>
-      </c>
-      <c r="E11" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F11" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Desenho da jornada digital até à entrega no Credit Experience e SWOC. Data condicionada pelas prioridades da equipa do Cred. Experience</t>
-        </is>
-      </c>
-      <c r="G11" s="591"/>
-      <c r="H11" s="591"/>
-      <c r="I11" s="591"/>
-      <c r="J11" s="591"/>
-      <c r="K11" s="591"/>
-      <c r="L11" s="591"/>
-      <c r="M11" s="591"/>
-      <c r="N11" s="591"/>
-      <c r="O11" s="591"/>
-      <c r="P11" s="591"/>
-      <c r="Q11" s="591"/>
-      <c r="R11" s="591"/>
-      <c r="S11" s="591"/>
-      <c r="T11" s="591"/>
-      <c r="U11" s="591"/>
-      <c r="V11" s="591"/>
-      <c r="W11" s="591"/>
-      <c r="X11" s="591"/>
-      <c r="Y11" s="591"/>
-      <c r="Z11" s="591"/>
-      <c r="AA11" s="591"/>
-      <c r="AB11" s="591"/>
-      <c r="AC11" s="591"/>
-      <c r="AD11" s="591"/>
-      <c r="AE11" s="591"/>
-      <c r="AF11" s="591"/>
-      <c r="AG11" s="591"/>
-      <c r="AH11" s="591"/>
-      <c r="AI11" s="591"/>
-      <c r="AJ11" s="591"/>
-      <c r="AK11" s="591"/>
-      <c r="AL11" s="591"/>
-      <c r="AM11" s="591"/>
-      <c r="AN11" s="591"/>
-      <c r="AO11" s="591"/>
-      <c r="AP11" s="589"/>
-      <c r="AQ11" s="591"/>
-      <c r="AR11" s="591"/>
-      <c r="AS11" s="591"/>
-      <c r="AT11" s="591"/>
-      <c r="AU11" s="591"/>
-      <c r="AV11" s="591"/>
-      <c r="AW11" s="591"/>
-      <c r="AX11" s="591"/>
-      <c r="AY11" s="591"/>
-      <c r="AZ11" s="591"/>
-      <c r="BA11" s="591"/>
-      <c r="BB11" s="591"/>
-      <c r="BC11" s="591"/>
-      <c r="BD11" s="591"/>
-      <c r="BE11" s="591"/>
-      <c r="BF11" s="591"/>
-      <c r="BG11" s="591"/>
-    </row>
-    <row r="12" ht="70" customHeight="1" spans="1:59">
-      <c r="A12" s="580" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New UX/UI Supply Chain Financing for Buyers</t>
-        </is>
-      </c>
-      <c r="B12" s="582"/>
-      <c r="C12" s="582"/>
-      <c r="D12" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reestruturação do Confirming para Compradores com mais e novas funcionalidades</t>
-        </is>
-      </c>
-      <c r="E12" s="582"/>
-      <c r="F12" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por iniciar diagnostico e alocação de recursos</t>
-        </is>
-      </c>
-      <c r="G12" s="582"/>
-      <c r="H12" s="582"/>
-      <c r="I12" s="582"/>
-      <c r="J12" s="582"/>
-      <c r="K12" s="582"/>
-      <c r="L12" s="582"/>
-      <c r="M12" s="582"/>
-      <c r="N12" s="582"/>
-      <c r="O12" s="582"/>
-      <c r="P12" s="582"/>
-      <c r="Q12" s="582"/>
-      <c r="R12" s="582"/>
-      <c r="S12" s="582"/>
-      <c r="T12" s="582"/>
-      <c r="U12" s="582"/>
-      <c r="V12" s="582"/>
-      <c r="W12" s="582"/>
-      <c r="X12" s="582"/>
-      <c r="Y12" s="582"/>
-      <c r="Z12" s="582"/>
-      <c r="AA12" s="582"/>
-      <c r="AB12" s="582"/>
-      <c r="AC12" s="582"/>
-      <c r="AD12" s="582"/>
-      <c r="AE12" s="582"/>
-      <c r="AF12" s="582"/>
-      <c r="AG12" s="582"/>
-      <c r="AH12" s="582"/>
-      <c r="AI12" s="582"/>
-      <c r="AJ12" s="582"/>
-      <c r="AK12" s="582"/>
-      <c r="AL12" s="582"/>
-      <c r="AM12" s="582"/>
-      <c r="AN12" s="582"/>
-      <c r="AO12" s="582"/>
-      <c r="AP12" s="582"/>
-      <c r="AQ12" s="582"/>
-      <c r="AR12" s="582"/>
-      <c r="AS12" s="582"/>
-      <c r="AT12" s="582"/>
-      <c r="AU12" s="582"/>
-      <c r="AV12" s="582"/>
-      <c r="AW12" s="582"/>
-      <c r="AX12" s="582"/>
-      <c r="AY12" s="582"/>
-      <c r="AZ12" s="582"/>
-      <c r="BA12" s="582"/>
-      <c r="BB12" s="582"/>
-      <c r="BC12" s="582"/>
-      <c r="BD12" s="582"/>
-      <c r="BE12" s="582"/>
-      <c r="BF12" s="582"/>
-      <c r="BG12" s="582"/>
-    </row>
-    <row r="13" ht="70" customHeight="1" spans="1:59">
-      <c r="A13" s="580" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trade Finance and Guarantees</t>
-        </is>
-      </c>
-      <c r="B13" s="582"/>
-      <c r="C13" s="582"/>
-      <c r="D13" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reestruturação da area com mais e melhores funcionalidades com destaque  para a revisão do processo documental</t>
-        </is>
-      </c>
-      <c r="E13" s="582"/>
-      <c r="F13" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por iniciar diagnostico e alocação de recursos</t>
-        </is>
-      </c>
-      <c r="G13" s="582"/>
-      <c r="H13" s="582"/>
-      <c r="I13" s="582"/>
-      <c r="J13" s="582"/>
-      <c r="K13" s="582"/>
-      <c r="L13" s="582"/>
-      <c r="M13" s="582"/>
-      <c r="N13" s="582"/>
-      <c r="O13" s="582"/>
-      <c r="P13" s="582"/>
-      <c r="Q13" s="582"/>
-      <c r="R13" s="582"/>
-      <c r="S13" s="582"/>
-      <c r="T13" s="582"/>
-      <c r="U13" s="582"/>
-      <c r="V13" s="582"/>
-      <c r="W13" s="582"/>
-      <c r="X13" s="582"/>
-      <c r="Y13" s="582"/>
-      <c r="Z13" s="582"/>
-      <c r="AA13" s="582"/>
-      <c r="AB13" s="582"/>
-      <c r="AC13" s="582"/>
-      <c r="AD13" s="582"/>
-      <c r="AE13" s="582"/>
-      <c r="AF13" s="582"/>
-      <c r="AG13" s="582"/>
-      <c r="AH13" s="582"/>
-      <c r="AI13" s="582"/>
-      <c r="AJ13" s="582"/>
-      <c r="AK13" s="582"/>
-      <c r="AL13" s="582"/>
-      <c r="AM13" s="582"/>
-      <c r="AN13" s="582"/>
-      <c r="AO13" s="582"/>
-      <c r="AP13" s="582"/>
-      <c r="AQ13" s="582"/>
-      <c r="AR13" s="582"/>
-      <c r="AS13" s="582"/>
-      <c r="AT13" s="582"/>
-      <c r="AU13" s="582"/>
-      <c r="AV13" s="582"/>
-      <c r="AW13" s="582"/>
-      <c r="AX13" s="582"/>
-      <c r="AY13" s="582"/>
-      <c r="AZ13" s="582"/>
-      <c r="BA13" s="582"/>
-      <c r="BB13" s="582"/>
-      <c r="BC13" s="582"/>
-      <c r="BD13" s="582"/>
-      <c r="BE13" s="582"/>
-      <c r="BF13" s="582"/>
-      <c r="BG13" s="582"/>
-    </row>
-    <row r="14" ht="70" customHeight="1" spans="1:59">
-      <c r="A14" s="580" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crédito Digital Avançar (Wave 2)</t>
-        </is>
-      </c>
-      <c r="B14" s="582"/>
-      <c r="C14" s="582"/>
-      <c r="D14" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integração do modelo de decisão automática até 15K/25k</t>
-        </is>
-      </c>
-      <c r="E14" s="582"/>
-      <c r="F14" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A 2ª fase arranca após a entrega da 1ª. Estimamos 2/3 meses para desenvolvimento e passagem a prod.. Pressupõe alteração da peça contratual</t>
-        </is>
-      </c>
-      <c r="G14" s="582"/>
-      <c r="H14" s="582"/>
-      <c r="I14" s="582"/>
-      <c r="J14" s="582"/>
-      <c r="K14" s="582"/>
-      <c r="L14" s="582"/>
-      <c r="M14" s="582"/>
-      <c r="N14" s="582"/>
-      <c r="O14" s="582"/>
-      <c r="P14" s="582"/>
-      <c r="Q14" s="582"/>
-      <c r="R14" s="582"/>
-      <c r="S14" s="582"/>
-      <c r="T14" s="582"/>
-      <c r="U14" s="582"/>
-      <c r="V14" s="582"/>
-      <c r="W14" s="582"/>
-      <c r="X14" s="582"/>
-      <c r="Y14" s="582"/>
-      <c r="Z14" s="582"/>
-      <c r="AA14" s="582"/>
-      <c r="AB14" s="582"/>
-      <c r="AC14" s="582"/>
-      <c r="AD14" s="582"/>
-      <c r="AE14" s="582"/>
-      <c r="AF14" s="582"/>
-      <c r="AG14" s="582"/>
-      <c r="AH14" s="582"/>
-      <c r="AI14" s="582"/>
-      <c r="AJ14" s="582"/>
-      <c r="AK14" s="582"/>
-      <c r="AL14" s="582"/>
-      <c r="AM14" s="582"/>
-      <c r="AN14" s="582"/>
-      <c r="AO14" s="582"/>
-      <c r="AP14" s="582"/>
-      <c r="AQ14" s="582"/>
-      <c r="AR14" s="582"/>
-      <c r="AS14" s="582"/>
-      <c r="AT14" s="582"/>
-      <c r="AU14" s="582"/>
-      <c r="AV14" s="582"/>
-      <c r="AW14" s="582"/>
-      <c r="AX14" s="582"/>
-      <c r="AY14" s="582"/>
-      <c r="AZ14" s="582"/>
-      <c r="BA14" s="582"/>
-      <c r="BB14" s="582"/>
-      <c r="BC14" s="582"/>
-      <c r="BD14" s="582"/>
-      <c r="BE14" s="582"/>
-      <c r="BF14" s="582"/>
-      <c r="BG14" s="582"/>
-    </row>
-    <row r="15" ht="70" customHeight="1" spans="1:59">
-      <c r="A15" s="580" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crédito Digital Avançar (Wave 3)</t>
-        </is>
-      </c>
-      <c r="B15" s="582"/>
-      <c r="C15" s="582"/>
-      <c r="D15" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% digital, mas permitindo a omnicanalidade e status das operações para consulta no MSE</t>
-        </is>
-      </c>
-      <c r="E15" s="582"/>
-      <c r="F15" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fase final que prevê uma jornada digital E2E com exceção da assinatura da livrança</t>
-        </is>
-      </c>
+      <c r="B15" s="577"/>
+      <c r="C15" s="577"/>
+      <c r="D15" s="577"/>
+      <c r="E15" s="577"/>
+      <c r="F15" s="577"/>
       <c r="G15" s="582"/>
       <c r="H15" s="582"/>
       <c r="I15" s="582"/>
@@ -17614,2776 +17504,1295 @@
       <c r="M15" s="582"/>
       <c r="N15" s="582"/>
       <c r="O15" s="582"/>
-      <c r="P15" s="582"/>
-      <c r="Q15" s="582"/>
-      <c r="R15" s="582"/>
-      <c r="S15" s="582"/>
-      <c r="T15" s="582"/>
-      <c r="U15" s="582"/>
-      <c r="V15" s="582"/>
-      <c r="W15" s="582"/>
-      <c r="X15" s="582"/>
-      <c r="Y15" s="582"/>
-      <c r="Z15" s="582"/>
-      <c r="AA15" s="582"/>
-      <c r="AB15" s="582"/>
-      <c r="AC15" s="582"/>
-      <c r="AD15" s="582"/>
-      <c r="AE15" s="582"/>
-      <c r="AF15" s="582"/>
-      <c r="AG15" s="582"/>
-      <c r="AH15" s="582"/>
-      <c r="AI15" s="582"/>
-      <c r="AJ15" s="582"/>
-      <c r="AK15" s="582"/>
-      <c r="AL15" s="582"/>
-      <c r="AM15" s="582"/>
-      <c r="AN15" s="582"/>
-      <c r="AO15" s="582"/>
-      <c r="AP15" s="582"/>
-      <c r="AQ15" s="582"/>
-      <c r="AR15" s="582"/>
-      <c r="AS15" s="582"/>
-      <c r="AT15" s="582"/>
-      <c r="AU15" s="582"/>
-      <c r="AV15" s="582"/>
-      <c r="AW15" s="582"/>
-      <c r="AX15" s="582"/>
-      <c r="AY15" s="582"/>
-      <c r="AZ15" s="582"/>
-      <c r="BA15" s="582"/>
-      <c r="BB15" s="582"/>
-      <c r="BC15" s="582"/>
-      <c r="BD15" s="582"/>
-      <c r="BE15" s="582"/>
-      <c r="BF15" s="582"/>
-      <c r="BG15" s="582"/>
-    </row>
-    <row r="16" ht="70" customHeight="1" spans="1:59">
-      <c r="A16" s="580" t="inlineStr">
+      <c r="P15" s="585"/>
+      <c r="Q15" s="585"/>
+      <c r="R15" s="585"/>
+      <c r="S15" s="585"/>
+      <c r="T15" s="586"/>
+      <c r="U15" s="586"/>
+      <c r="V15" s="586"/>
+      <c r="W15" s="586"/>
+      <c r="X15" s="586"/>
+      <c r="Y15" s="577"/>
+      <c r="Z15" s="577"/>
+      <c r="AA15" s="577"/>
+      <c r="AB15" s="577"/>
+      <c r="AC15" s="577"/>
+      <c r="AD15" s="577"/>
+      <c r="AE15" s="577"/>
+      <c r="AF15" s="577"/>
+      <c r="AG15" s="577"/>
+      <c r="AH15" s="577"/>
+      <c r="AI15" s="577"/>
+      <c r="AJ15" s="577"/>
+      <c r="AK15" s="577"/>
+      <c r="AL15" s="577"/>
+      <c r="AM15" s="577"/>
+      <c r="AN15" s="577"/>
+      <c r="AO15" s="577"/>
+      <c r="AP15" s="577"/>
+      <c r="AQ15" s="577"/>
+      <c r="AR15" s="577"/>
+      <c r="AS15" s="577"/>
+      <c r="AT15" s="577"/>
+      <c r="AU15" s="577"/>
+      <c r="AV15" s="577"/>
+      <c r="AW15" s="577"/>
+      <c r="AX15" s="577"/>
+      <c r="AY15" s="577"/>
+      <c r="AZ15" s="577"/>
+      <c r="BA15" s="577"/>
+      <c r="BB15" s="577"/>
+      <c r="BC15" s="577"/>
+      <c r="BD15" s="577"/>
+      <c r="BE15" s="577"/>
+      <c r="BF15" s="577"/>
+      <c r="BG15" s="577"/>
+    </row>
+    <row r="16" ht="26" customHeight="1" spans="1:59">
+      <c r="A16" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factoring Revamp</t>
+          <t xml:space="preserve">Agenda 2.0</t>
         </is>
       </c>
-      <c r="B16" s="582"/>
-      <c r="C16" s="582"/>
-      <c r="D16" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reestruturação da jornada de factoring com melhorias nos serviços, com destaque para a área de devedores</t>
-        </is>
-      </c>
-      <c r="E16" s="582"/>
-      <c r="F16" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por iniciar diagnóstico e alocação de recursos</t>
-        </is>
-      </c>
-      <c r="G16" s="582"/>
-      <c r="H16" s="582"/>
-      <c r="I16" s="582"/>
-      <c r="J16" s="582"/>
-      <c r="K16" s="582"/>
+      <c r="B16" s="577"/>
+      <c r="C16" s="577"/>
+      <c r="D16" s="577"/>
+      <c r="E16" s="577"/>
+      <c r="F16" s="577"/>
+      <c r="G16" s="581"/>
+      <c r="H16" s="581"/>
+      <c r="I16" s="581"/>
+      <c r="J16" s="581"/>
+      <c r="K16" s="581"/>
       <c r="L16" s="582"/>
       <c r="M16" s="582"/>
       <c r="N16" s="582"/>
       <c r="O16" s="582"/>
-      <c r="P16" s="582"/>
-      <c r="Q16" s="582"/>
-      <c r="R16" s="582"/>
-      <c r="S16" s="582"/>
-      <c r="T16" s="582"/>
-      <c r="U16" s="582"/>
-      <c r="V16" s="582"/>
-      <c r="W16" s="582"/>
-      <c r="X16" s="582"/>
-      <c r="Y16" s="582"/>
-      <c r="Z16" s="582"/>
-      <c r="AA16" s="582"/>
-      <c r="AB16" s="582"/>
-      <c r="AC16" s="582"/>
-      <c r="AD16" s="582"/>
-      <c r="AE16" s="582"/>
-      <c r="AF16" s="582"/>
-      <c r="AG16" s="582"/>
-      <c r="AH16" s="582"/>
-      <c r="AI16" s="582"/>
-      <c r="AJ16" s="582"/>
-      <c r="AK16" s="582"/>
-      <c r="AL16" s="582"/>
-      <c r="AM16" s="582"/>
-      <c r="AN16" s="582"/>
-      <c r="AO16" s="582"/>
-      <c r="AP16" s="582"/>
-      <c r="AQ16" s="582"/>
-      <c r="AR16" s="582"/>
-      <c r="AS16" s="582"/>
-      <c r="AT16" s="582"/>
-      <c r="AU16" s="582"/>
-      <c r="AV16" s="582"/>
-      <c r="AW16" s="582"/>
-      <c r="AX16" s="582"/>
-      <c r="AY16" s="582"/>
-      <c r="AZ16" s="582"/>
-      <c r="BA16" s="582"/>
-      <c r="BB16" s="582"/>
-      <c r="BC16" s="582"/>
-      <c r="BD16" s="582"/>
-      <c r="BE16" s="582"/>
-      <c r="BF16" s="582"/>
-      <c r="BG16" s="582"/>
-    </row>
-    <row r="17" ht="70" customHeight="1" spans="1:59">
-      <c r="A17" s="580" t="inlineStr">
+      <c r="P16" s="580"/>
+      <c r="Q16" s="580"/>
+      <c r="R16" s="580"/>
+      <c r="S16" s="580"/>
+      <c r="T16" s="580"/>
+      <c r="U16" s="580"/>
+      <c r="V16" s="580"/>
+      <c r="W16" s="580"/>
+      <c r="X16" s="580"/>
+      <c r="Y16" s="580"/>
+      <c r="Z16" s="580"/>
+      <c r="AA16" s="580"/>
+      <c r="AB16" s="580"/>
+      <c r="AC16" s="580"/>
+      <c r="AD16" s="580"/>
+      <c r="AE16" s="580"/>
+      <c r="AF16" s="580"/>
+      <c r="AG16" s="577"/>
+      <c r="AH16" s="577"/>
+      <c r="AI16" s="577"/>
+      <c r="AJ16" s="577"/>
+      <c r="AK16" s="577"/>
+      <c r="AL16" s="577"/>
+      <c r="AM16" s="577"/>
+      <c r="AN16" s="577"/>
+      <c r="AO16" s="577"/>
+      <c r="AP16" s="577"/>
+      <c r="AQ16" s="577"/>
+      <c r="AR16" s="577"/>
+      <c r="AS16" s="577"/>
+      <c r="AT16" s="577"/>
+      <c r="AU16" s="577"/>
+      <c r="AV16" s="577"/>
+      <c r="AW16" s="577"/>
+      <c r="AX16" s="577"/>
+      <c r="AY16" s="577"/>
+      <c r="AZ16" s="577"/>
+      <c r="BA16" s="577"/>
+      <c r="BB16" s="577"/>
+      <c r="BC16" s="577"/>
+      <c r="BD16" s="577"/>
+      <c r="BE16" s="577"/>
+      <c r="BF16" s="577"/>
+      <c r="BG16" s="577"/>
+    </row>
+    <row r="17" ht="26" customHeight="1" spans="1:59">
+      <c r="A17" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leasing simulação e contratação</t>
+          <t xml:space="preserve">Projeto KAFKA</t>
         </is>
       </c>
-      <c r="B17" s="582"/>
-      <c r="C17" s="582"/>
-      <c r="D17" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jornada E2E Leasing automóvel, imobiliário e mobiliário</t>
-        </is>
-      </c>
-      <c r="E17" s="582"/>
-      <c r="F17" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por iniciar diagnóstico e alocação de recursos</t>
-        </is>
-      </c>
-      <c r="G17" s="582"/>
-      <c r="H17" s="582"/>
-      <c r="I17" s="582"/>
-      <c r="J17" s="582"/>
-      <c r="K17" s="582"/>
-      <c r="L17" s="582"/>
-      <c r="M17" s="582"/>
-      <c r="N17" s="582"/>
-      <c r="O17" s="582"/>
+      <c r="B17" s="577"/>
+      <c r="C17" s="577"/>
+      <c r="D17" s="577"/>
+      <c r="E17" s="577"/>
+      <c r="F17" s="577"/>
+      <c r="G17" s="581"/>
+      <c r="H17" s="581"/>
+      <c r="I17" s="581"/>
+      <c r="J17" s="581"/>
+      <c r="K17" s="581"/>
+      <c r="L17" s="581"/>
+      <c r="M17" s="581"/>
+      <c r="N17" s="581"/>
+      <c r="O17" s="581"/>
       <c r="P17" s="582"/>
       <c r="Q17" s="582"/>
       <c r="R17" s="582"/>
       <c r="S17" s="582"/>
-      <c r="T17" s="582"/>
-      <c r="U17" s="582"/>
-      <c r="V17" s="582"/>
-      <c r="W17" s="582"/>
-      <c r="X17" s="582"/>
-      <c r="Y17" s="582"/>
-      <c r="Z17" s="582"/>
-      <c r="AA17" s="582"/>
-      <c r="AB17" s="582"/>
-      <c r="AC17" s="582"/>
-      <c r="AD17" s="582"/>
-      <c r="AE17" s="582"/>
-      <c r="AF17" s="582"/>
-      <c r="AG17" s="582"/>
-      <c r="AH17" s="582"/>
-      <c r="AI17" s="582"/>
-      <c r="AJ17" s="582"/>
-      <c r="AK17" s="582"/>
-      <c r="AL17" s="582"/>
-      <c r="AM17" s="582"/>
-      <c r="AN17" s="582"/>
-      <c r="AO17" s="582"/>
-      <c r="AP17" s="582"/>
-      <c r="AQ17" s="582"/>
-      <c r="AR17" s="582"/>
-      <c r="AS17" s="582"/>
-      <c r="AT17" s="582"/>
-      <c r="AU17" s="582"/>
-      <c r="AV17" s="582"/>
-      <c r="AW17" s="582"/>
-      <c r="AX17" s="582"/>
-      <c r="AY17" s="582"/>
-      <c r="AZ17" s="582"/>
-      <c r="BA17" s="582"/>
-      <c r="BB17" s="582"/>
-      <c r="BC17" s="582"/>
-      <c r="BD17" s="582"/>
-      <c r="BE17" s="582"/>
-      <c r="BF17" s="582"/>
-      <c r="BG17" s="582"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:59">
+      <c r="T17" s="585"/>
+      <c r="U17" s="585"/>
+      <c r="V17" s="585"/>
+      <c r="W17" s="585"/>
+      <c r="X17" s="585"/>
+      <c r="Y17" s="577"/>
+      <c r="Z17" s="577"/>
+      <c r="AA17" s="577"/>
+      <c r="AB17" s="577"/>
+      <c r="AC17" s="577"/>
+      <c r="AD17" s="577"/>
+      <c r="AE17" s="577"/>
+      <c r="AF17" s="577"/>
+      <c r="AG17" s="577"/>
+      <c r="AH17" s="577"/>
+      <c r="AI17" s="577"/>
+      <c r="AJ17" s="577"/>
+      <c r="AK17" s="577"/>
+      <c r="AL17" s="577"/>
+      <c r="AM17" s="577"/>
+      <c r="AN17" s="577"/>
+      <c r="AO17" s="577"/>
+      <c r="AP17" s="577"/>
+      <c r="AQ17" s="577"/>
+      <c r="AR17" s="577"/>
+      <c r="AS17" s="577"/>
+      <c r="AT17" s="577"/>
+      <c r="AU17" s="577"/>
+      <c r="AV17" s="577"/>
+      <c r="AW17" s="577"/>
+      <c r="AX17" s="577"/>
+      <c r="AY17" s="577"/>
+      <c r="AZ17" s="577"/>
+      <c r="BA17" s="577"/>
+      <c r="BB17" s="577"/>
+      <c r="BC17" s="577"/>
+      <c r="BD17" s="577"/>
+      <c r="BE17" s="577"/>
+      <c r="BF17" s="577"/>
+      <c r="BG17" s="577"/>
+    </row>
+    <row r="18" ht="26" customHeight="1" spans="1:59">
       <c r="A18" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core Lab   (18 projetos)</t>
+          <t xml:space="preserve">Crédito Digital Avançar (Wave 1)</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="70" customHeight="1" spans="1:59">
-      <c r="A19" s="577" t="inlineStr">
+      <c r="B18" s="577"/>
+      <c r="C18" s="577"/>
+      <c r="D18" s="577"/>
+      <c r="E18" s="577"/>
+      <c r="F18" s="577"/>
+      <c r="G18" s="581"/>
+      <c r="H18" s="581"/>
+      <c r="I18" s="581"/>
+      <c r="J18" s="581"/>
+      <c r="K18" s="581"/>
+      <c r="L18" s="581"/>
+      <c r="M18" s="581"/>
+      <c r="N18" s="581"/>
+      <c r="O18" s="581"/>
+      <c r="P18" s="582"/>
+      <c r="Q18" s="582"/>
+      <c r="R18" s="582"/>
+      <c r="S18" s="582"/>
+      <c r="T18" s="582"/>
+      <c r="U18" s="582"/>
+      <c r="V18" s="582"/>
+      <c r="W18" s="582"/>
+      <c r="X18" s="582"/>
+      <c r="Y18" s="577"/>
+      <c r="Z18" s="577"/>
+      <c r="AA18" s="577"/>
+      <c r="AB18" s="577"/>
+      <c r="AC18" s="577"/>
+      <c r="AD18" s="577"/>
+      <c r="AE18" s="577"/>
+      <c r="AF18" s="577"/>
+      <c r="AG18" s="577"/>
+      <c r="AH18" s="577"/>
+      <c r="AI18" s="577"/>
+      <c r="AJ18" s="577"/>
+      <c r="AK18" s="577"/>
+      <c r="AL18" s="577"/>
+      <c r="AM18" s="577"/>
+      <c r="AN18" s="577"/>
+      <c r="AO18" s="577"/>
+      <c r="AP18" s="577"/>
+      <c r="AQ18" s="577"/>
+      <c r="AR18" s="577"/>
+      <c r="AS18" s="577"/>
+      <c r="AT18" s="577"/>
+      <c r="AU18" s="577"/>
+      <c r="AV18" s="577"/>
+      <c r="AW18" s="577"/>
+      <c r="AX18" s="577"/>
+      <c r="AY18" s="577"/>
+      <c r="AZ18" s="577"/>
+      <c r="BA18" s="577"/>
+      <c r="BB18" s="577"/>
+      <c r="BC18" s="577"/>
+      <c r="BD18" s="577"/>
+      <c r="BE18" s="577"/>
+      <c r="BF18" s="577"/>
+      <c r="BG18" s="577"/>
+    </row>
+    <row r="19" ht="26" customHeight="1" spans="1:59">
+      <c r="A19" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">API enhanced entity registry for non-Clients (COMPprofile) (1)</t>
+          <t xml:space="preserve">Via Verde</t>
         </is>
       </c>
-      <c r="B19" s="579"/>
-      <c r="C19" s="579"/>
-      <c r="D19" s="578" t="inlineStr">
+      <c r="B19" s="577"/>
+      <c r="C19" s="577"/>
+      <c r="D19" s="577"/>
+      <c r="E19" s="577"/>
+      <c r="F19" s="577"/>
+      <c r="G19" s="581"/>
+      <c r="H19" s="581"/>
+      <c r="I19" s="581"/>
+      <c r="J19" s="581"/>
+      <c r="K19" s="581"/>
+      <c r="L19" s="581"/>
+      <c r="M19" s="581"/>
+      <c r="N19" s="581"/>
+      <c r="O19" s="581"/>
+      <c r="P19" s="585"/>
+      <c r="Q19" s="585"/>
+      <c r="R19" s="585"/>
+      <c r="S19" s="585"/>
+      <c r="T19" s="585"/>
+      <c r="U19" s="585"/>
+      <c r="V19" s="585"/>
+      <c r="W19" s="585"/>
+      <c r="X19" s="585"/>
+      <c r="Y19" s="585"/>
+      <c r="Z19" s="585"/>
+      <c r="AA19" s="585"/>
+      <c r="AB19" s="585"/>
+      <c r="AC19" s="585"/>
+      <c r="AD19" s="585"/>
+      <c r="AE19" s="585"/>
+      <c r="AF19" s="585"/>
+      <c r="AG19" s="577"/>
+      <c r="AH19" s="577"/>
+      <c r="AI19" s="577"/>
+      <c r="AJ19" s="577"/>
+      <c r="AK19" s="577"/>
+      <c r="AL19" s="577"/>
+      <c r="AM19" s="577"/>
+      <c r="AN19" s="577"/>
+      <c r="AO19" s="577"/>
+      <c r="AP19" s="577"/>
+      <c r="AQ19" s="577"/>
+      <c r="AR19" s="577"/>
+      <c r="AS19" s="577"/>
+      <c r="AT19" s="577"/>
+      <c r="AU19" s="577"/>
+      <c r="AV19" s="577"/>
+      <c r="AW19" s="577"/>
+      <c r="AX19" s="577"/>
+      <c r="AY19" s="577"/>
+      <c r="AZ19" s="577"/>
+      <c r="BA19" s="577"/>
+      <c r="BB19" s="577"/>
+      <c r="BC19" s="577"/>
+      <c r="BD19" s="577"/>
+      <c r="BE19" s="577"/>
+      <c r="BF19" s="577"/>
+      <c r="BG19" s="577"/>
+    </row>
+    <row r="20" ht="26" customHeight="1" spans="1:59">
+      <c r="A20" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registo de empresas nacionais no CIS e respetivos  comprovativos (1º use case Fornecedores não Clientes)</t>
+          <t xml:space="preserve">Factoring - Digital notifications</t>
         </is>
       </c>
-      <c r="E19" s="579" t="inlineStr">
+      <c r="B20" s="577"/>
+      <c r="C20" s="577"/>
+      <c r="D20" s="577"/>
+      <c r="E20" s="577"/>
+      <c r="F20" s="577"/>
+      <c r="G20" s="581"/>
+      <c r="H20" s="581"/>
+      <c r="I20" s="581"/>
+      <c r="J20" s="581"/>
+      <c r="K20" s="581"/>
+      <c r="L20" s="581"/>
+      <c r="M20" s="581"/>
+      <c r="N20" s="581"/>
+      <c r="O20" s="581"/>
+      <c r="P20" s="582"/>
+      <c r="Q20" s="582"/>
+      <c r="R20" s="582"/>
+      <c r="S20" s="582"/>
+      <c r="T20" s="582"/>
+      <c r="U20" s="582"/>
+      <c r="V20" s="582"/>
+      <c r="W20" s="582"/>
+      <c r="X20" s="582"/>
+      <c r="Y20" s="577"/>
+      <c r="Z20" s="577"/>
+      <c r="AA20" s="577"/>
+      <c r="AB20" s="577"/>
+      <c r="AC20" s="577"/>
+      <c r="AD20" s="577"/>
+      <c r="AE20" s="577"/>
+      <c r="AF20" s="577"/>
+      <c r="AG20" s="577"/>
+      <c r="AH20" s="577"/>
+      <c r="AI20" s="577"/>
+      <c r="AJ20" s="577"/>
+      <c r="AK20" s="577"/>
+      <c r="AL20" s="577"/>
+      <c r="AM20" s="577"/>
+      <c r="AN20" s="577"/>
+      <c r="AO20" s="577"/>
+      <c r="AP20" s="577"/>
+      <c r="AQ20" s="577"/>
+      <c r="AR20" s="577"/>
+      <c r="AS20" s="577"/>
+      <c r="AT20" s="577"/>
+      <c r="AU20" s="577"/>
+      <c r="AV20" s="577"/>
+      <c r="AW20" s="577"/>
+      <c r="AX20" s="577"/>
+      <c r="AY20" s="577"/>
+      <c r="AZ20" s="577"/>
+      <c r="BA20" s="577"/>
+      <c r="BB20" s="577"/>
+      <c r="BC20" s="577"/>
+      <c r="BD20" s="577"/>
+      <c r="BE20" s="577"/>
+      <c r="BF20" s="577"/>
+      <c r="BG20" s="577"/>
+    </row>
+    <row r="21" ht="26" customHeight="1" spans="1:59">
+      <c r="A21" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">25-11-2026</t>
+          <t xml:space="preserve">Requisição de Cheques</t>
         </is>
       </c>
-      <c r="F19" s="578" t="inlineStr">
+      <c r="B21" s="577"/>
+      <c r="C21" s="577"/>
+      <c r="D21" s="577"/>
+      <c r="E21" s="577"/>
+      <c r="F21" s="577"/>
+      <c r="G21" s="580"/>
+      <c r="H21" s="580"/>
+      <c r="I21" s="580"/>
+      <c r="J21" s="580"/>
+      <c r="K21" s="580"/>
+      <c r="L21" s="581"/>
+      <c r="M21" s="581"/>
+      <c r="N21" s="581"/>
+      <c r="O21" s="581"/>
+      <c r="P21" s="583"/>
+      <c r="Q21" s="583"/>
+      <c r="R21" s="583"/>
+      <c r="S21" s="583"/>
+      <c r="T21" s="583"/>
+      <c r="U21" s="583"/>
+      <c r="V21" s="583"/>
+      <c r="W21" s="583"/>
+      <c r="X21" s="583"/>
+      <c r="Y21" s="585"/>
+      <c r="Z21" s="585"/>
+      <c r="AA21" s="585"/>
+      <c r="AB21" s="585"/>
+      <c r="AC21" s="585"/>
+      <c r="AD21" s="585"/>
+      <c r="AE21" s="585"/>
+      <c r="AF21" s="585"/>
+      <c r="AG21" s="577"/>
+      <c r="AH21" s="577"/>
+      <c r="AI21" s="577"/>
+      <c r="AJ21" s="577"/>
+      <c r="AK21" s="577"/>
+      <c r="AL21" s="577"/>
+      <c r="AM21" s="577"/>
+      <c r="AN21" s="577"/>
+      <c r="AO21" s="577"/>
+      <c r="AP21" s="577"/>
+      <c r="AQ21" s="577"/>
+      <c r="AR21" s="577"/>
+      <c r="AS21" s="577"/>
+      <c r="AT21" s="577"/>
+      <c r="AU21" s="577"/>
+      <c r="AV21" s="577"/>
+      <c r="AW21" s="577"/>
+      <c r="AX21" s="577"/>
+      <c r="AY21" s="577"/>
+      <c r="AZ21" s="577"/>
+      <c r="BA21" s="577"/>
+      <c r="BB21" s="577"/>
+      <c r="BC21" s="577"/>
+      <c r="BD21" s="577"/>
+      <c r="BE21" s="577"/>
+      <c r="BF21" s="577"/>
+      <c r="BG21" s="577"/>
+    </row>
+    <row r="22" ht="26" customHeight="1" spans="1:59">
+      <c r="A22" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falta certificar coerência de dados da API. 
-Confrontar dados InformaDB com CRC ~1 semana a tempo integral
-FCA 11-03-2026: a acompanhar novamente a certificação
-FCA 27-01-2026: retirar do Back Log. Core LAB da apoio como Consultor</t>
+          <t xml:space="preserve">B2B Millennium API</t>
         </is>
       </c>
-      <c r="G19" s="591"/>
-      <c r="H19" s="591"/>
-      <c r="I19" s="591"/>
-      <c r="J19" s="591"/>
-      <c r="K19" s="591"/>
-      <c r="L19" s="591"/>
-      <c r="M19" s="591"/>
-      <c r="N19" s="591"/>
-      <c r="O19" s="591"/>
-      <c r="P19" s="591"/>
-      <c r="Q19" s="591"/>
-      <c r="R19" s="591"/>
-      <c r="S19" s="591"/>
-      <c r="T19" s="591"/>
-      <c r="U19" s="591"/>
-      <c r="V19" s="591"/>
-      <c r="W19" s="591"/>
-      <c r="X19" s="591"/>
-      <c r="Y19" s="591"/>
-      <c r="Z19" s="591"/>
-      <c r="AA19" s="591"/>
-      <c r="AB19" s="591"/>
-      <c r="AC19" s="591"/>
-      <c r="AD19" s="591"/>
-      <c r="AE19" s="591"/>
-      <c r="AF19" s="591"/>
-      <c r="AG19" s="591"/>
-      <c r="AH19" s="591"/>
-      <c r="AI19" s="591"/>
-      <c r="AJ19" s="591"/>
-      <c r="AK19" s="591"/>
-      <c r="AL19" s="591"/>
-      <c r="AM19" s="591"/>
-      <c r="AN19" s="591"/>
-      <c r="AO19" s="591"/>
-      <c r="AP19" s="591"/>
-      <c r="AQ19" s="591"/>
-      <c r="AR19" s="591"/>
-      <c r="AS19" s="591"/>
-      <c r="AT19" s="591"/>
-      <c r="AU19" s="591"/>
-      <c r="AV19" s="591"/>
-      <c r="AW19" s="591"/>
-      <c r="AX19" s="591"/>
-      <c r="AY19" s="591"/>
-      <c r="AZ19" s="591"/>
-      <c r="BA19" s="591"/>
-      <c r="BB19" s="590"/>
-      <c r="BC19" s="591"/>
-      <c r="BD19" s="591"/>
-      <c r="BE19" s="591"/>
-      <c r="BF19" s="591"/>
-      <c r="BG19" s="591"/>
-    </row>
-    <row r="20" ht="70" customHeight="1" spans="1:59">
-      <c r="A20" s="577" t="inlineStr">
+      <c r="B22" s="577"/>
+      <c r="C22" s="577"/>
+      <c r="D22" s="577"/>
+      <c r="E22" s="577"/>
+      <c r="F22" s="577"/>
+      <c r="G22" s="580"/>
+      <c r="H22" s="580"/>
+      <c r="I22" s="580"/>
+      <c r="J22" s="580"/>
+      <c r="K22" s="580"/>
+      <c r="L22" s="581"/>
+      <c r="M22" s="581"/>
+      <c r="N22" s="581"/>
+      <c r="O22" s="581"/>
+      <c r="P22" s="584"/>
+      <c r="Q22" s="584"/>
+      <c r="R22" s="584"/>
+      <c r="S22" s="584"/>
+      <c r="T22" s="582"/>
+      <c r="U22" s="582"/>
+      <c r="V22" s="582"/>
+      <c r="W22" s="582"/>
+      <c r="X22" s="582"/>
+      <c r="Y22" s="583"/>
+      <c r="Z22" s="583"/>
+      <c r="AA22" s="583"/>
+      <c r="AB22" s="583"/>
+      <c r="AC22" s="583"/>
+      <c r="AD22" s="583"/>
+      <c r="AE22" s="583"/>
+      <c r="AF22" s="583"/>
+      <c r="AG22" s="577"/>
+      <c r="AH22" s="577"/>
+      <c r="AI22" s="577"/>
+      <c r="AJ22" s="577"/>
+      <c r="AK22" s="577"/>
+      <c r="AL22" s="577"/>
+      <c r="AM22" s="577"/>
+      <c r="AN22" s="577"/>
+      <c r="AO22" s="577"/>
+      <c r="AP22" s="577"/>
+      <c r="AQ22" s="577"/>
+      <c r="AR22" s="577"/>
+      <c r="AS22" s="577"/>
+      <c r="AT22" s="577"/>
+      <c r="AU22" s="577"/>
+      <c r="AV22" s="577"/>
+      <c r="AW22" s="577"/>
+      <c r="AX22" s="577"/>
+      <c r="AY22" s="577"/>
+      <c r="AZ22" s="577"/>
+      <c r="BA22" s="577"/>
+      <c r="BB22" s="577"/>
+      <c r="BC22" s="577"/>
+      <c r="BD22" s="577"/>
+      <c r="BE22" s="577"/>
+      <c r="BF22" s="577"/>
+      <c r="BG22" s="577"/>
+    </row>
+    <row r="23" ht="26" customHeight="1" spans="1:59">
+      <c r="A23" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">New website onboarding for Suppliers (non-Clients) (1)</t>
+          <t xml:space="preserve">Pedido de cartão de débito (E2E)</t>
         </is>
       </c>
-      <c r="B20" s="579"/>
-      <c r="C20" s="579"/>
-      <c r="D20" s="578" t="inlineStr">
+      <c r="B23" s="577"/>
+      <c r="C23" s="577"/>
+      <c r="D23" s="577"/>
+      <c r="E23" s="577"/>
+      <c r="F23" s="577"/>
+      <c r="G23" s="582"/>
+      <c r="H23" s="582"/>
+      <c r="I23" s="582"/>
+      <c r="J23" s="582"/>
+      <c r="K23" s="582"/>
+      <c r="L23" s="582"/>
+      <c r="M23" s="582"/>
+      <c r="N23" s="582"/>
+      <c r="O23" s="582"/>
+      <c r="P23" s="582"/>
+      <c r="Q23" s="582"/>
+      <c r="R23" s="582"/>
+      <c r="S23" s="582"/>
+      <c r="T23" s="582"/>
+      <c r="U23" s="582"/>
+      <c r="V23" s="582"/>
+      <c r="W23" s="582"/>
+      <c r="X23" s="582"/>
+      <c r="Y23" s="577"/>
+      <c r="Z23" s="577"/>
+      <c r="AA23" s="577"/>
+      <c r="AB23" s="577"/>
+      <c r="AC23" s="577"/>
+      <c r="AD23" s="577"/>
+      <c r="AE23" s="577"/>
+      <c r="AF23" s="577"/>
+      <c r="AG23" s="577"/>
+      <c r="AH23" s="577"/>
+      <c r="AI23" s="577"/>
+      <c r="AJ23" s="577"/>
+      <c r="AK23" s="577"/>
+      <c r="AL23" s="577"/>
+      <c r="AM23" s="577"/>
+      <c r="AN23" s="577"/>
+      <c r="AO23" s="577"/>
+      <c r="AP23" s="577"/>
+      <c r="AQ23" s="577"/>
+      <c r="AR23" s="577"/>
+      <c r="AS23" s="577"/>
+      <c r="AT23" s="577"/>
+      <c r="AU23" s="577"/>
+      <c r="AV23" s="577"/>
+      <c r="AW23" s="577"/>
+      <c r="AX23" s="577"/>
+      <c r="AY23" s="577"/>
+      <c r="AZ23" s="577"/>
+      <c r="BA23" s="577"/>
+      <c r="BB23" s="577"/>
+      <c r="BC23" s="577"/>
+      <c r="BD23" s="577"/>
+      <c r="BE23" s="577"/>
+      <c r="BF23" s="577"/>
+      <c r="BG23" s="577"/>
+    </row>
+    <row r="24" ht="26" customHeight="1" spans="1:59">
+      <c r="A24" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registo e recenseamento de Fornecedores nacionais não Clientes no MSE – Confirming</t>
+          <t xml:space="preserve">PayByMillennium</t>
         </is>
       </c>
-      <c r="E20" s="579" t="inlineStr">
+      <c r="B24" s="577"/>
+      <c r="C24" s="577"/>
+      <c r="D24" s="577"/>
+      <c r="E24" s="577"/>
+      <c r="F24" s="577"/>
+      <c r="G24" s="581"/>
+      <c r="H24" s="581"/>
+      <c r="I24" s="581"/>
+      <c r="J24" s="581"/>
+      <c r="K24" s="581"/>
+      <c r="L24" s="581"/>
+      <c r="M24" s="581"/>
+      <c r="N24" s="581"/>
+      <c r="O24" s="581"/>
+      <c r="P24" s="581"/>
+      <c r="Q24" s="581"/>
+      <c r="R24" s="581"/>
+      <c r="S24" s="581"/>
+      <c r="T24" s="580"/>
+      <c r="U24" s="580"/>
+      <c r="V24" s="580"/>
+      <c r="W24" s="580"/>
+      <c r="X24" s="580"/>
+      <c r="Y24" s="577"/>
+      <c r="Z24" s="577"/>
+      <c r="AA24" s="577"/>
+      <c r="AB24" s="577"/>
+      <c r="AC24" s="577"/>
+      <c r="AD24" s="577"/>
+      <c r="AE24" s="577"/>
+      <c r="AF24" s="577"/>
+      <c r="AG24" s="577"/>
+      <c r="AH24" s="577"/>
+      <c r="AI24" s="577"/>
+      <c r="AJ24" s="577"/>
+      <c r="AK24" s="577"/>
+      <c r="AL24" s="577"/>
+      <c r="AM24" s="577"/>
+      <c r="AN24" s="577"/>
+      <c r="AO24" s="577"/>
+      <c r="AP24" s="577"/>
+      <c r="AQ24" s="577"/>
+      <c r="AR24" s="577"/>
+      <c r="AS24" s="577"/>
+      <c r="AT24" s="577"/>
+      <c r="AU24" s="577"/>
+      <c r="AV24" s="577"/>
+      <c r="AW24" s="577"/>
+      <c r="AX24" s="577"/>
+      <c r="AY24" s="577"/>
+      <c r="AZ24" s="577"/>
+      <c r="BA24" s="577"/>
+      <c r="BB24" s="577"/>
+      <c r="BC24" s="577"/>
+      <c r="BD24" s="577"/>
+      <c r="BE24" s="577"/>
+      <c r="BF24" s="577"/>
+      <c r="BG24" s="577"/>
+    </row>
+    <row r="25" ht="26" customHeight="1" spans="1:59">
+      <c r="A25" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-03-2026</t>
+          <t xml:space="preserve">Cartões Servicing</t>
         </is>
       </c>
-      <c r="F20" s="578" t="inlineStr">
+      <c r="B25" s="577"/>
+      <c r="C25" s="577"/>
+      <c r="D25" s="577"/>
+      <c r="E25" s="577"/>
+      <c r="F25" s="577"/>
+      <c r="G25" s="581"/>
+      <c r="H25" s="581"/>
+      <c r="I25" s="581"/>
+      <c r="J25" s="581"/>
+      <c r="K25" s="581"/>
+      <c r="L25" s="581"/>
+      <c r="M25" s="581"/>
+      <c r="N25" s="581"/>
+      <c r="O25" s="581"/>
+      <c r="P25" s="581"/>
+      <c r="Q25" s="581"/>
+      <c r="R25" s="581"/>
+      <c r="S25" s="581"/>
+      <c r="T25" s="580"/>
+      <c r="U25" s="580"/>
+      <c r="V25" s="580"/>
+      <c r="W25" s="580"/>
+      <c r="X25" s="580"/>
+      <c r="Y25" s="577"/>
+      <c r="Z25" s="577"/>
+      <c r="AA25" s="577"/>
+      <c r="AB25" s="577"/>
+      <c r="AC25" s="577"/>
+      <c r="AD25" s="577"/>
+      <c r="AE25" s="577"/>
+      <c r="AF25" s="577"/>
+      <c r="AG25" s="577"/>
+      <c r="AH25" s="577"/>
+      <c r="AI25" s="577"/>
+      <c r="AJ25" s="577"/>
+      <c r="AK25" s="577"/>
+      <c r="AL25" s="577"/>
+      <c r="AM25" s="577"/>
+      <c r="AN25" s="577"/>
+      <c r="AO25" s="577"/>
+      <c r="AP25" s="577"/>
+      <c r="AQ25" s="577"/>
+      <c r="AR25" s="577"/>
+      <c r="AS25" s="577"/>
+      <c r="AT25" s="577"/>
+      <c r="AU25" s="577"/>
+      <c r="AV25" s="577"/>
+      <c r="AW25" s="577"/>
+      <c r="AX25" s="577"/>
+      <c r="AY25" s="577"/>
+      <c r="AZ25" s="577"/>
+      <c r="BA25" s="577"/>
+      <c r="BB25" s="577"/>
+      <c r="BC25" s="577"/>
+      <c r="BD25" s="577"/>
+      <c r="BE25" s="577"/>
+      <c r="BF25" s="577"/>
+      <c r="BG25" s="577"/>
+    </row>
+    <row r="26" ht="26" customHeight="1" spans="1:59">
+      <c r="A26" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Base (~75%) será reutilizado no revamp do novo Registo e Recenseamento ao MSE
-FCA 11-03-2026: Alterei PRD para Mar 26
-FCA 27-01-2026:  inicio de certificação. Mantem ida a PRD em FEV2026</t>
+          <t xml:space="preserve">Criação de Utilizadores (Operadores)</t>
         </is>
       </c>
-      <c r="G20" s="591"/>
-      <c r="H20" s="591"/>
-      <c r="I20" s="591"/>
-      <c r="J20" s="591"/>
-      <c r="K20" s="591"/>
-      <c r="L20" s="591"/>
-      <c r="M20" s="591"/>
-      <c r="N20" s="591"/>
-      <c r="O20" s="591"/>
-      <c r="P20" s="591"/>
-      <c r="Q20" s="591"/>
-      <c r="R20" s="591"/>
-      <c r="S20" s="590"/>
-      <c r="T20" s="591"/>
-      <c r="U20" s="591"/>
-      <c r="V20" s="591"/>
-      <c r="W20" s="591"/>
-      <c r="X20" s="591"/>
-      <c r="Y20" s="591"/>
-      <c r="Z20" s="591"/>
-      <c r="AA20" s="591"/>
-      <c r="AB20" s="591"/>
-      <c r="AC20" s="591"/>
-      <c r="AD20" s="591"/>
-      <c r="AE20" s="591"/>
-      <c r="AF20" s="591"/>
-      <c r="AG20" s="591"/>
-      <c r="AH20" s="591"/>
-      <c r="AI20" s="591"/>
-      <c r="AJ20" s="591"/>
-      <c r="AK20" s="591"/>
-      <c r="AL20" s="591"/>
-      <c r="AM20" s="591"/>
-      <c r="AN20" s="591"/>
-      <c r="AO20" s="591"/>
-      <c r="AP20" s="591"/>
-      <c r="AQ20" s="591"/>
-      <c r="AR20" s="591"/>
-      <c r="AS20" s="591"/>
-      <c r="AT20" s="591"/>
-      <c r="AU20" s="591"/>
-      <c r="AV20" s="591"/>
-      <c r="AW20" s="591"/>
-      <c r="AX20" s="591"/>
-      <c r="AY20" s="591"/>
-      <c r="AZ20" s="591"/>
-      <c r="BA20" s="591"/>
-      <c r="BB20" s="591"/>
-      <c r="BC20" s="591"/>
-      <c r="BD20" s="591"/>
-      <c r="BE20" s="591"/>
-      <c r="BF20" s="591"/>
-      <c r="BG20" s="591"/>
-    </row>
-    <row r="21" ht="70" customHeight="1" spans="1:59">
-      <c r="A21" s="577" t="inlineStr">
+      <c r="B26" s="577"/>
+      <c r="C26" s="577"/>
+      <c r="D26" s="577"/>
+      <c r="E26" s="577"/>
+      <c r="F26" s="577"/>
+      <c r="G26" s="581"/>
+      <c r="H26" s="581"/>
+      <c r="I26" s="581"/>
+      <c r="J26" s="581"/>
+      <c r="K26" s="581"/>
+      <c r="L26" s="581"/>
+      <c r="M26" s="581"/>
+      <c r="N26" s="581"/>
+      <c r="O26" s="581"/>
+      <c r="P26" s="582"/>
+      <c r="Q26" s="582"/>
+      <c r="R26" s="582"/>
+      <c r="S26" s="582"/>
+      <c r="T26" s="582"/>
+      <c r="U26" s="582"/>
+      <c r="V26" s="582"/>
+      <c r="W26" s="582"/>
+      <c r="X26" s="582"/>
+      <c r="Y26" s="577"/>
+      <c r="Z26" s="577"/>
+      <c r="AA26" s="577"/>
+      <c r="AB26" s="577"/>
+      <c r="AC26" s="577"/>
+      <c r="AD26" s="577"/>
+      <c r="AE26" s="577"/>
+      <c r="AF26" s="577"/>
+      <c r="AG26" s="577"/>
+      <c r="AH26" s="577"/>
+      <c r="AI26" s="577"/>
+      <c r="AJ26" s="577"/>
+      <c r="AK26" s="577"/>
+      <c r="AL26" s="577"/>
+      <c r="AM26" s="577"/>
+      <c r="AN26" s="577"/>
+      <c r="AO26" s="577"/>
+      <c r="AP26" s="577"/>
+      <c r="AQ26" s="577"/>
+      <c r="AR26" s="577"/>
+      <c r="AS26" s="577"/>
+      <c r="AT26" s="577"/>
+      <c r="AU26" s="577"/>
+      <c r="AV26" s="577"/>
+      <c r="AW26" s="577"/>
+      <c r="AX26" s="577"/>
+      <c r="AY26" s="577"/>
+      <c r="AZ26" s="577"/>
+      <c r="BA26" s="577"/>
+      <c r="BB26" s="577"/>
+      <c r="BC26" s="577"/>
+      <c r="BD26" s="577"/>
+      <c r="BE26" s="577"/>
+      <c r="BF26" s="577"/>
+      <c r="BG26" s="577"/>
+    </row>
+    <row r="27" ht="26" customHeight="1" spans="1:59">
+      <c r="A27" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPProfile : Back office + Onboarding and maintenance</t>
+          <t xml:space="preserve">Certificado Digital</t>
         </is>
       </c>
-      <c r="B21" s="579"/>
-      <c r="C21" s="579"/>
-      <c r="D21" s="578" t="inlineStr">
+      <c r="B27" s="577"/>
+      <c r="C27" s="577"/>
+      <c r="D27" s="577"/>
+      <c r="E27" s="577"/>
+      <c r="F27" s="577"/>
+      <c r="G27" s="581"/>
+      <c r="H27" s="581"/>
+      <c r="I27" s="581"/>
+      <c r="J27" s="581"/>
+      <c r="K27" s="581"/>
+      <c r="L27" s="581"/>
+      <c r="M27" s="581"/>
+      <c r="N27" s="581"/>
+      <c r="O27" s="581"/>
+      <c r="P27" s="582"/>
+      <c r="Q27" s="582"/>
+      <c r="R27" s="582"/>
+      <c r="S27" s="582"/>
+      <c r="T27" s="582"/>
+      <c r="U27" s="582"/>
+      <c r="V27" s="582"/>
+      <c r="W27" s="582"/>
+      <c r="X27" s="582"/>
+      <c r="Y27" s="577"/>
+      <c r="Z27" s="577"/>
+      <c r="AA27" s="577"/>
+      <c r="AB27" s="577"/>
+      <c r="AC27" s="577"/>
+      <c r="AD27" s="577"/>
+      <c r="AE27" s="577"/>
+      <c r="AF27" s="577"/>
+      <c r="AG27" s="577"/>
+      <c r="AH27" s="577"/>
+      <c r="AI27" s="577"/>
+      <c r="AJ27" s="577"/>
+      <c r="AK27" s="577"/>
+      <c r="AL27" s="577"/>
+      <c r="AM27" s="577"/>
+      <c r="AN27" s="577"/>
+      <c r="AO27" s="577"/>
+      <c r="AP27" s="577"/>
+      <c r="AQ27" s="577"/>
+      <c r="AR27" s="577"/>
+      <c r="AS27" s="577"/>
+      <c r="AT27" s="577"/>
+      <c r="AU27" s="577"/>
+      <c r="AV27" s="577"/>
+      <c r="AW27" s="577"/>
+      <c r="AX27" s="577"/>
+      <c r="AY27" s="577"/>
+      <c r="AZ27" s="577"/>
+      <c r="BA27" s="577"/>
+      <c r="BB27" s="577"/>
+      <c r="BC27" s="577"/>
+      <c r="BD27" s="577"/>
+      <c r="BE27" s="577"/>
+      <c r="BF27" s="577"/>
+      <c r="BG27" s="577"/>
+    </row>
+    <row r="28" ht="26" customHeight="1" spans="1:59">
+      <c r="A28" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Com back office para tratamento e classificação de todos os dados recebidos das várias fontes. Gera pacotes de dados standardizados e documentos prontos a serem consumidos internamente.  Pedido cria entidades em Central com arquivo de documentos</t>
+          <t xml:space="preserve">M Certificados</t>
         </is>
       </c>
-      <c r="E21" s="579" t="inlineStr">
+      <c r="B28" s="577"/>
+      <c r="C28" s="577"/>
+      <c r="D28" s="577"/>
+      <c r="E28" s="577"/>
+      <c r="F28" s="577"/>
+      <c r="G28" s="581"/>
+      <c r="H28" s="581"/>
+      <c r="I28" s="581"/>
+      <c r="J28" s="581"/>
+      <c r="K28" s="581"/>
+      <c r="L28" s="581"/>
+      <c r="M28" s="581"/>
+      <c r="N28" s="581"/>
+      <c r="O28" s="581"/>
+      <c r="P28" s="581"/>
+      <c r="Q28" s="581"/>
+      <c r="R28" s="581"/>
+      <c r="S28" s="581"/>
+      <c r="T28" s="580"/>
+      <c r="U28" s="580"/>
+      <c r="V28" s="580"/>
+      <c r="W28" s="580"/>
+      <c r="X28" s="580"/>
+      <c r="Y28" s="577"/>
+      <c r="Z28" s="577"/>
+      <c r="AA28" s="577"/>
+      <c r="AB28" s="577"/>
+      <c r="AC28" s="577"/>
+      <c r="AD28" s="577"/>
+      <c r="AE28" s="577"/>
+      <c r="AF28" s="577"/>
+      <c r="AG28" s="577"/>
+      <c r="AH28" s="577"/>
+      <c r="AI28" s="577"/>
+      <c r="AJ28" s="577"/>
+      <c r="AK28" s="577"/>
+      <c r="AL28" s="577"/>
+      <c r="AM28" s="577"/>
+      <c r="AN28" s="577"/>
+      <c r="AO28" s="577"/>
+      <c r="AP28" s="577"/>
+      <c r="AQ28" s="577"/>
+      <c r="AR28" s="577"/>
+      <c r="AS28" s="577"/>
+      <c r="AT28" s="577"/>
+      <c r="AU28" s="577"/>
+      <c r="AV28" s="577"/>
+      <c r="AW28" s="577"/>
+      <c r="AX28" s="577"/>
+      <c r="AY28" s="577"/>
+      <c r="AZ28" s="577"/>
+      <c r="BA28" s="577"/>
+      <c r="BB28" s="577"/>
+      <c r="BC28" s="577"/>
+      <c r="BD28" s="577"/>
+      <c r="BE28" s="577"/>
+      <c r="BF28" s="577"/>
+      <c r="BG28" s="577"/>
+    </row>
+    <row r="29" ht="26" customHeight="1" spans="1:59">
+      <c r="A29" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fev 26</t>
+          <t xml:space="preserve">Open Banking</t>
         </is>
       </c>
-      <c r="F21" s="578" t="inlineStr">
+      <c r="B29" s="577"/>
+      <c r="C29" s="577"/>
+      <c r="D29" s="577"/>
+      <c r="E29" s="577"/>
+      <c r="F29" s="577"/>
+      <c r="G29" s="580"/>
+      <c r="H29" s="580"/>
+      <c r="I29" s="580"/>
+      <c r="J29" s="580"/>
+      <c r="K29" s="580"/>
+      <c r="L29" s="580"/>
+      <c r="M29" s="580"/>
+      <c r="N29" s="580"/>
+      <c r="O29" s="580"/>
+      <c r="P29" s="580"/>
+      <c r="Q29" s="580"/>
+      <c r="R29" s="580"/>
+      <c r="S29" s="580"/>
+      <c r="T29" s="584"/>
+      <c r="U29" s="584"/>
+      <c r="V29" s="584"/>
+      <c r="W29" s="584"/>
+      <c r="X29" s="584"/>
+      <c r="Y29" s="582"/>
+      <c r="Z29" s="582"/>
+      <c r="AA29" s="582"/>
+      <c r="AB29" s="582"/>
+      <c r="AC29" s="583"/>
+      <c r="AD29" s="583"/>
+      <c r="AE29" s="583"/>
+      <c r="AF29" s="583"/>
+      <c r="AG29" s="577"/>
+      <c r="AH29" s="577"/>
+      <c r="AI29" s="577"/>
+      <c r="AJ29" s="577"/>
+      <c r="AK29" s="577"/>
+      <c r="AL29" s="577"/>
+      <c r="AM29" s="577"/>
+      <c r="AN29" s="577"/>
+      <c r="AO29" s="577"/>
+      <c r="AP29" s="577"/>
+      <c r="AQ29" s="577"/>
+      <c r="AR29" s="577"/>
+      <c r="AS29" s="577"/>
+      <c r="AT29" s="577"/>
+      <c r="AU29" s="577"/>
+      <c r="AV29" s="577"/>
+      <c r="AW29" s="577"/>
+      <c r="AX29" s="577"/>
+      <c r="AY29" s="577"/>
+      <c r="AZ29" s="577"/>
+      <c r="BA29" s="577"/>
+      <c r="BB29" s="577"/>
+      <c r="BC29" s="577"/>
+      <c r="BD29" s="577"/>
+      <c r="BE29" s="577"/>
+      <c r="BF29" s="577"/>
+      <c r="BG29" s="577"/>
+    </row>
+    <row r="30" ht="26" customHeight="1" spans="1:59">
+      <c r="A30" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">FCA 11-03-2026: está em PRD desde FEV</t>
+          <t xml:space="preserve">Retornos de Ficheiros</t>
         </is>
       </c>
-      <c r="G21" s="591"/>
-      <c r="H21" s="591"/>
-      <c r="I21" s="591"/>
-      <c r="J21" s="591"/>
-      <c r="K21" s="590"/>
-      <c r="L21" s="591"/>
-      <c r="M21" s="591"/>
-      <c r="N21" s="591"/>
-      <c r="O21" s="591"/>
-      <c r="P21" s="591"/>
-      <c r="Q21" s="591"/>
-      <c r="R21" s="591"/>
-      <c r="S21" s="591"/>
-      <c r="T21" s="591"/>
-      <c r="U21" s="591"/>
-      <c r="V21" s="591"/>
-      <c r="W21" s="591"/>
-      <c r="X21" s="591"/>
-      <c r="Y21" s="591"/>
-      <c r="Z21" s="591"/>
-      <c r="AA21" s="591"/>
-      <c r="AB21" s="591"/>
-      <c r="AC21" s="591"/>
-      <c r="AD21" s="591"/>
-      <c r="AE21" s="591"/>
-      <c r="AF21" s="591"/>
-      <c r="AG21" s="591"/>
-      <c r="AH21" s="591"/>
-      <c r="AI21" s="591"/>
-      <c r="AJ21" s="591"/>
-      <c r="AK21" s="591"/>
-      <c r="AL21" s="591"/>
-      <c r="AM21" s="591"/>
-      <c r="AN21" s="591"/>
-      <c r="AO21" s="591"/>
-      <c r="AP21" s="591"/>
-      <c r="AQ21" s="591"/>
-      <c r="AR21" s="591"/>
-      <c r="AS21" s="591"/>
-      <c r="AT21" s="591"/>
-      <c r="AU21" s="591"/>
-      <c r="AV21" s="591"/>
-      <c r="AW21" s="591"/>
-      <c r="AX21" s="591"/>
-      <c r="AY21" s="591"/>
-      <c r="AZ21" s="591"/>
-      <c r="BA21" s="591"/>
-      <c r="BB21" s="591"/>
-      <c r="BC21" s="591"/>
-      <c r="BD21" s="591"/>
-      <c r="BE21" s="591"/>
-      <c r="BF21" s="591"/>
-      <c r="BG21" s="591"/>
-    </row>
-    <row r="22" ht="70" customHeight="1" spans="1:59">
-      <c r="A22" s="577" t="inlineStr">
+      <c r="B30" s="577"/>
+      <c r="C30" s="577"/>
+      <c r="D30" s="577"/>
+      <c r="E30" s="577"/>
+      <c r="F30" s="577"/>
+      <c r="G30" s="580"/>
+      <c r="H30" s="580"/>
+      <c r="I30" s="580"/>
+      <c r="J30" s="580"/>
+      <c r="K30" s="580"/>
+      <c r="L30" s="580"/>
+      <c r="M30" s="580"/>
+      <c r="N30" s="580"/>
+      <c r="O30" s="580"/>
+      <c r="P30" s="581"/>
+      <c r="Q30" s="581"/>
+      <c r="R30" s="581"/>
+      <c r="S30" s="581"/>
+      <c r="T30" s="581"/>
+      <c r="U30" s="581"/>
+      <c r="V30" s="581"/>
+      <c r="W30" s="581"/>
+      <c r="X30" s="581"/>
+      <c r="Y30" s="577"/>
+      <c r="Z30" s="577"/>
+      <c r="AA30" s="577"/>
+      <c r="AB30" s="577"/>
+      <c r="AC30" s="577"/>
+      <c r="AD30" s="577"/>
+      <c r="AE30" s="577"/>
+      <c r="AF30" s="577"/>
+      <c r="AG30" s="577"/>
+      <c r="AH30" s="577"/>
+      <c r="AI30" s="577"/>
+      <c r="AJ30" s="577"/>
+      <c r="AK30" s="577"/>
+      <c r="AL30" s="577"/>
+      <c r="AM30" s="577"/>
+      <c r="AN30" s="577"/>
+      <c r="AO30" s="577"/>
+      <c r="AP30" s="577"/>
+      <c r="AQ30" s="577"/>
+      <c r="AR30" s="577"/>
+      <c r="AS30" s="577"/>
+      <c r="AT30" s="577"/>
+      <c r="AU30" s="577"/>
+      <c r="AV30" s="577"/>
+      <c r="AW30" s="577"/>
+      <c r="AX30" s="577"/>
+      <c r="AY30" s="577"/>
+      <c r="AZ30" s="577"/>
+      <c r="BA30" s="577"/>
+      <c r="BB30" s="577"/>
+      <c r="BC30" s="577"/>
+      <c r="BD30" s="577"/>
+      <c r="BE30" s="577"/>
+      <c r="BF30" s="577"/>
+      <c r="BG30" s="577"/>
+    </row>
+    <row r="31" ht="26" customHeight="1" spans="1:59">
+      <c r="A31" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPProfile : Implementação “Notify”</t>
+          <t xml:space="preserve">M Autenticator</t>
         </is>
       </c>
-      <c r="B22" s="579"/>
-      <c r="C22" s="579"/>
-      <c r="D22" s="578" t="inlineStr">
+      <c r="B31" s="577"/>
+      <c r="C31" s="577"/>
+      <c r="D31" s="577"/>
+      <c r="E31" s="577"/>
+      <c r="F31" s="577"/>
+      <c r="G31" s="580"/>
+      <c r="H31" s="580"/>
+      <c r="I31" s="580"/>
+      <c r="J31" s="580"/>
+      <c r="K31" s="580"/>
+      <c r="L31" s="580"/>
+      <c r="M31" s="580"/>
+      <c r="N31" s="580"/>
+      <c r="O31" s="580"/>
+      <c r="P31" s="580"/>
+      <c r="Q31" s="580"/>
+      <c r="R31" s="580"/>
+      <c r="S31" s="580"/>
+      <c r="T31" s="580"/>
+      <c r="U31" s="580"/>
+      <c r="V31" s="580"/>
+      <c r="W31" s="580"/>
+      <c r="X31" s="580"/>
+      <c r="Y31" s="577"/>
+      <c r="Z31" s="577"/>
+      <c r="AA31" s="577"/>
+      <c r="AB31" s="577"/>
+      <c r="AC31" s="577"/>
+      <c r="AD31" s="577"/>
+      <c r="AE31" s="577"/>
+      <c r="AF31" s="577"/>
+      <c r="AG31" s="577"/>
+      <c r="AH31" s="577"/>
+      <c r="AI31" s="577"/>
+      <c r="AJ31" s="577"/>
+      <c r="AK31" s="577"/>
+      <c r="AL31" s="577"/>
+      <c r="AM31" s="577"/>
+      <c r="AN31" s="577"/>
+      <c r="AO31" s="577"/>
+      <c r="AP31" s="577"/>
+      <c r="AQ31" s="577"/>
+      <c r="AR31" s="577"/>
+      <c r="AS31" s="577"/>
+      <c r="AT31" s="577"/>
+      <c r="AU31" s="577"/>
+      <c r="AV31" s="577"/>
+      <c r="AW31" s="577"/>
+      <c r="AX31" s="577"/>
+      <c r="AY31" s="577"/>
+      <c r="AZ31" s="577"/>
+      <c r="BA31" s="577"/>
+      <c r="BB31" s="577"/>
+      <c r="BC31" s="577"/>
+      <c r="BD31" s="577"/>
+      <c r="BE31" s="577"/>
+      <c r="BF31" s="577"/>
+      <c r="BG31" s="577"/>
+    </row>
+    <row r="32" ht="26" customHeight="1" spans="1:59">
+      <c r="A32" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promove ações e tarefas internas após notificação de alteração de dados criticos das Empresas</t>
+          <t xml:space="preserve">Registo e Recenseamento</t>
         </is>
       </c>
-      <c r="E22" s="579" t="inlineStr">
+      <c r="B32" s="577"/>
+      <c r="C32" s="577"/>
+      <c r="D32" s="577"/>
+      <c r="E32" s="577"/>
+      <c r="F32" s="577"/>
+      <c r="G32" s="580"/>
+      <c r="H32" s="580"/>
+      <c r="I32" s="580"/>
+      <c r="J32" s="580"/>
+      <c r="K32" s="580"/>
+      <c r="L32" s="580"/>
+      <c r="M32" s="580"/>
+      <c r="N32" s="580"/>
+      <c r="O32" s="580"/>
+      <c r="P32" s="580"/>
+      <c r="Q32" s="580"/>
+      <c r="R32" s="580"/>
+      <c r="S32" s="580"/>
+      <c r="T32" s="580"/>
+      <c r="U32" s="580"/>
+      <c r="V32" s="580"/>
+      <c r="W32" s="580"/>
+      <c r="X32" s="580"/>
+      <c r="Y32" s="577"/>
+      <c r="Z32" s="577"/>
+      <c r="AA32" s="577"/>
+      <c r="AB32" s="577"/>
+      <c r="AC32" s="577"/>
+      <c r="AD32" s="577"/>
+      <c r="AE32" s="577"/>
+      <c r="AF32" s="577"/>
+      <c r="AG32" s="577"/>
+      <c r="AH32" s="577"/>
+      <c r="AI32" s="577"/>
+      <c r="AJ32" s="577"/>
+      <c r="AK32" s="577"/>
+      <c r="AL32" s="577"/>
+      <c r="AM32" s="577"/>
+      <c r="AN32" s="577"/>
+      <c r="AO32" s="577"/>
+      <c r="AP32" s="577"/>
+      <c r="AQ32" s="577"/>
+      <c r="AR32" s="577"/>
+      <c r="AS32" s="577"/>
+      <c r="AT32" s="577"/>
+      <c r="AU32" s="577"/>
+      <c r="AV32" s="577"/>
+      <c r="AW32" s="577"/>
+      <c r="AX32" s="577"/>
+      <c r="AY32" s="577"/>
+      <c r="AZ32" s="577"/>
+      <c r="BA32" s="577"/>
+      <c r="BB32" s="577"/>
+      <c r="BC32" s="577"/>
+      <c r="BD32" s="577"/>
+      <c r="BE32" s="577"/>
+      <c r="BF32" s="577"/>
+      <c r="BG32" s="577"/>
+    </row>
+    <row r="33" ht="26" customHeight="1" spans="1:59">
+      <c r="A33" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD</t>
+          <t xml:space="preserve">Pesquisador</t>
         </is>
       </c>
-      <c r="F22" s="578" t="inlineStr">
+      <c r="B33" s="577"/>
+      <c r="C33" s="577"/>
+      <c r="D33" s="577"/>
+      <c r="E33" s="577"/>
+      <c r="F33" s="577"/>
+      <c r="G33" s="580"/>
+      <c r="H33" s="580"/>
+      <c r="I33" s="580"/>
+      <c r="J33" s="580"/>
+      <c r="K33" s="580"/>
+      <c r="L33" s="580"/>
+      <c r="M33" s="580"/>
+      <c r="N33" s="580"/>
+      <c r="O33" s="580"/>
+      <c r="P33" s="580"/>
+      <c r="Q33" s="580"/>
+      <c r="R33" s="580"/>
+      <c r="S33" s="580"/>
+      <c r="T33" s="580"/>
+      <c r="U33" s="580"/>
+      <c r="V33" s="580"/>
+      <c r="W33" s="580"/>
+      <c r="X33" s="580"/>
+      <c r="Y33" s="577"/>
+      <c r="Z33" s="577"/>
+      <c r="AA33" s="577"/>
+      <c r="AB33" s="577"/>
+      <c r="AC33" s="577"/>
+      <c r="AD33" s="577"/>
+      <c r="AE33" s="577"/>
+      <c r="AF33" s="577"/>
+      <c r="AG33" s="577"/>
+      <c r="AH33" s="577"/>
+      <c r="AI33" s="577"/>
+      <c r="AJ33" s="577"/>
+      <c r="AK33" s="577"/>
+      <c r="AL33" s="577"/>
+      <c r="AM33" s="577"/>
+      <c r="AN33" s="577"/>
+      <c r="AO33" s="577"/>
+      <c r="AP33" s="577"/>
+      <c r="AQ33" s="577"/>
+      <c r="AR33" s="577"/>
+      <c r="AS33" s="577"/>
+      <c r="AT33" s="577"/>
+      <c r="AU33" s="577"/>
+      <c r="AV33" s="577"/>
+      <c r="AW33" s="577"/>
+      <c r="AX33" s="577"/>
+      <c r="AY33" s="577"/>
+      <c r="AZ33" s="577"/>
+      <c r="BA33" s="577"/>
+      <c r="BB33" s="577"/>
+      <c r="BC33" s="577"/>
+      <c r="BD33" s="577"/>
+      <c r="BE33" s="577"/>
+      <c r="BF33" s="577"/>
+      <c r="BG33" s="577"/>
+    </row>
+    <row r="34" ht="26" customHeight="1" spans="1:59">
+      <c r="A34" s="576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Em avaliação integração com outras plataformas de gestão de dados das Empresas existente no do Banco</t>
+          <t xml:space="preserve">Nova Montra /Jornadas Meios de Recebimento</t>
         </is>
       </c>
-      <c r="G22" s="591"/>
-      <c r="H22" s="591"/>
-      <c r="I22" s="591"/>
-      <c r="J22" s="591"/>
-      <c r="K22" s="589"/>
-      <c r="L22" s="591"/>
-      <c r="M22" s="591"/>
-      <c r="N22" s="591"/>
-      <c r="O22" s="591"/>
-      <c r="P22" s="591"/>
-      <c r="Q22" s="591"/>
-      <c r="R22" s="591"/>
-      <c r="S22" s="591"/>
-      <c r="T22" s="591"/>
-      <c r="U22" s="591"/>
-      <c r="V22" s="591"/>
-      <c r="W22" s="591"/>
-      <c r="X22" s="591"/>
-      <c r="Y22" s="591"/>
-      <c r="Z22" s="591"/>
-      <c r="AA22" s="591"/>
-      <c r="AB22" s="591"/>
-      <c r="AC22" s="591"/>
-      <c r="AD22" s="591"/>
-      <c r="AE22" s="591"/>
-      <c r="AF22" s="591"/>
-      <c r="AG22" s="591"/>
-      <c r="AH22" s="591"/>
-      <c r="AI22" s="591"/>
-      <c r="AJ22" s="591"/>
-      <c r="AK22" s="591"/>
-      <c r="AL22" s="591"/>
-      <c r="AM22" s="591"/>
-      <c r="AN22" s="591"/>
-      <c r="AO22" s="591"/>
-      <c r="AP22" s="591"/>
-      <c r="AQ22" s="591"/>
-      <c r="AR22" s="591"/>
-      <c r="AS22" s="591"/>
-      <c r="AT22" s="591"/>
-      <c r="AU22" s="591"/>
-      <c r="AV22" s="591"/>
-      <c r="AW22" s="591"/>
-      <c r="AX22" s="591"/>
-      <c r="AY22" s="591"/>
-      <c r="AZ22" s="591"/>
-      <c r="BA22" s="591"/>
-      <c r="BB22" s="591"/>
-      <c r="BC22" s="591"/>
-      <c r="BD22" s="591"/>
-      <c r="BE22" s="591"/>
-      <c r="BF22" s="591"/>
-      <c r="BG22" s="591"/>
-    </row>
-    <row r="23" ht="70" customHeight="1" spans="1:59">
-      <c r="A23" s="577" t="inlineStr">
+      <c r="B34" s="577"/>
+      <c r="C34" s="577"/>
+      <c r="D34" s="577"/>
+      <c r="E34" s="577"/>
+      <c r="F34" s="577"/>
+      <c r="G34" s="577"/>
+      <c r="H34" s="577"/>
+      <c r="I34" s="577"/>
+      <c r="J34" s="577"/>
+      <c r="K34" s="577"/>
+      <c r="L34" s="577"/>
+      <c r="M34" s="577"/>
+      <c r="N34" s="577"/>
+      <c r="O34" s="577"/>
+      <c r="P34" s="577"/>
+      <c r="Q34" s="577"/>
+      <c r="R34" s="577"/>
+      <c r="S34" s="577"/>
+      <c r="T34" s="580"/>
+      <c r="U34" s="580"/>
+      <c r="V34" s="580"/>
+      <c r="W34" s="580"/>
+      <c r="X34" s="580"/>
+      <c r="Y34" s="584"/>
+      <c r="Z34" s="584"/>
+      <c r="AA34" s="584"/>
+      <c r="AB34" s="584"/>
+      <c r="AC34" s="583"/>
+      <c r="AD34" s="583"/>
+      <c r="AE34" s="583"/>
+      <c r="AF34" s="583"/>
+      <c r="AG34" s="577"/>
+      <c r="AH34" s="577"/>
+      <c r="AI34" s="577"/>
+      <c r="AJ34" s="577"/>
+      <c r="AK34" s="577"/>
+      <c r="AL34" s="577"/>
+      <c r="AM34" s="577"/>
+      <c r="AN34" s="577"/>
+      <c r="AO34" s="577"/>
+      <c r="AP34" s="577"/>
+      <c r="AQ34" s="577"/>
+      <c r="AR34" s="577"/>
+      <c r="AS34" s="577"/>
+      <c r="AT34" s="577"/>
+      <c r="AU34" s="577"/>
+      <c r="AV34" s="577"/>
+      <c r="AW34" s="577"/>
+      <c r="AX34" s="577"/>
+      <c r="AY34" s="577"/>
+      <c r="AZ34" s="577"/>
+      <c r="BA34" s="577"/>
+      <c r="BB34" s="577"/>
+      <c r="BC34" s="577"/>
+      <c r="BD34" s="577"/>
+      <c r="BE34" s="577"/>
+      <c r="BF34" s="577"/>
+      <c r="BG34" s="577"/>
+    </row>
+    <row r="35" ht="60" customHeight="1" spans="1:59">
+      <c r="A35" s="579" t="inlineStr">
         <is>
-          <t xml:space="preserve">100% Digital Account Closure</t>
+          <t xml:space="preserve">Notas: • Projetos, fases e datas reproduzidos da calendarização mensal original (sheet «Calendário IT», agora oculta), com os meses expandidos em semanas. • PO, Stakeholders, Descrição do âmbito, Data passagem a produção e Comentário/PdS ficam por preencher (sem fonte na sheet original) — a completar em coordenação com Pedro/Ivânia. • A fase «Produção» na grelha indica a passagem a produção. • Semana atual destacada a vermelho.</t>
         </is>
       </c>
-      <c r="B23" s="579"/>
-      <c r="C23" s="579"/>
-      <c r="D23" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pedido de encerramento de conta no site de Empresas</t>
-        </is>
-      </c>
-      <c r="E23" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01-07-2026</t>
-        </is>
-      </c>
-      <c r="F23" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Requisito legal – BdP
-FCA 09-03-2026: vai a QA a 12-03
-FCA 30-01-2026: Holding, DEV suspendido por priorização de atividades
-FCA 27-01-2026: Avaliar com COFF se pode aguardar
-FCA 20-01-2025: está em standby</t>
-        </is>
-      </c>
-      <c r="G23" s="591"/>
-      <c r="H23" s="591"/>
-      <c r="I23" s="591"/>
-      <c r="J23" s="591"/>
-      <c r="K23" s="591"/>
-      <c r="L23" s="591"/>
-      <c r="M23" s="591"/>
-      <c r="N23" s="591"/>
-      <c r="O23" s="591"/>
-      <c r="P23" s="591"/>
-      <c r="Q23" s="591"/>
-      <c r="R23" s="591"/>
-      <c r="S23" s="589"/>
-      <c r="T23" s="589"/>
-      <c r="U23" s="589"/>
-      <c r="V23" s="589"/>
-      <c r="W23" s="589"/>
-      <c r="X23" s="589"/>
-      <c r="Y23" s="589"/>
-      <c r="Z23" s="589"/>
-      <c r="AA23" s="589"/>
-      <c r="AB23" s="589"/>
-      <c r="AC23" s="589"/>
-      <c r="AD23" s="589"/>
-      <c r="AE23" s="589"/>
-      <c r="AF23" s="589"/>
-      <c r="AG23" s="590"/>
-      <c r="AH23" s="591"/>
-      <c r="AI23" s="591"/>
-      <c r="AJ23" s="591"/>
-      <c r="AK23" s="591"/>
-      <c r="AL23" s="591"/>
-      <c r="AM23" s="591"/>
-      <c r="AN23" s="591"/>
-      <c r="AO23" s="591"/>
-      <c r="AP23" s="591"/>
-      <c r="AQ23" s="591"/>
-      <c r="AR23" s="591"/>
-      <c r="AS23" s="591"/>
-      <c r="AT23" s="591"/>
-      <c r="AU23" s="591"/>
-      <c r="AV23" s="591"/>
-      <c r="AW23" s="591"/>
-      <c r="AX23" s="591"/>
-      <c r="AY23" s="591"/>
-      <c r="AZ23" s="591"/>
-      <c r="BA23" s="591"/>
-      <c r="BB23" s="591"/>
-      <c r="BC23" s="591"/>
-      <c r="BD23" s="591"/>
-      <c r="BE23" s="591"/>
-      <c r="BF23" s="591"/>
-      <c r="BG23" s="591"/>
-    </row>
-    <row r="24" ht="70" customHeight="1" spans="1:59">
-      <c r="A24" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Company Data Maintenance Journey – Phase 3 – Email</t>
-        </is>
-      </c>
-      <c r="B24" s="579"/>
-      <c r="C24" s="579"/>
-      <c r="D24" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jornada para Empresas com dados expirados Soc Quotas e Unipessoais  Sócios pessoas singulares 1 assinatura apenas 1 gerente</t>
-        </is>
-      </c>
-      <c r="E24" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01-12-2025</t>
-        </is>
-      </c>
-      <c r="F24" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comunicar à Rede e Clientes até 15 Dez    Retira ~20% dos casos das Sucursais Processo o WFMC em certificação pelo COM c/apoio DBDE
-FCA 20-01-2025: Subiu a PRD a 22-12-25. Sem WFMC/Envio por e-mail ao COM</t>
-        </is>
-      </c>
-      <c r="G24" s="591"/>
-      <c r="H24" s="591"/>
-      <c r="I24" s="591"/>
-      <c r="J24" s="591"/>
-      <c r="K24" s="591"/>
-      <c r="L24" s="591"/>
-      <c r="M24" s="591"/>
-      <c r="N24" s="591"/>
-      <c r="O24" s="591"/>
-      <c r="P24" s="591"/>
-      <c r="Q24" s="591"/>
-      <c r="R24" s="591"/>
-      <c r="S24" s="591"/>
-      <c r="T24" s="591"/>
-      <c r="U24" s="591"/>
-      <c r="V24" s="591"/>
-      <c r="W24" s="591"/>
-      <c r="X24" s="591"/>
-      <c r="Y24" s="591"/>
-      <c r="Z24" s="591"/>
-      <c r="AA24" s="591"/>
-      <c r="AB24" s="591"/>
-      <c r="AC24" s="591"/>
-      <c r="AD24" s="591"/>
-      <c r="AE24" s="591"/>
-      <c r="AF24" s="591"/>
-      <c r="AG24" s="591"/>
-      <c r="AH24" s="591"/>
-      <c r="AI24" s="591"/>
-      <c r="AJ24" s="591"/>
-      <c r="AK24" s="591"/>
-      <c r="AL24" s="591"/>
-      <c r="AM24" s="591"/>
-      <c r="AN24" s="591"/>
-      <c r="AO24" s="591"/>
-      <c r="AP24" s="591"/>
-      <c r="AQ24" s="591"/>
-      <c r="AR24" s="591"/>
-      <c r="AS24" s="591"/>
-      <c r="AT24" s="591"/>
-      <c r="AU24" s="591"/>
-      <c r="AV24" s="591"/>
-      <c r="AW24" s="591"/>
-      <c r="AX24" s="591"/>
-      <c r="AY24" s="591"/>
-      <c r="AZ24" s="591"/>
-      <c r="BA24" s="591"/>
-      <c r="BB24" s="589"/>
-      <c r="BC24" s="591"/>
-      <c r="BD24" s="591"/>
-      <c r="BE24" s="591"/>
-      <c r="BF24" s="591"/>
-      <c r="BG24" s="591"/>
-    </row>
-    <row r="25" ht="70" customHeight="1" spans="1:59">
-      <c r="A25" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Company Data Maintenance journey – Phase 4 – WFMC</t>
-        </is>
-      </c>
-      <c r="B25" s="579"/>
-      <c r="C25" s="579"/>
-      <c r="D25" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Melhorias e simplificação do  scope Fase 3, inclui  para 1 ou mais Gerentes, sem filtrar situação dos dados pessoais dos gerentes que intervenientes e com entrega de processo em WFMC</t>
-        </is>
-      </c>
-      <c r="E25" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abr 26</t>
-        </is>
-      </c>
-      <c r="F25" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cerca de 30% dos casos
-Assegurar processo entregue apenas no WFMC – certificação COM c/ Apoio DBDE
-Em Abr 26 - Após ter WFMC abrir solução a casos em que existam Gerentes intervneientes com dados expirados no Banco para atingir +45%</t>
-        </is>
-      </c>
-      <c r="G25" s="591"/>
-      <c r="H25" s="591"/>
-      <c r="I25" s="591"/>
-      <c r="J25" s="591"/>
-      <c r="K25" s="591"/>
-      <c r="L25" s="591"/>
-      <c r="M25" s="591"/>
-      <c r="N25" s="591"/>
-      <c r="O25" s="591"/>
-      <c r="P25" s="591"/>
-      <c r="Q25" s="591"/>
-      <c r="R25" s="591"/>
-      <c r="S25" s="589"/>
-      <c r="T25" s="590"/>
-      <c r="U25" s="591"/>
-      <c r="V25" s="591"/>
-      <c r="W25" s="591"/>
-      <c r="X25" s="591"/>
-      <c r="Y25" s="591"/>
-      <c r="Z25" s="591"/>
-      <c r="AA25" s="591"/>
-      <c r="AB25" s="591"/>
-      <c r="AC25" s="591"/>
-      <c r="AD25" s="591"/>
-      <c r="AE25" s="591"/>
-      <c r="AF25" s="591"/>
-      <c r="AG25" s="591"/>
-      <c r="AH25" s="591"/>
-      <c r="AI25" s="591"/>
-      <c r="AJ25" s="591"/>
-      <c r="AK25" s="591"/>
-      <c r="AL25" s="591"/>
-      <c r="AM25" s="591"/>
-      <c r="AN25" s="591"/>
-      <c r="AO25" s="591"/>
-      <c r="AP25" s="591"/>
-      <c r="AQ25" s="591"/>
-      <c r="AR25" s="591"/>
-      <c r="AS25" s="591"/>
-      <c r="AT25" s="591"/>
-      <c r="AU25" s="591"/>
-      <c r="AV25" s="591"/>
-      <c r="AW25" s="591"/>
-      <c r="AX25" s="591"/>
-      <c r="AY25" s="591"/>
-      <c r="AZ25" s="591"/>
-      <c r="BA25" s="591"/>
-      <c r="BB25" s="591"/>
-      <c r="BC25" s="591"/>
-      <c r="BD25" s="591"/>
-      <c r="BE25" s="591"/>
-      <c r="BF25" s="591"/>
-      <c r="BG25" s="591"/>
-    </row>
-    <row r="26" ht="70" customHeight="1" spans="1:59">
-      <c r="A26" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Customer CARE | C2C - acesso direto com chamada em contexto</t>
-        </is>
-      </c>
-      <c r="B26" s="579"/>
-      <c r="C26" s="579"/>
-      <c r="D26" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chamada á entregue na PAM/iPAC aos Operadores da linha de Apoio com Dados do Cliente e da Empresa em Contexto. Permite assegurar ao Operador que o Cliente que pede a chamada foi autenticado e identificado no login ao MSE.</t>
-        </is>
-      </c>
-      <c r="E26" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abr 26</t>
-        </is>
-      </c>
-      <c r="F26" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Disponível após login no site para todos os utilizadores
-FCA 09-03-2026: Em QA a 12-03
-FCA 18-02-2026: Definido com Fernando Cavalheiro este MVP para acompanhar a atividade SE016484 da DBD com o desnevolvimento de criação do novo serviço C2C e entrega chamada na PAM</t>
-        </is>
-      </c>
-      <c r="G26" s="591"/>
-      <c r="H26" s="591"/>
-      <c r="I26" s="591"/>
-      <c r="J26" s="591"/>
-      <c r="K26" s="591"/>
-      <c r="L26" s="591"/>
-      <c r="M26" s="591"/>
-      <c r="N26" s="591"/>
-      <c r="O26" s="591"/>
-      <c r="P26" s="591"/>
-      <c r="Q26" s="591"/>
-      <c r="R26" s="591"/>
-      <c r="S26" s="589"/>
-      <c r="T26" s="590"/>
-      <c r="U26" s="591"/>
-      <c r="V26" s="591"/>
-      <c r="W26" s="591"/>
-      <c r="X26" s="591"/>
-      <c r="Y26" s="591"/>
-      <c r="Z26" s="591"/>
-      <c r="AA26" s="591"/>
-      <c r="AB26" s="591"/>
-      <c r="AC26" s="591"/>
-      <c r="AD26" s="591"/>
-      <c r="AE26" s="591"/>
-      <c r="AF26" s="591"/>
-      <c r="AG26" s="591"/>
-      <c r="AH26" s="591"/>
-      <c r="AI26" s="591"/>
-      <c r="AJ26" s="591"/>
-      <c r="AK26" s="591"/>
-      <c r="AL26" s="591"/>
-      <c r="AM26" s="591"/>
-      <c r="AN26" s="591"/>
-      <c r="AO26" s="591"/>
-      <c r="AP26" s="591"/>
-      <c r="AQ26" s="591"/>
-      <c r="AR26" s="591"/>
-      <c r="AS26" s="591"/>
-      <c r="AT26" s="591"/>
-      <c r="AU26" s="591"/>
-      <c r="AV26" s="591"/>
-      <c r="AW26" s="591"/>
-      <c r="AX26" s="591"/>
-      <c r="AY26" s="591"/>
-      <c r="AZ26" s="591"/>
-      <c r="BA26" s="591"/>
-      <c r="BB26" s="591"/>
-      <c r="BC26" s="591"/>
-      <c r="BD26" s="591"/>
-      <c r="BE26" s="591"/>
-      <c r="BF26" s="591"/>
-      <c r="BG26" s="591"/>
-    </row>
-    <row r="27" ht="70" customHeight="1" spans="1:59">
-      <c r="A27" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crédito Avançar (50k)</t>
-        </is>
-      </c>
-      <c r="B27" s="579"/>
-      <c r="C27" s="579"/>
-      <c r="D27" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Venda remota com envio de documentos pelo iPac para assinatura digital em operações pendentes no MSE</t>
-        </is>
-      </c>
-      <c r="E27" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F27" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Depende da retirada do “Acordo de Preenchimento de Livrança” do contrato de crédito. Atenção!  GT Livrança Digital</t>
-        </is>
-      </c>
-      <c r="G27" s="591"/>
-      <c r="H27" s="591"/>
-      <c r="I27" s="591"/>
-      <c r="J27" s="591"/>
-      <c r="K27" s="591"/>
-      <c r="L27" s="591"/>
-      <c r="M27" s="591"/>
-      <c r="N27" s="591"/>
-      <c r="O27" s="591"/>
-      <c r="P27" s="591"/>
-      <c r="Q27" s="591"/>
-      <c r="R27" s="591"/>
-      <c r="S27" s="591"/>
-      <c r="T27" s="591"/>
-      <c r="U27" s="591"/>
-      <c r="V27" s="591"/>
-      <c r="W27" s="591"/>
-      <c r="X27" s="591"/>
-      <c r="Y27" s="591"/>
-      <c r="Z27" s="591"/>
-      <c r="AA27" s="591"/>
-      <c r="AB27" s="591"/>
-      <c r="AC27" s="591"/>
-      <c r="AD27" s="591"/>
-      <c r="AE27" s="591"/>
-      <c r="AF27" s="591"/>
-      <c r="AG27" s="591"/>
-      <c r="AH27" s="591"/>
-      <c r="AI27" s="591"/>
-      <c r="AJ27" s="591"/>
-      <c r="AK27" s="591"/>
-      <c r="AL27" s="591"/>
-      <c r="AM27" s="591"/>
-      <c r="AN27" s="591"/>
-      <c r="AO27" s="591"/>
-      <c r="AP27" s="591"/>
-      <c r="AQ27" s="591"/>
-      <c r="AR27" s="591"/>
-      <c r="AS27" s="591"/>
-      <c r="AT27" s="591"/>
-      <c r="AU27" s="591"/>
-      <c r="AV27" s="591"/>
-      <c r="AW27" s="591"/>
-      <c r="AX27" s="591"/>
-      <c r="AY27" s="591"/>
-      <c r="AZ27" s="591"/>
-      <c r="BA27" s="591"/>
-      <c r="BB27" s="591"/>
-      <c r="BC27" s="591"/>
-      <c r="BD27" s="591"/>
-      <c r="BE27" s="591"/>
-      <c r="BF27" s="591"/>
-      <c r="BG27" s="591"/>
-    </row>
-    <row r="28" ht="70" customHeight="1" spans="1:59">
-      <c r="A28" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Smart Moove, TPA, Cartões de Débito, Depositos Prazo e Crédito</t>
-        </is>
-      </c>
-      <c r="B28" s="579"/>
-      <c r="C28" s="579"/>
-      <c r="D28" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Venda remota com envio de documentos pelo iPac para assinatura digital em operações pendentes no MSE</t>
-        </is>
-      </c>
-      <c r="E28" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fev 26</t>
-        </is>
-      </c>
-      <c r="F28" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pronto para arrancar no go live
-FCA 09-03-2026: EM PRD
-FCA 13-02-2026: incluidos os DPs
-FCA 27-01-2026: Em certificação</t>
-        </is>
-      </c>
-      <c r="G28" s="591"/>
-      <c r="H28" s="591"/>
-      <c r="I28" s="591"/>
-      <c r="J28" s="591"/>
-      <c r="K28" s="590"/>
-      <c r="L28" s="591"/>
-      <c r="M28" s="591"/>
-      <c r="N28" s="591"/>
-      <c r="O28" s="591"/>
-      <c r="P28" s="591"/>
-      <c r="Q28" s="591"/>
-      <c r="R28" s="591"/>
-      <c r="S28" s="591"/>
-      <c r="T28" s="591"/>
-      <c r="U28" s="591"/>
-      <c r="V28" s="591"/>
-      <c r="W28" s="591"/>
-      <c r="X28" s="591"/>
-      <c r="Y28" s="591"/>
-      <c r="Z28" s="591"/>
-      <c r="AA28" s="591"/>
-      <c r="AB28" s="591"/>
-      <c r="AC28" s="591"/>
-      <c r="AD28" s="591"/>
-      <c r="AE28" s="591"/>
-      <c r="AF28" s="591"/>
-      <c r="AG28" s="591"/>
-      <c r="AH28" s="591"/>
-      <c r="AI28" s="591"/>
-      <c r="AJ28" s="591"/>
-      <c r="AK28" s="591"/>
-      <c r="AL28" s="591"/>
-      <c r="AM28" s="591"/>
-      <c r="AN28" s="591"/>
-      <c r="AO28" s="591"/>
-      <c r="AP28" s="591"/>
-      <c r="AQ28" s="591"/>
-      <c r="AR28" s="591"/>
-      <c r="AS28" s="591"/>
-      <c r="AT28" s="591"/>
-      <c r="AU28" s="591"/>
-      <c r="AV28" s="591"/>
-      <c r="AW28" s="591"/>
-      <c r="AX28" s="591"/>
-      <c r="AY28" s="591"/>
-      <c r="AZ28" s="591"/>
-      <c r="BA28" s="591"/>
-      <c r="BB28" s="591"/>
-      <c r="BC28" s="591"/>
-      <c r="BD28" s="591"/>
-      <c r="BE28" s="591"/>
-      <c r="BF28" s="591"/>
-      <c r="BG28" s="591"/>
-    </row>
-    <row r="29" ht="70" customHeight="1" spans="1:59">
-      <c r="A29" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seguros (BNL 2.0)</t>
-        </is>
-      </c>
-      <c r="B29" s="579"/>
-      <c r="C29" s="579"/>
-      <c r="D29" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Venda remota com envio de documentos pelo iPac para assinatura digital em operações pendentes no MSE</t>
-        </is>
-      </c>
-      <c r="E29" s="579"/>
-      <c r="F29" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FCA 09-03-2026: EM PRD
-FCA 30-01-2026: go live com testes ao msm tempo dos produtos bancários. Certificação concluida até Mar 26
-FCA 27-01-2026: Aguadar entrega serviços da AGEAS</t>
-        </is>
-      </c>
-      <c r="G29" s="591"/>
-      <c r="H29" s="591"/>
-      <c r="I29" s="591"/>
-      <c r="J29" s="591"/>
-      <c r="K29" s="591"/>
-      <c r="L29" s="591"/>
-      <c r="M29" s="591"/>
-      <c r="N29" s="591"/>
-      <c r="O29" s="591"/>
-      <c r="P29" s="591"/>
-      <c r="Q29" s="591"/>
-      <c r="R29" s="591"/>
-      <c r="S29" s="591"/>
-      <c r="T29" s="591"/>
-      <c r="U29" s="591"/>
-      <c r="V29" s="591"/>
-      <c r="W29" s="591"/>
-      <c r="X29" s="591"/>
-      <c r="Y29" s="591"/>
-      <c r="Z29" s="591"/>
-      <c r="AA29" s="591"/>
-      <c r="AB29" s="591"/>
-      <c r="AC29" s="591"/>
-      <c r="AD29" s="591"/>
-      <c r="AE29" s="591"/>
-      <c r="AF29" s="591"/>
-      <c r="AG29" s="591"/>
-      <c r="AH29" s="591"/>
-      <c r="AI29" s="591"/>
-      <c r="AJ29" s="591"/>
-      <c r="AK29" s="591"/>
-      <c r="AL29" s="591"/>
-      <c r="AM29" s="591"/>
-      <c r="AN29" s="591"/>
-      <c r="AO29" s="591"/>
-      <c r="AP29" s="591"/>
-      <c r="AQ29" s="591"/>
-      <c r="AR29" s="591"/>
-      <c r="AS29" s="591"/>
-      <c r="AT29" s="591"/>
-      <c r="AU29" s="591"/>
-      <c r="AV29" s="591"/>
-      <c r="AW29" s="591"/>
-      <c r="AX29" s="591"/>
-      <c r="AY29" s="591"/>
-      <c r="AZ29" s="591"/>
-      <c r="BA29" s="591"/>
-      <c r="BB29" s="591"/>
-      <c r="BC29" s="591"/>
-      <c r="BD29" s="591"/>
-      <c r="BE29" s="591"/>
-      <c r="BF29" s="591"/>
-      <c r="BG29" s="591"/>
-    </row>
-    <row r="30" ht="70" customHeight="1" spans="1:59">
-      <c r="A30" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New website onboarding for All Clients</t>
-        </is>
-      </c>
-      <c r="B30" s="579"/>
-      <c r="C30" s="579"/>
-      <c r="D30" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Novo processo de registo inicial da Empresa e recenseamento de utilizadores no site de Empresas</t>
-        </is>
-      </c>
-      <c r="E30" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F30" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Revamp do Registo e Recenseamento para Clientes e Não Clientes - reaproveita processo fornecedores Confirming. Em fase de levantamento de requisitos</t>
-        </is>
-      </c>
-      <c r="G30" s="591"/>
-      <c r="H30" s="591"/>
-      <c r="I30" s="591"/>
-      <c r="J30" s="591"/>
-      <c r="K30" s="591"/>
-      <c r="L30" s="591"/>
-      <c r="M30" s="591"/>
-      <c r="N30" s="591"/>
-      <c r="O30" s="591"/>
-      <c r="P30" s="591"/>
-      <c r="Q30" s="591"/>
-      <c r="R30" s="591"/>
-      <c r="S30" s="591"/>
-      <c r="T30" s="591"/>
-      <c r="U30" s="591"/>
-      <c r="V30" s="591"/>
-      <c r="W30" s="591"/>
-      <c r="X30" s="591"/>
-      <c r="Y30" s="591"/>
-      <c r="Z30" s="591"/>
-      <c r="AA30" s="591"/>
-      <c r="AB30" s="591"/>
-      <c r="AC30" s="591"/>
-      <c r="AD30" s="591"/>
-      <c r="AE30" s="591"/>
-      <c r="AF30" s="591"/>
-      <c r="AG30" s="591"/>
-      <c r="AH30" s="591"/>
-      <c r="AI30" s="591"/>
-      <c r="AJ30" s="591"/>
-      <c r="AK30" s="591"/>
-      <c r="AL30" s="591"/>
-      <c r="AM30" s="591"/>
-      <c r="AN30" s="591"/>
-      <c r="AO30" s="591"/>
-      <c r="AP30" s="591"/>
-      <c r="AQ30" s="591"/>
-      <c r="AR30" s="591"/>
-      <c r="AS30" s="591"/>
-      <c r="AT30" s="591"/>
-      <c r="AU30" s="591"/>
-      <c r="AV30" s="591"/>
-      <c r="AW30" s="591"/>
-      <c r="AX30" s="591"/>
-      <c r="AY30" s="591"/>
-      <c r="AZ30" s="591"/>
-      <c r="BA30" s="591"/>
-      <c r="BB30" s="591"/>
-      <c r="BC30" s="591"/>
-      <c r="BD30" s="591"/>
-      <c r="BE30" s="591"/>
-      <c r="BF30" s="591"/>
-      <c r="BG30" s="591"/>
-    </row>
-    <row r="31" ht="70" customHeight="1" spans="1:59">
-      <c r="A31" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Customer CARE | Revamp</t>
-        </is>
-      </c>
-      <c r="B31" s="579"/>
-      <c r="C31" s="579"/>
-      <c r="D31" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Apoio ao Cliente com FAQ´s geradas com o GenAI antes do Contacto com o Banco</t>
-        </is>
-      </c>
-      <c r="E31" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Set 26</t>
-        </is>
-      </c>
-      <c r="F31" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WIP – Projeto em Azure: entrega em Dez
-FCA 13-02-2026: Calendarizado com AFA QA em Jun e PRD em Set
-FCA 27-01-2026: Quick WIN caiu. Arranca com C2C. Em especificação Azure e aguarda serviço C2C pela DBD
-FCA 20-01-2026: requer prioirzação no Labb e no IT</t>
-        </is>
-      </c>
-      <c r="G31" s="591"/>
-      <c r="H31" s="591"/>
-      <c r="I31" s="591"/>
-      <c r="J31" s="591"/>
-      <c r="K31" s="591"/>
-      <c r="L31" s="591"/>
-      <c r="M31" s="591"/>
-      <c r="N31" s="591"/>
-      <c r="O31" s="591"/>
-      <c r="P31" s="591"/>
-      <c r="Q31" s="591"/>
-      <c r="R31" s="591"/>
-      <c r="S31" s="591"/>
-      <c r="T31" s="591"/>
-      <c r="U31" s="591"/>
-      <c r="V31" s="591"/>
-      <c r="W31" s="591"/>
-      <c r="X31" s="591"/>
-      <c r="Y31" s="591"/>
-      <c r="Z31" s="591"/>
-      <c r="AA31" s="591"/>
-      <c r="AB31" s="591"/>
-      <c r="AC31" s="591"/>
-      <c r="AD31" s="591"/>
-      <c r="AE31" s="591"/>
-      <c r="AF31" s="589"/>
-      <c r="AG31" s="589"/>
-      <c r="AH31" s="589"/>
-      <c r="AI31" s="589"/>
-      <c r="AJ31" s="589"/>
-      <c r="AK31" s="589"/>
-      <c r="AL31" s="589"/>
-      <c r="AM31" s="589"/>
-      <c r="AN31" s="589"/>
-      <c r="AO31" s="589"/>
-      <c r="AP31" s="590"/>
-      <c r="AQ31" s="591"/>
-      <c r="AR31" s="591"/>
-      <c r="AS31" s="591"/>
-      <c r="AT31" s="591"/>
-      <c r="AU31" s="591"/>
-      <c r="AV31" s="591"/>
-      <c r="AW31" s="591"/>
-      <c r="AX31" s="591"/>
-      <c r="AY31" s="591"/>
-      <c r="AZ31" s="591"/>
-      <c r="BA31" s="591"/>
-      <c r="BB31" s="591"/>
-      <c r="BC31" s="591"/>
-      <c r="BD31" s="591"/>
-      <c r="BE31" s="591"/>
-      <c r="BF31" s="591"/>
-      <c r="BG31" s="591"/>
-    </row>
-    <row r="32" ht="70" customHeight="1" spans="1:59">
-      <c r="A32" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital Middle Office (MVP)</t>
-        </is>
-      </c>
-      <c r="B32" s="579"/>
-      <c r="C32" s="579"/>
-      <c r="D32" s="578"/>
-      <c r="E32" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26-06-2026</t>
-        </is>
-      </c>
-      <c r="F32" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scope em conclusão: DTO/DBDE
-FCA 20-01-2026: WIP com DTO</t>
-        </is>
-      </c>
-      <c r="G32" s="591"/>
-      <c r="H32" s="591"/>
-      <c r="I32" s="591"/>
-      <c r="J32" s="591"/>
-      <c r="K32" s="591"/>
-      <c r="L32" s="591"/>
-      <c r="M32" s="591"/>
-      <c r="N32" s="591"/>
-      <c r="O32" s="591"/>
-      <c r="P32" s="591"/>
-      <c r="Q32" s="591"/>
-      <c r="R32" s="591"/>
-      <c r="S32" s="591"/>
-      <c r="T32" s="591"/>
-      <c r="U32" s="591"/>
-      <c r="V32" s="591"/>
-      <c r="W32" s="591"/>
-      <c r="X32" s="591"/>
-      <c r="Y32" s="591"/>
-      <c r="Z32" s="591"/>
-      <c r="AA32" s="591"/>
-      <c r="AB32" s="591"/>
-      <c r="AC32" s="591"/>
-      <c r="AD32" s="591"/>
-      <c r="AE32" s="591"/>
-      <c r="AF32" s="590"/>
-      <c r="AG32" s="591"/>
-      <c r="AH32" s="591"/>
-      <c r="AI32" s="591"/>
-      <c r="AJ32" s="591"/>
-      <c r="AK32" s="591"/>
-      <c r="AL32" s="591"/>
-      <c r="AM32" s="591"/>
-      <c r="AN32" s="591"/>
-      <c r="AO32" s="591"/>
-      <c r="AP32" s="591"/>
-      <c r="AQ32" s="591"/>
-      <c r="AR32" s="591"/>
-      <c r="AS32" s="591"/>
-      <c r="AT32" s="591"/>
-      <c r="AU32" s="591"/>
-      <c r="AV32" s="591"/>
-      <c r="AW32" s="591"/>
-      <c r="AX32" s="591"/>
-      <c r="AY32" s="591"/>
-      <c r="AZ32" s="591"/>
-      <c r="BA32" s="591"/>
-      <c r="BB32" s="591"/>
-      <c r="BC32" s="591"/>
-      <c r="BD32" s="591"/>
-      <c r="BE32" s="591"/>
-      <c r="BF32" s="591"/>
-      <c r="BG32" s="591"/>
-    </row>
-    <row r="33" ht="70" customHeight="1" spans="1:59">
-      <c r="A33" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital Middle Office (MVP 2)</t>
-        </is>
-      </c>
-      <c r="B33" s="579"/>
-      <c r="C33" s="579"/>
-      <c r="D33" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Novas funcionalidades</t>
-        </is>
-      </c>
-      <c r="E33" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F33" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por definir</t>
-        </is>
-      </c>
-      <c r="G33" s="591"/>
-      <c r="H33" s="591"/>
-      <c r="I33" s="591"/>
-      <c r="J33" s="591"/>
-      <c r="K33" s="591"/>
-      <c r="L33" s="591"/>
-      <c r="M33" s="591"/>
-      <c r="N33" s="591"/>
-      <c r="O33" s="591"/>
-      <c r="P33" s="591"/>
-      <c r="Q33" s="591"/>
-      <c r="R33" s="591"/>
-      <c r="S33" s="591"/>
-      <c r="T33" s="591"/>
-      <c r="U33" s="591"/>
-      <c r="V33" s="591"/>
-      <c r="W33" s="591"/>
-      <c r="X33" s="591"/>
-      <c r="Y33" s="591"/>
-      <c r="Z33" s="591"/>
-      <c r="AA33" s="591"/>
-      <c r="AB33" s="591"/>
-      <c r="AC33" s="591"/>
-      <c r="AD33" s="591"/>
-      <c r="AE33" s="591"/>
-      <c r="AF33" s="591"/>
-      <c r="AG33" s="591"/>
-      <c r="AH33" s="591"/>
-      <c r="AI33" s="591"/>
-      <c r="AJ33" s="591"/>
-      <c r="AK33" s="591"/>
-      <c r="AL33" s="591"/>
-      <c r="AM33" s="591"/>
-      <c r="AN33" s="591"/>
-      <c r="AO33" s="591"/>
-      <c r="AP33" s="591"/>
-      <c r="AQ33" s="591"/>
-      <c r="AR33" s="591"/>
-      <c r="AS33" s="591"/>
-      <c r="AT33" s="591"/>
-      <c r="AU33" s="591"/>
-      <c r="AV33" s="591"/>
-      <c r="AW33" s="591"/>
-      <c r="AX33" s="591"/>
-      <c r="AY33" s="591"/>
-      <c r="AZ33" s="591"/>
-      <c r="BA33" s="591"/>
-      <c r="BB33" s="591"/>
-      <c r="BC33" s="591"/>
-      <c r="BD33" s="591"/>
-      <c r="BE33" s="591"/>
-      <c r="BF33" s="591"/>
-      <c r="BG33" s="591"/>
-    </row>
-    <row r="34" ht="70" customHeight="1" spans="1:59">
-      <c r="A34" s="580" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Utilizadores - Gestão e novos recenseamentos</t>
-        </is>
-      </c>
-      <c r="B34" s="582"/>
-      <c r="C34" s="582"/>
-      <c r="D34" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Revamp e upgerade da gestão de utilizadores após login no MSE</t>
-        </is>
-      </c>
-      <c r="E34" s="582" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F34" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FCA 27-01-2026: Shapping e Conceito por fechar com equipa do Site. Alocar Nuno Belo após</t>
-        </is>
-      </c>
-      <c r="G34" s="582"/>
-      <c r="H34" s="582"/>
-      <c r="I34" s="582"/>
-      <c r="J34" s="582"/>
-      <c r="K34" s="582"/>
-      <c r="L34" s="582"/>
-      <c r="M34" s="582"/>
-      <c r="N34" s="582"/>
-      <c r="O34" s="582"/>
-      <c r="P34" s="582"/>
-      <c r="Q34" s="582"/>
-      <c r="R34" s="582"/>
-      <c r="S34" s="582"/>
-      <c r="T34" s="582"/>
-      <c r="U34" s="582"/>
-      <c r="V34" s="582"/>
-      <c r="W34" s="582"/>
-      <c r="X34" s="582"/>
-      <c r="Y34" s="582"/>
-      <c r="Z34" s="582"/>
-      <c r="AA34" s="582"/>
-      <c r="AB34" s="582"/>
-      <c r="AC34" s="582"/>
-      <c r="AD34" s="582"/>
-      <c r="AE34" s="582"/>
-      <c r="AF34" s="582"/>
-      <c r="AG34" s="582"/>
-      <c r="AH34" s="582"/>
-      <c r="AI34" s="582"/>
-      <c r="AJ34" s="582"/>
-      <c r="AK34" s="582"/>
-      <c r="AL34" s="582"/>
-      <c r="AM34" s="582"/>
-      <c r="AN34" s="582"/>
-      <c r="AO34" s="582"/>
-      <c r="AP34" s="582"/>
-      <c r="AQ34" s="582"/>
-      <c r="AR34" s="582"/>
-      <c r="AS34" s="582"/>
-      <c r="AT34" s="582"/>
-      <c r="AU34" s="582"/>
-      <c r="AV34" s="582"/>
-      <c r="AW34" s="582"/>
-      <c r="AX34" s="582"/>
-      <c r="AY34" s="582"/>
-      <c r="AZ34" s="582"/>
-      <c r="BA34" s="582"/>
-      <c r="BB34" s="582"/>
-      <c r="BC34" s="582"/>
-      <c r="BD34" s="582"/>
-      <c r="BE34" s="582"/>
-      <c r="BF34" s="582"/>
-      <c r="BG34" s="582"/>
-    </row>
-    <row r="35" ht="70" customHeight="1" spans="1:59">
-      <c r="A35" s="580" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Registo completo no site -Face lift / upgrade</t>
-        </is>
-      </c>
-      <c r="B35" s="582"/>
-      <c r="C35" s="582"/>
-      <c r="D35" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Face lift da jornada de registo completo no Site de Empresas com inclusão de melhorias nomeadamente utilização do COMPPROFILE para obtenção dos dados da Empesa</t>
-        </is>
-      </c>
-      <c r="E35" s="582" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F35" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FCA 27-01-2026: Shapping e Conceito por fechar com equipa do Site. Alocar Nuno Belo após</t>
-        </is>
-      </c>
-      <c r="G35" s="582"/>
-      <c r="H35" s="582"/>
-      <c r="I35" s="582"/>
-      <c r="J35" s="582"/>
-      <c r="K35" s="582"/>
-      <c r="L35" s="582"/>
-      <c r="M35" s="582"/>
-      <c r="N35" s="582"/>
-      <c r="O35" s="582"/>
-      <c r="P35" s="582"/>
-      <c r="Q35" s="582"/>
-      <c r="R35" s="582"/>
-      <c r="S35" s="582"/>
-      <c r="T35" s="582"/>
-      <c r="U35" s="582"/>
-      <c r="V35" s="582"/>
-      <c r="W35" s="582"/>
-      <c r="X35" s="582"/>
-      <c r="Y35" s="582"/>
-      <c r="Z35" s="582"/>
-      <c r="AA35" s="582"/>
-      <c r="AB35" s="582"/>
-      <c r="AC35" s="582"/>
-      <c r="AD35" s="582"/>
-      <c r="AE35" s="582"/>
-      <c r="AF35" s="582"/>
-      <c r="AG35" s="582"/>
-      <c r="AH35" s="582"/>
-      <c r="AI35" s="582"/>
-      <c r="AJ35" s="582"/>
-      <c r="AK35" s="582"/>
-      <c r="AL35" s="582"/>
-      <c r="AM35" s="582"/>
-      <c r="AN35" s="582"/>
-      <c r="AO35" s="582"/>
-      <c r="AP35" s="582"/>
-      <c r="AQ35" s="582"/>
-      <c r="AR35" s="582"/>
-      <c r="AS35" s="582"/>
-      <c r="AT35" s="582"/>
-      <c r="AU35" s="582"/>
-      <c r="AV35" s="582"/>
-      <c r="AW35" s="582"/>
-      <c r="AX35" s="582"/>
-      <c r="AY35" s="582"/>
-      <c r="AZ35" s="582"/>
-      <c r="BA35" s="582"/>
-      <c r="BB35" s="582"/>
-      <c r="BC35" s="582"/>
-      <c r="BD35" s="582"/>
-      <c r="BE35" s="582"/>
-      <c r="BF35" s="582"/>
-      <c r="BG35" s="582"/>
-    </row>
-    <row r="36" ht="70" customHeight="1" spans="1:59">
-      <c r="A36" s="580" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Company Data Maintenance Journey – Phase 5</t>
-        </is>
-      </c>
-      <c r="B36" s="582"/>
-      <c r="C36" s="582"/>
-      <c r="D36" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Use case da Fase 4 + atualização de dados pessoais para todos os Gerentes intervenientes nas contas da Empresas</t>
-        </is>
-      </c>
-      <c r="E36" s="582"/>
-      <c r="F36" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Implica fluxo de atualização de dados pessoais dos Gerentes intervenientes nas contas (FIC P) ~60% coverage of uses cases
-FCA 20-01-2026: Retirqar do Back Log?? Faz sentido fase 5? Ou basta ter info/alarmistica a encaminhar Gerentes para atualização de dados na APP Particulares ou na Sucursal</t>
-        </is>
-      </c>
-      <c r="G36" s="582"/>
-      <c r="H36" s="582"/>
-      <c r="I36" s="582"/>
-      <c r="J36" s="582"/>
-      <c r="K36" s="582"/>
-      <c r="L36" s="582"/>
-      <c r="M36" s="582"/>
-      <c r="N36" s="582"/>
-      <c r="O36" s="582"/>
-      <c r="P36" s="582"/>
-      <c r="Q36" s="582"/>
-      <c r="R36" s="582"/>
-      <c r="S36" s="582"/>
-      <c r="T36" s="582"/>
-      <c r="U36" s="582"/>
-      <c r="V36" s="582"/>
-      <c r="W36" s="582"/>
-      <c r="X36" s="582"/>
-      <c r="Y36" s="582"/>
-      <c r="Z36" s="582"/>
-      <c r="AA36" s="582"/>
-      <c r="AB36" s="582"/>
-      <c r="AC36" s="582"/>
-      <c r="AD36" s="582"/>
-      <c r="AE36" s="582"/>
-      <c r="AF36" s="582"/>
-      <c r="AG36" s="582"/>
-      <c r="AH36" s="582"/>
-      <c r="AI36" s="582"/>
-      <c r="AJ36" s="582"/>
-      <c r="AK36" s="582"/>
-      <c r="AL36" s="582"/>
-      <c r="AM36" s="582"/>
-      <c r="AN36" s="582"/>
-      <c r="AO36" s="582"/>
-      <c r="AP36" s="582"/>
-      <c r="AQ36" s="582"/>
-      <c r="AR36" s="582"/>
-      <c r="AS36" s="582"/>
-      <c r="AT36" s="582"/>
-      <c r="AU36" s="582"/>
-      <c r="AV36" s="582"/>
-      <c r="AW36" s="582"/>
-      <c r="AX36" s="582"/>
-      <c r="AY36" s="582"/>
-      <c r="AZ36" s="582"/>
-      <c r="BA36" s="582"/>
-      <c r="BB36" s="582"/>
-      <c r="BC36" s="582"/>
-      <c r="BD36" s="582"/>
-      <c r="BE36" s="582"/>
-      <c r="BF36" s="582"/>
-      <c r="BG36" s="582"/>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:59">
-      <c r="A37" s="576" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Payments Lab   (3 projetos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="70" customHeight="1" spans="1:59">
-      <c r="A38" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Debit Card Request</t>
-        </is>
-      </c>
-      <c r="B38" s="579"/>
-      <c r="C38" s="579"/>
-      <c r="D38" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jornada de aquisição de cartão de débito (E2E)</t>
-        </is>
-      </c>
-      <c r="E38" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abr 26</t>
-        </is>
-      </c>
-      <c r="F38" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atraso por realocação de recursos para Transferências imediatas e moratorias</t>
-        </is>
-      </c>
-      <c r="G38" s="591"/>
-      <c r="H38" s="591"/>
-      <c r="I38" s="591"/>
-      <c r="J38" s="591"/>
-      <c r="K38" s="591"/>
-      <c r="L38" s="591"/>
-      <c r="M38" s="591"/>
-      <c r="N38" s="591"/>
-      <c r="O38" s="591"/>
-      <c r="P38" s="591"/>
-      <c r="Q38" s="591"/>
-      <c r="R38" s="591"/>
-      <c r="S38" s="589"/>
-      <c r="T38" s="590"/>
-      <c r="U38" s="591"/>
-      <c r="V38" s="591"/>
-      <c r="W38" s="591"/>
-      <c r="X38" s="591"/>
-      <c r="Y38" s="591"/>
-      <c r="Z38" s="591"/>
-      <c r="AA38" s="591"/>
-      <c r="AB38" s="591"/>
-      <c r="AC38" s="591"/>
-      <c r="AD38" s="591"/>
-      <c r="AE38" s="591"/>
-      <c r="AF38" s="591"/>
-      <c r="AG38" s="591"/>
-      <c r="AH38" s="591"/>
-      <c r="AI38" s="591"/>
-      <c r="AJ38" s="591"/>
-      <c r="AK38" s="591"/>
-      <c r="AL38" s="591"/>
-      <c r="AM38" s="591"/>
-      <c r="AN38" s="591"/>
-      <c r="AO38" s="591"/>
-      <c r="AP38" s="591"/>
-      <c r="AQ38" s="591"/>
-      <c r="AR38" s="591"/>
-      <c r="AS38" s="591"/>
-      <c r="AT38" s="591"/>
-      <c r="AU38" s="591"/>
-      <c r="AV38" s="591"/>
-      <c r="AW38" s="591"/>
-      <c r="AX38" s="591"/>
-      <c r="AY38" s="591"/>
-      <c r="AZ38" s="591"/>
-      <c r="BA38" s="591"/>
-      <c r="BB38" s="591"/>
-      <c r="BC38" s="591"/>
-      <c r="BD38" s="591"/>
-      <c r="BE38" s="591"/>
-      <c r="BF38" s="591"/>
-      <c r="BG38" s="591"/>
-    </row>
-    <row r="39" ht="70" customHeight="1" spans="1:59">
-      <c r="A39" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New Pay-By Millennium</t>
-        </is>
-      </c>
-      <c r="B39" s="579"/>
-      <c r="C39" s="579"/>
-      <c r="D39" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Serviço de emissão de pedidos de pagamento</t>
-        </is>
-      </c>
-      <c r="E39" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26-06-2026</t>
-        </is>
-      </c>
-      <c r="F39" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Versão simplificada – apenas com Entidade Ref MB para testar conceito e time-to-market. A incluir no Contrato Único de Acquiring Digital</t>
-        </is>
-      </c>
-      <c r="G39" s="591"/>
-      <c r="H39" s="591"/>
-      <c r="I39" s="591"/>
-      <c r="J39" s="591"/>
-      <c r="K39" s="591"/>
-      <c r="L39" s="591"/>
-      <c r="M39" s="591"/>
-      <c r="N39" s="591"/>
-      <c r="O39" s="591"/>
-      <c r="P39" s="591"/>
-      <c r="Q39" s="591"/>
-      <c r="R39" s="591"/>
-      <c r="S39" s="591"/>
-      <c r="T39" s="589"/>
-      <c r="U39" s="589"/>
-      <c r="V39" s="589"/>
-      <c r="W39" s="589"/>
-      <c r="X39" s="589"/>
-      <c r="Y39" s="589"/>
-      <c r="Z39" s="589"/>
-      <c r="AA39" s="589"/>
-      <c r="AB39" s="589"/>
-      <c r="AC39" s="589"/>
-      <c r="AD39" s="589"/>
-      <c r="AE39" s="589"/>
-      <c r="AF39" s="590"/>
-      <c r="AG39" s="591"/>
-      <c r="AH39" s="591"/>
-      <c r="AI39" s="591"/>
-      <c r="AJ39" s="591"/>
-      <c r="AK39" s="591"/>
-      <c r="AL39" s="591"/>
-      <c r="AM39" s="591"/>
-      <c r="AN39" s="591"/>
-      <c r="AO39" s="591"/>
-      <c r="AP39" s="591"/>
-      <c r="AQ39" s="591"/>
-      <c r="AR39" s="591"/>
-      <c r="AS39" s="591"/>
-      <c r="AT39" s="591"/>
-      <c r="AU39" s="591"/>
-      <c r="AV39" s="591"/>
-      <c r="AW39" s="591"/>
-      <c r="AX39" s="591"/>
-      <c r="AY39" s="591"/>
-      <c r="AZ39" s="591"/>
-      <c r="BA39" s="591"/>
-      <c r="BB39" s="591"/>
-      <c r="BC39" s="591"/>
-      <c r="BD39" s="591"/>
-      <c r="BE39" s="591"/>
-      <c r="BF39" s="591"/>
-      <c r="BG39" s="591"/>
-    </row>
-    <row r="40" ht="70" customHeight="1" spans="1:59">
-      <c r="A40" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full Cards Servicing</t>
-        </is>
-      </c>
-      <c r="B40" s="579"/>
-      <c r="C40" s="579"/>
-      <c r="D40" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gestão da carteira de cartões para as Empresa: Consulta de saldos, movimentos e extratos,  carregamento (pré-pagos), cancelamento, e substituição de cartão</t>
-        </is>
-      </c>
-      <c r="E40" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26-07-2026</t>
-        </is>
-      </c>
-      <c r="F40" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A ausência de serviço pós-venda nos cartões tem sido referida frequentemente por Clientes e Sucursais (ex. M Refeição)</t>
-        </is>
-      </c>
-      <c r="G40" s="591"/>
-      <c r="H40" s="591"/>
-      <c r="I40" s="591"/>
-      <c r="J40" s="591"/>
-      <c r="K40" s="591"/>
-      <c r="L40" s="591"/>
-      <c r="M40" s="591"/>
-      <c r="N40" s="591"/>
-      <c r="O40" s="591"/>
-      <c r="P40" s="591"/>
-      <c r="Q40" s="591"/>
-      <c r="R40" s="591"/>
-      <c r="S40" s="591"/>
-      <c r="T40" s="591"/>
-      <c r="U40" s="591"/>
-      <c r="V40" s="591"/>
-      <c r="W40" s="591"/>
-      <c r="X40" s="591"/>
-      <c r="Y40" s="591"/>
-      <c r="Z40" s="591"/>
-      <c r="AA40" s="591"/>
-      <c r="AB40" s="591"/>
-      <c r="AC40" s="591"/>
-      <c r="AD40" s="591"/>
-      <c r="AE40" s="591"/>
-      <c r="AF40" s="589"/>
-      <c r="AG40" s="589"/>
-      <c r="AH40" s="589"/>
-      <c r="AI40" s="589"/>
-      <c r="AJ40" s="590"/>
-      <c r="AK40" s="591"/>
-      <c r="AL40" s="591"/>
-      <c r="AM40" s="591"/>
-      <c r="AN40" s="591"/>
-      <c r="AO40" s="591"/>
-      <c r="AP40" s="591"/>
-      <c r="AQ40" s="591"/>
-      <c r="AR40" s="591"/>
-      <c r="AS40" s="591"/>
-      <c r="AT40" s="591"/>
-      <c r="AU40" s="591"/>
-      <c r="AV40" s="591"/>
-      <c r="AW40" s="591"/>
-      <c r="AX40" s="591"/>
-      <c r="AY40" s="591"/>
-      <c r="AZ40" s="591"/>
-      <c r="BA40" s="591"/>
-      <c r="BB40" s="591"/>
-      <c r="BC40" s="591"/>
-      <c r="BD40" s="591"/>
-      <c r="BE40" s="591"/>
-      <c r="BF40" s="591"/>
-      <c r="BG40" s="591"/>
-    </row>
-    <row r="41" ht="20" customHeight="1" spans="1:59">
-      <c r="A41" s="576" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Best Site Lab   (4 projetos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="70" customHeight="1" spans="1:59">
-      <c r="A42" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CMBO – Content Management BackOffice</t>
-        </is>
-      </c>
-      <c r="B42" s="579"/>
-      <c r="C42" s="579"/>
-      <c r="D42" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Migração de conteúdos de Sharepoint c/ descontinuação da Plataforma SP</t>
-        </is>
-      </c>
-      <c r="E42" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26-06-2026</t>
-        </is>
-      </c>
-      <c r="F42" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EN – Produção: Jun.26 ; PT - Producao Set 26 ; ES Producao Dez 26</t>
-        </is>
-      </c>
-      <c r="G42" s="591"/>
-      <c r="H42" s="591"/>
-      <c r="I42" s="591"/>
-      <c r="J42" s="591"/>
-      <c r="K42" s="591"/>
-      <c r="L42" s="591"/>
-      <c r="M42" s="591"/>
-      <c r="N42" s="591"/>
-      <c r="O42" s="591"/>
-      <c r="P42" s="591"/>
-      <c r="Q42" s="591"/>
-      <c r="R42" s="591"/>
-      <c r="S42" s="591"/>
-      <c r="T42" s="591"/>
-      <c r="U42" s="591"/>
-      <c r="V42" s="591"/>
-      <c r="W42" s="591"/>
-      <c r="X42" s="591"/>
-      <c r="Y42" s="591"/>
-      <c r="Z42" s="591"/>
-      <c r="AA42" s="591"/>
-      <c r="AB42" s="591"/>
-      <c r="AC42" s="591"/>
-      <c r="AD42" s="591"/>
-      <c r="AE42" s="591"/>
-      <c r="AF42" s="590"/>
-      <c r="AG42" s="591"/>
-      <c r="AH42" s="591"/>
-      <c r="AI42" s="591"/>
-      <c r="AJ42" s="591"/>
-      <c r="AK42" s="591"/>
-      <c r="AL42" s="591"/>
-      <c r="AM42" s="591"/>
-      <c r="AN42" s="591"/>
-      <c r="AO42" s="591"/>
-      <c r="AP42" s="591"/>
-      <c r="AQ42" s="591"/>
-      <c r="AR42" s="591"/>
-      <c r="AS42" s="591"/>
-      <c r="AT42" s="591"/>
-      <c r="AU42" s="591"/>
-      <c r="AV42" s="591"/>
-      <c r="AW42" s="591"/>
-      <c r="AX42" s="591"/>
-      <c r="AY42" s="591"/>
-      <c r="AZ42" s="591"/>
-      <c r="BA42" s="591"/>
-      <c r="BB42" s="591"/>
-      <c r="BC42" s="591"/>
-      <c r="BD42" s="591"/>
-      <c r="BE42" s="591"/>
-      <c r="BF42" s="589"/>
-      <c r="BG42" s="591"/>
-    </row>
-    <row r="43" ht="70" customHeight="1" spans="1:59">
-      <c r="A43" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M-Authenticator – Digital Certificate Alternative</t>
-        </is>
-      </c>
-      <c r="B43" s="579"/>
-      <c r="C43" s="579"/>
-      <c r="D43" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">APP de autenticação forte</t>
-        </is>
-      </c>
-      <c r="E43" s="579"/>
-      <c r="F43" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Em fase de levantamento de requisitos</t>
-        </is>
-      </c>
-      <c r="G43" s="591"/>
-      <c r="H43" s="591"/>
-      <c r="I43" s="591"/>
-      <c r="J43" s="591"/>
-      <c r="K43" s="591"/>
-      <c r="L43" s="591"/>
-      <c r="M43" s="591"/>
-      <c r="N43" s="591"/>
-      <c r="O43" s="591"/>
-      <c r="P43" s="591"/>
-      <c r="Q43" s="591"/>
-      <c r="R43" s="591"/>
-      <c r="S43" s="591"/>
-      <c r="T43" s="591"/>
-      <c r="U43" s="591"/>
-      <c r="V43" s="591"/>
-      <c r="W43" s="591"/>
-      <c r="X43" s="591"/>
-      <c r="Y43" s="591"/>
-      <c r="Z43" s="591"/>
-      <c r="AA43" s="591"/>
-      <c r="AB43" s="591"/>
-      <c r="AC43" s="591"/>
-      <c r="AD43" s="591"/>
-      <c r="AE43" s="591"/>
-      <c r="AF43" s="589"/>
-      <c r="AG43" s="591"/>
-      <c r="AH43" s="591"/>
-      <c r="AI43" s="591"/>
-      <c r="AJ43" s="591"/>
-      <c r="AK43" s="591"/>
-      <c r="AL43" s="591"/>
-      <c r="AM43" s="591"/>
-      <c r="AN43" s="591"/>
-      <c r="AO43" s="591"/>
-      <c r="AP43" s="591"/>
-      <c r="AQ43" s="591"/>
-      <c r="AR43" s="591"/>
-      <c r="AS43" s="591"/>
-      <c r="AT43" s="591"/>
-      <c r="AU43" s="591"/>
-      <c r="AV43" s="591"/>
-      <c r="AW43" s="591"/>
-      <c r="AX43" s="591"/>
-      <c r="AY43" s="591"/>
-      <c r="AZ43" s="591"/>
-      <c r="BA43" s="591"/>
-      <c r="BB43" s="591"/>
-      <c r="BC43" s="591"/>
-      <c r="BD43" s="591"/>
-      <c r="BE43" s="591"/>
-      <c r="BF43" s="591"/>
-      <c r="BG43" s="591"/>
-    </row>
-    <row r="44" ht="70" customHeight="1" spans="1:59">
-      <c r="A44" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New CRM &amp; Banners Management   “PMDE”</t>
-        </is>
-      </c>
-      <c r="B44" s="579"/>
-      <c r="C44" s="579"/>
-      <c r="D44" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plataforma de gestão de campanhas / banners no MSE</t>
-        </is>
-      </c>
-      <c r="E44" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abr 26</t>
-        </is>
-      </c>
-      <c r="F44" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Permite atuação direta (DBDE) e Campanhas CRM. Plataforma reutilizável para outros canais</t>
-        </is>
-      </c>
-      <c r="G44" s="591"/>
-      <c r="H44" s="591"/>
-      <c r="I44" s="591"/>
-      <c r="J44" s="591"/>
-      <c r="K44" s="589"/>
-      <c r="L44" s="589"/>
-      <c r="M44" s="589"/>
-      <c r="N44" s="589"/>
-      <c r="O44" s="589"/>
-      <c r="P44" s="589"/>
-      <c r="Q44" s="589"/>
-      <c r="R44" s="589"/>
-      <c r="S44" s="589"/>
-      <c r="T44" s="590"/>
-      <c r="U44" s="591"/>
-      <c r="V44" s="591"/>
-      <c r="W44" s="591"/>
-      <c r="X44" s="591"/>
-      <c r="Y44" s="591"/>
-      <c r="Z44" s="591"/>
-      <c r="AA44" s="591"/>
-      <c r="AB44" s="591"/>
-      <c r="AC44" s="591"/>
-      <c r="AD44" s="591"/>
-      <c r="AE44" s="591"/>
-      <c r="AF44" s="591"/>
-      <c r="AG44" s="591"/>
-      <c r="AH44" s="591"/>
-      <c r="AI44" s="591"/>
-      <c r="AJ44" s="591"/>
-      <c r="AK44" s="591"/>
-      <c r="AL44" s="591"/>
-      <c r="AM44" s="591"/>
-      <c r="AN44" s="591"/>
-      <c r="AO44" s="591"/>
-      <c r="AP44" s="591"/>
-      <c r="AQ44" s="591"/>
-      <c r="AR44" s="591"/>
-      <c r="AS44" s="591"/>
-      <c r="AT44" s="591"/>
-      <c r="AU44" s="591"/>
-      <c r="AV44" s="591"/>
-      <c r="AW44" s="591"/>
-      <c r="AX44" s="591"/>
-      <c r="AY44" s="591"/>
-      <c r="AZ44" s="591"/>
-      <c r="BA44" s="591"/>
-      <c r="BB44" s="591"/>
-      <c r="BC44" s="591"/>
-      <c r="BD44" s="591"/>
-      <c r="BE44" s="591"/>
-      <c r="BF44" s="591"/>
-      <c r="BG44" s="591"/>
-    </row>
-    <row r="45" ht="70" customHeight="1" spans="1:59">
-      <c r="A45" s="580" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M-Certificados</t>
-        </is>
-      </c>
-      <c r="B45" s="582"/>
-      <c r="C45" s="582"/>
-      <c r="D45" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avaliar interesse em modernizar aplicativo ou encontrar nova forma de criar Certificados Digitais</t>
-        </is>
-      </c>
-      <c r="E45" s="582"/>
-      <c r="F45" s="581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fern. Cavalheiro: Avaliação técnica
-Jorge Rodrigues: Atualizar páginas públicas</t>
-        </is>
-      </c>
-      <c r="G45" s="582"/>
-      <c r="H45" s="582"/>
-      <c r="I45" s="582"/>
-      <c r="J45" s="582"/>
-      <c r="K45" s="582"/>
-      <c r="L45" s="582"/>
-      <c r="M45" s="582"/>
-      <c r="N45" s="582"/>
-      <c r="O45" s="582"/>
-      <c r="P45" s="582"/>
-      <c r="Q45" s="582"/>
-      <c r="R45" s="582"/>
-      <c r="S45" s="582"/>
-      <c r="T45" s="582"/>
-      <c r="U45" s="582"/>
-      <c r="V45" s="582"/>
-      <c r="W45" s="582"/>
-      <c r="X45" s="582"/>
-      <c r="Y45" s="582"/>
-      <c r="Z45" s="582"/>
-      <c r="AA45" s="582"/>
-      <c r="AB45" s="582"/>
-      <c r="AC45" s="582"/>
-      <c r="AD45" s="582"/>
-      <c r="AE45" s="582"/>
-      <c r="AF45" s="582"/>
-      <c r="AG45" s="582"/>
-      <c r="AH45" s="582"/>
-      <c r="AI45" s="582"/>
-      <c r="AJ45" s="582"/>
-      <c r="AK45" s="582"/>
-      <c r="AL45" s="582"/>
-      <c r="AM45" s="582"/>
-      <c r="AN45" s="582"/>
-      <c r="AO45" s="582"/>
-      <c r="AP45" s="582"/>
-      <c r="AQ45" s="582"/>
-      <c r="AR45" s="582"/>
-      <c r="AS45" s="582"/>
-      <c r="AT45" s="582"/>
-      <c r="AU45" s="582"/>
-      <c r="AV45" s="582"/>
-      <c r="AW45" s="582"/>
-      <c r="AX45" s="582"/>
-      <c r="AY45" s="582"/>
-      <c r="AZ45" s="582"/>
-      <c r="BA45" s="582"/>
-      <c r="BB45" s="582"/>
-      <c r="BC45" s="582"/>
-      <c r="BD45" s="582"/>
-      <c r="BE45" s="582"/>
-      <c r="BF45" s="582"/>
-      <c r="BG45" s="582"/>
-    </row>
-    <row r="46" ht="20" customHeight="1" spans="1:59">
-      <c r="A46" s="576" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API Integration Lab   (8 projetos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="70" customHeight="1" spans="1:59">
-      <c r="A47" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2B – Evoluir de SOAP para “REST”</t>
-        </is>
-      </c>
-      <c r="B47" s="579"/>
-      <c r="C47" s="579"/>
-      <c r="D47" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atualmente, a utilização de APIs baseadas em SOAP representa uma barreira para a integração com parceiros como Milestone e Atlar, afetando clientes como Qima (Certis PT) e Ophelos (Intrum PT). A migração para APIs REST é essencial para aumentar a adoção e facilitar a interoperabilidade com sistemas modernos.</t>
-        </is>
-      </c>
-      <c r="E47" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abr 26</t>
-        </is>
-      </c>
-      <c r="F47" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">User Story 921359: B2B | Alteração do Protocolo da Mensagem | Alteração da Mensagem de SOAP para REST</t>
-        </is>
-      </c>
-      <c r="G47" s="591"/>
-      <c r="H47" s="591"/>
-      <c r="I47" s="591"/>
-      <c r="J47" s="591"/>
-      <c r="K47" s="591"/>
-      <c r="L47" s="591"/>
-      <c r="M47" s="591"/>
-      <c r="N47" s="591"/>
-      <c r="O47" s="591"/>
-      <c r="P47" s="591"/>
-      <c r="Q47" s="591"/>
-      <c r="R47" s="591"/>
-      <c r="S47" s="591"/>
-      <c r="T47" s="590"/>
-      <c r="U47" s="591"/>
-      <c r="V47" s="591"/>
-      <c r="W47" s="591"/>
-      <c r="X47" s="591"/>
-      <c r="Y47" s="591"/>
-      <c r="Z47" s="591"/>
-      <c r="AA47" s="591"/>
-      <c r="AB47" s="591"/>
-      <c r="AC47" s="591"/>
-      <c r="AD47" s="591"/>
-      <c r="AE47" s="591"/>
-      <c r="AF47" s="591"/>
-      <c r="AG47" s="591"/>
-      <c r="AH47" s="591"/>
-      <c r="AI47" s="591"/>
-      <c r="AJ47" s="591"/>
-      <c r="AK47" s="591"/>
-      <c r="AL47" s="591"/>
-      <c r="AM47" s="591"/>
-      <c r="AN47" s="591"/>
-      <c r="AO47" s="591"/>
-      <c r="AP47" s="591"/>
-      <c r="AQ47" s="591"/>
-      <c r="AR47" s="591"/>
-      <c r="AS47" s="591"/>
-      <c r="AT47" s="591"/>
-      <c r="AU47" s="591"/>
-      <c r="AV47" s="591"/>
-      <c r="AW47" s="591"/>
-      <c r="AX47" s="591"/>
-      <c r="AY47" s="591"/>
-      <c r="AZ47" s="591"/>
-      <c r="BA47" s="591"/>
-      <c r="BB47" s="591"/>
-      <c r="BC47" s="591"/>
-      <c r="BD47" s="591"/>
-      <c r="BE47" s="591"/>
-      <c r="BF47" s="591"/>
-      <c r="BG47" s="591"/>
-    </row>
-    <row r="48" ht="70" customHeight="1" spans="1:59">
-      <c r="A48" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2B – ConfirmationCOPB na PSDC</t>
-        </is>
-      </c>
-      <c r="B48" s="579"/>
-      <c r="C48" s="579"/>
-      <c r="D48" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Permitir registar e monitorizar a utilização do serviço ConfirmationCOPB na PSDC, atualmente sem histórico por ser uma consulta e não uma transação.</t>
-        </is>
-      </c>
-      <c r="E48" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F48" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">User Story 962042: B2B | Criação na PSDC | Criação de entrada do serviço ConfirmationCOPB</t>
-        </is>
-      </c>
-      <c r="G48" s="591"/>
-      <c r="H48" s="591"/>
-      <c r="I48" s="591"/>
-      <c r="J48" s="591"/>
-      <c r="K48" s="591"/>
-      <c r="L48" s="591"/>
-      <c r="M48" s="591"/>
-      <c r="N48" s="591"/>
-      <c r="O48" s="591"/>
-      <c r="P48" s="591"/>
-      <c r="Q48" s="591"/>
-      <c r="R48" s="591"/>
-      <c r="S48" s="591"/>
-      <c r="T48" s="591"/>
-      <c r="U48" s="591"/>
-      <c r="V48" s="591"/>
-      <c r="W48" s="591"/>
-      <c r="X48" s="591"/>
-      <c r="Y48" s="591"/>
-      <c r="Z48" s="591"/>
-      <c r="AA48" s="591"/>
-      <c r="AB48" s="591"/>
-      <c r="AC48" s="591"/>
-      <c r="AD48" s="591"/>
-      <c r="AE48" s="591"/>
-      <c r="AF48" s="591"/>
-      <c r="AG48" s="591"/>
-      <c r="AH48" s="591"/>
-      <c r="AI48" s="591"/>
-      <c r="AJ48" s="591"/>
-      <c r="AK48" s="591"/>
-      <c r="AL48" s="591"/>
-      <c r="AM48" s="591"/>
-      <c r="AN48" s="591"/>
-      <c r="AO48" s="591"/>
-      <c r="AP48" s="591"/>
-      <c r="AQ48" s="591"/>
-      <c r="AR48" s="591"/>
-      <c r="AS48" s="591"/>
-      <c r="AT48" s="591"/>
-      <c r="AU48" s="591"/>
-      <c r="AV48" s="591"/>
-      <c r="AW48" s="591"/>
-      <c r="AX48" s="591"/>
-      <c r="AY48" s="591"/>
-      <c r="AZ48" s="591"/>
-      <c r="BA48" s="591"/>
-      <c r="BB48" s="591"/>
-      <c r="BC48" s="591"/>
-      <c r="BD48" s="591"/>
-      <c r="BE48" s="591"/>
-      <c r="BF48" s="591"/>
-      <c r="BG48" s="591"/>
-    </row>
-    <row r="49" ht="70" customHeight="1" spans="1:59">
-      <c r="A49" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2B – Transferência Nacional | Aceitar o IBAN além do NIB</t>
-        </is>
-      </c>
-      <c r="B49" s="579"/>
-      <c r="C49" s="579"/>
-      <c r="D49" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pretende-se que a ordem de transferência nacional aceite também o IBAN da conta a creditar, além do NIB atualmente usado.O campo XferInfo.DepAcctIdTo.AcctId deverá permitir IBAN como alternativa ao NIB.</t>
-        </is>
-      </c>
-      <c r="E49" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fev 26</t>
-        </is>
-      </c>
-      <c r="F49" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">User Story 926458: B2B | Transferências | Passar a fazer transferências também por IBAN</t>
-        </is>
-      </c>
-      <c r="G49" s="591"/>
-      <c r="H49" s="591"/>
-      <c r="I49" s="591"/>
-      <c r="J49" s="591"/>
-      <c r="K49" s="590"/>
-      <c r="L49" s="591"/>
-      <c r="M49" s="591"/>
-      <c r="N49" s="591"/>
-      <c r="O49" s="591"/>
-      <c r="P49" s="591"/>
-      <c r="Q49" s="591"/>
-      <c r="R49" s="591"/>
-      <c r="S49" s="591"/>
-      <c r="T49" s="591"/>
-      <c r="U49" s="591"/>
-      <c r="V49" s="591"/>
-      <c r="W49" s="591"/>
-      <c r="X49" s="591"/>
-      <c r="Y49" s="591"/>
-      <c r="Z49" s="591"/>
-      <c r="AA49" s="591"/>
-      <c r="AB49" s="591"/>
-      <c r="AC49" s="591"/>
-      <c r="AD49" s="591"/>
-      <c r="AE49" s="591"/>
-      <c r="AF49" s="591"/>
-      <c r="AG49" s="591"/>
-      <c r="AH49" s="591"/>
-      <c r="AI49" s="591"/>
-      <c r="AJ49" s="591"/>
-      <c r="AK49" s="591"/>
-      <c r="AL49" s="591"/>
-      <c r="AM49" s="591"/>
-      <c r="AN49" s="591"/>
-      <c r="AO49" s="591"/>
-      <c r="AP49" s="591"/>
-      <c r="AQ49" s="591"/>
-      <c r="AR49" s="591"/>
-      <c r="AS49" s="591"/>
-      <c r="AT49" s="591"/>
-      <c r="AU49" s="591"/>
-      <c r="AV49" s="591"/>
-      <c r="AW49" s="591"/>
-      <c r="AX49" s="591"/>
-      <c r="AY49" s="591"/>
-      <c r="AZ49" s="591"/>
-      <c r="BA49" s="591"/>
-      <c r="BB49" s="591"/>
-      <c r="BC49" s="591"/>
-      <c r="BD49" s="591"/>
-      <c r="BE49" s="591"/>
-      <c r="BF49" s="591"/>
-      <c r="BG49" s="591"/>
-    </row>
-    <row r="50" ht="70" customHeight="1" spans="1:59">
-      <c r="A50" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2B – Open banking PISP</t>
-        </is>
-      </c>
-      <c r="B50" s="579"/>
-      <c r="C50" s="579"/>
-      <c r="D50" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Permitir a execução de operações através de outros Bancos, em linha com o que é feito atualmente no iziBizi.</t>
-        </is>
-      </c>
-      <c r="E50" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F50" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">User Story 956426: B2B | Criação de Serviços | PISP</t>
-        </is>
-      </c>
-      <c r="G50" s="591"/>
-      <c r="H50" s="591"/>
-      <c r="I50" s="591"/>
-      <c r="J50" s="591"/>
-      <c r="K50" s="591"/>
-      <c r="L50" s="591"/>
-      <c r="M50" s="591"/>
-      <c r="N50" s="591"/>
-      <c r="O50" s="591"/>
-      <c r="P50" s="591"/>
-      <c r="Q50" s="591"/>
-      <c r="R50" s="591"/>
-      <c r="S50" s="591"/>
-      <c r="T50" s="591"/>
-      <c r="U50" s="591"/>
-      <c r="V50" s="591"/>
-      <c r="W50" s="591"/>
-      <c r="X50" s="591"/>
-      <c r="Y50" s="591"/>
-      <c r="Z50" s="591"/>
-      <c r="AA50" s="591"/>
-      <c r="AB50" s="591"/>
-      <c r="AC50" s="591"/>
-      <c r="AD50" s="591"/>
-      <c r="AE50" s="591"/>
-      <c r="AF50" s="591"/>
-      <c r="AG50" s="591"/>
-      <c r="AH50" s="591"/>
-      <c r="AI50" s="591"/>
-      <c r="AJ50" s="591"/>
-      <c r="AK50" s="591"/>
-      <c r="AL50" s="591"/>
-      <c r="AM50" s="591"/>
-      <c r="AN50" s="591"/>
-      <c r="AO50" s="591"/>
-      <c r="AP50" s="591"/>
-      <c r="AQ50" s="591"/>
-      <c r="AR50" s="591"/>
-      <c r="AS50" s="591"/>
-      <c r="AT50" s="591"/>
-      <c r="AU50" s="591"/>
-      <c r="AV50" s="591"/>
-      <c r="AW50" s="591"/>
-      <c r="AX50" s="591"/>
-      <c r="AY50" s="591"/>
-      <c r="AZ50" s="591"/>
-      <c r="BA50" s="591"/>
-      <c r="BB50" s="591"/>
-      <c r="BC50" s="591"/>
-      <c r="BD50" s="591"/>
-      <c r="BE50" s="591"/>
-      <c r="BF50" s="591"/>
-      <c r="BG50" s="591"/>
-    </row>
-    <row r="51" ht="70" customHeight="1" spans="1:59">
-      <c r="A51" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2B – Motivo Devolução TRFs</t>
-        </is>
-      </c>
-      <c r="B51" s="579"/>
-      <c r="C51" s="579"/>
-      <c r="D51" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Permitir a consulta do detalhe do motivo da devolução de uma transferência. Caso de uso: Solverde, que solicitou este serviço.</t>
-        </is>
-      </c>
-      <c r="E51" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F51" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">User Story 966231: B2B | Transferências - Motivo devolução</t>
-        </is>
-      </c>
-      <c r="G51" s="591"/>
-      <c r="H51" s="591"/>
-      <c r="I51" s="591"/>
-      <c r="J51" s="591"/>
-      <c r="K51" s="591"/>
-      <c r="L51" s="591"/>
-      <c r="M51" s="591"/>
-      <c r="N51" s="591"/>
-      <c r="O51" s="591"/>
-      <c r="P51" s="591"/>
-      <c r="Q51" s="591"/>
-      <c r="R51" s="591"/>
-      <c r="S51" s="591"/>
-      <c r="T51" s="591"/>
-      <c r="U51" s="591"/>
-      <c r="V51" s="591"/>
-      <c r="W51" s="591"/>
-      <c r="X51" s="591"/>
-      <c r="Y51" s="591"/>
-      <c r="Z51" s="591"/>
-      <c r="AA51" s="591"/>
-      <c r="AB51" s="591"/>
-      <c r="AC51" s="591"/>
-      <c r="AD51" s="591"/>
-      <c r="AE51" s="591"/>
-      <c r="AF51" s="591"/>
-      <c r="AG51" s="591"/>
-      <c r="AH51" s="591"/>
-      <c r="AI51" s="591"/>
-      <c r="AJ51" s="591"/>
-      <c r="AK51" s="591"/>
-      <c r="AL51" s="591"/>
-      <c r="AM51" s="591"/>
-      <c r="AN51" s="591"/>
-      <c r="AO51" s="591"/>
-      <c r="AP51" s="591"/>
-      <c r="AQ51" s="591"/>
-      <c r="AR51" s="591"/>
-      <c r="AS51" s="591"/>
-      <c r="AT51" s="591"/>
-      <c r="AU51" s="591"/>
-      <c r="AV51" s="591"/>
-      <c r="AW51" s="591"/>
-      <c r="AX51" s="591"/>
-      <c r="AY51" s="591"/>
-      <c r="AZ51" s="591"/>
-      <c r="BA51" s="591"/>
-      <c r="BB51" s="591"/>
-      <c r="BC51" s="591"/>
-      <c r="BD51" s="591"/>
-      <c r="BE51" s="591"/>
-      <c r="BF51" s="591"/>
-      <c r="BG51" s="591"/>
-    </row>
-    <row r="52" ht="70" customHeight="1" spans="1:59">
-      <c r="A52" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2B/MultiBancário Eventos Kafka</t>
-        </is>
-      </c>
-      <c r="B52" s="579"/>
-      <c r="C52" s="579"/>
-      <c r="D52" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Serviço que irá permitir integração nos ERP’s das empresas com protocolos de confirming, as mensagens sobre o estado atual das faturas</t>
-        </is>
-      </c>
-      <c r="E52" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mai 26</t>
-        </is>
-      </c>
-      <c r="F52" s="578"/>
-      <c r="G52" s="591"/>
-      <c r="H52" s="591"/>
-      <c r="I52" s="591"/>
-      <c r="J52" s="591"/>
-      <c r="K52" s="591"/>
-      <c r="L52" s="591"/>
-      <c r="M52" s="591"/>
-      <c r="N52" s="591"/>
-      <c r="O52" s="591"/>
-      <c r="P52" s="591"/>
-      <c r="Q52" s="591"/>
-      <c r="R52" s="591"/>
-      <c r="S52" s="591"/>
-      <c r="T52" s="591"/>
-      <c r="U52" s="591"/>
-      <c r="V52" s="591"/>
-      <c r="W52" s="591"/>
-      <c r="X52" s="590"/>
-      <c r="Y52" s="591"/>
-      <c r="Z52" s="591"/>
-      <c r="AA52" s="591"/>
-      <c r="AB52" s="591"/>
-      <c r="AC52" s="591"/>
-      <c r="AD52" s="591"/>
-      <c r="AE52" s="591"/>
-      <c r="AF52" s="591"/>
-      <c r="AG52" s="591"/>
-      <c r="AH52" s="591"/>
-      <c r="AI52" s="591"/>
-      <c r="AJ52" s="591"/>
-      <c r="AK52" s="591"/>
-      <c r="AL52" s="591"/>
-      <c r="AM52" s="591"/>
-      <c r="AN52" s="591"/>
-      <c r="AO52" s="591"/>
-      <c r="AP52" s="591"/>
-      <c r="AQ52" s="591"/>
-      <c r="AR52" s="591"/>
-      <c r="AS52" s="591"/>
-      <c r="AT52" s="591"/>
-      <c r="AU52" s="591"/>
-      <c r="AV52" s="591"/>
-      <c r="AW52" s="591"/>
-      <c r="AX52" s="591"/>
-      <c r="AY52" s="591"/>
-      <c r="AZ52" s="591"/>
-      <c r="BA52" s="591"/>
-      <c r="BB52" s="591"/>
-      <c r="BC52" s="591"/>
-      <c r="BD52" s="591"/>
-      <c r="BE52" s="591"/>
-      <c r="BF52" s="591"/>
-      <c r="BG52" s="591"/>
-    </row>
-    <row r="53" ht="70" customHeight="1" spans="1:59">
-      <c r="A53" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">iziBizi – Refresh Tokens</t>
-        </is>
-      </c>
-      <c r="B53" s="579"/>
-      <c r="C53" s="579"/>
-      <c r="D53" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No MSE, após alteração da password, o token do lado do iziBizi não é atualizado. Isto bloqueia diariamente o acesso para utilizadores com iziBizi ativo.</t>
-        </is>
-      </c>
-      <c r="E53" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F53" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">User Story 973193: iziBizi | Melhorias | Refresh Tokens</t>
-        </is>
-      </c>
-      <c r="G53" s="591"/>
-      <c r="H53" s="591"/>
-      <c r="I53" s="591"/>
-      <c r="J53" s="591"/>
-      <c r="K53" s="591"/>
-      <c r="L53" s="591"/>
-      <c r="M53" s="591"/>
-      <c r="N53" s="591"/>
-      <c r="O53" s="591"/>
-      <c r="P53" s="591"/>
-      <c r="Q53" s="591"/>
-      <c r="R53" s="591"/>
-      <c r="S53" s="591"/>
-      <c r="T53" s="591"/>
-      <c r="U53" s="591"/>
-      <c r="V53" s="591"/>
-      <c r="W53" s="591"/>
-      <c r="X53" s="591"/>
-      <c r="Y53" s="591"/>
-      <c r="Z53" s="591"/>
-      <c r="AA53" s="591"/>
-      <c r="AB53" s="591"/>
-      <c r="AC53" s="591"/>
-      <c r="AD53" s="591"/>
-      <c r="AE53" s="591"/>
-      <c r="AF53" s="591"/>
-      <c r="AG53" s="591"/>
-      <c r="AH53" s="591"/>
-      <c r="AI53" s="591"/>
-      <c r="AJ53" s="591"/>
-      <c r="AK53" s="591"/>
-      <c r="AL53" s="591"/>
-      <c r="AM53" s="591"/>
-      <c r="AN53" s="591"/>
-      <c r="AO53" s="591"/>
-      <c r="AP53" s="591"/>
-      <c r="AQ53" s="591"/>
-      <c r="AR53" s="591"/>
-      <c r="AS53" s="591"/>
-      <c r="AT53" s="591"/>
-      <c r="AU53" s="591"/>
-      <c r="AV53" s="591"/>
-      <c r="AW53" s="591"/>
-      <c r="AX53" s="591"/>
-      <c r="AY53" s="591"/>
-      <c r="AZ53" s="591"/>
-      <c r="BA53" s="591"/>
-      <c r="BB53" s="591"/>
-      <c r="BC53" s="591"/>
-      <c r="BD53" s="591"/>
-      <c r="BE53" s="591"/>
-      <c r="BF53" s="591"/>
-      <c r="BG53" s="591"/>
-    </row>
-    <row r="54" ht="70" customHeight="1" spans="1:59">
-      <c r="A54" s="577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M-Contabilidade – Refresh Tokens</t>
-        </is>
-      </c>
-      <c r="B54" s="579"/>
-      <c r="C54" s="579"/>
-      <c r="D54" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No MSE, após alteração da password, o token do lado do M Contabilidade não é atualizado. Isto bloqueia diariamente o acesso para utilizadores com M Contabilidade ativo.</t>
-        </is>
-      </c>
-      <c r="E54" s="579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c r="F54" s="578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">User Story 973284: M Contabilidade| Melhorias | Refresh Tokens</t>
-        </is>
-      </c>
-      <c r="G54" s="591"/>
-      <c r="H54" s="591"/>
-      <c r="I54" s="591"/>
-      <c r="J54" s="591"/>
-      <c r="K54" s="591"/>
-      <c r="L54" s="591"/>
-      <c r="M54" s="591"/>
-      <c r="N54" s="591"/>
-      <c r="O54" s="591"/>
-      <c r="P54" s="591"/>
-      <c r="Q54" s="591"/>
-      <c r="R54" s="591"/>
-      <c r="S54" s="591"/>
-      <c r="T54" s="591"/>
-      <c r="U54" s="591"/>
-      <c r="V54" s="591"/>
-      <c r="W54" s="591"/>
-      <c r="X54" s="591"/>
-      <c r="Y54" s="591"/>
-      <c r="Z54" s="591"/>
-      <c r="AA54" s="591"/>
-      <c r="AB54" s="591"/>
-      <c r="AC54" s="591"/>
-      <c r="AD54" s="591"/>
-      <c r="AE54" s="591"/>
-      <c r="AF54" s="591"/>
-      <c r="AG54" s="591"/>
-      <c r="AH54" s="591"/>
-      <c r="AI54" s="591"/>
-      <c r="AJ54" s="591"/>
-      <c r="AK54" s="591"/>
-      <c r="AL54" s="591"/>
-      <c r="AM54" s="591"/>
-      <c r="AN54" s="591"/>
-      <c r="AO54" s="591"/>
-      <c r="AP54" s="591"/>
-      <c r="AQ54" s="591"/>
-      <c r="AR54" s="591"/>
-      <c r="AS54" s="591"/>
-      <c r="AT54" s="591"/>
-      <c r="AU54" s="591"/>
-      <c r="AV54" s="591"/>
-      <c r="AW54" s="591"/>
-      <c r="AX54" s="591"/>
-      <c r="AY54" s="591"/>
-      <c r="AZ54" s="591"/>
-      <c r="BA54" s="591"/>
-      <c r="BB54" s="591"/>
-      <c r="BC54" s="591"/>
-      <c r="BD54" s="591"/>
-      <c r="BE54" s="591"/>
-      <c r="BF54" s="591"/>
-      <c r="BG54" s="591"/>
-    </row>
-    <row r="55" ht="60" customHeight="1" spans="1:59">
-      <c r="A55" s="593" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notas:  • PO e Stakeholders a preencher em coordenação com Pedro e Ivânia.  • Banda verde-clara = período de Qualidade/Certificação (entre QUA e PROD); verde-escuro = passagem a Produção (go-live).  • Datas indicadas como «Mês/Ano» (ex. «Abr 26») são aproximadas — colocadas no início do mês.  • Go-lives anteriores a 2026 não têm marca na grelha (ver coluna «Data passagem a produção»).  • Dados extraídos da sheet «Overview Geral»; atualizar semanalmente.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="31">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:BG1"/>
     <mergeCell ref="A2:F2"/>
@@ -20396,7 +18805,6 @@
     <mergeCell ref="AF2:AH2"/>
     <mergeCell ref="AJ2:AL2"/>
     <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AR2:AT2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
@@ -20415,12 +18823,7 @@
     <mergeCell ref="AT3:AX3"/>
     <mergeCell ref="AY3:BB3"/>
     <mergeCell ref="BC3:BG3"/>
-    <mergeCell ref="A5:BG5"/>
-    <mergeCell ref="A18:BG18"/>
-    <mergeCell ref="A37:BG37"/>
-    <mergeCell ref="A41:BG41"/>
-    <mergeCell ref="A46:BG46"/>
-    <mergeCell ref="A55:BG55"/>
+    <mergeCell ref="A35:BG35"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" scale="40"/>
